--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54814224-581F-4218-81BB-2753C79B15A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBDA185-6F98-4AF3-9123-C5EB55D6ACAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28710" yWindow="345" windowWidth="24615" windowHeight="14175" firstSheet="2" activeTab="11" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" activeTab="9" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="433">
   <si>
     <t>Gene</t>
   </si>
@@ -145,9 +145,6 @@
   </si>
   <si>
     <t>Tumour content not available</t>
-  </si>
-  <si>
-    <t>Please note: The neoplastic cell content of this sample is not available. The presence of low-level variants cannot be excluded. This assay has been validated to detect as little as 5% mutant DNA in a background of wildtype DNA.</t>
   </si>
   <si>
     <t>&lt;10% neoplastic cells (CLL)</t>
@@ -659,9 +656,6 @@
     <t>TET2 mutations are recurrent in AML.
 TET2 comutation has been reported in AML with CBFB::MYH11, AML with KMT2A rearrangement and frequently in AML with NPM1 mutation (WHO 5th Edition).
 TET2 is recurrently mutated in various haematological malignancies, however, some TET2 alterations can be age related or present in other neoplasms. Please correlate with other clinical and pathological findings for interpretation.</t>
-  </si>
-  <si>
-    <t>WT1 mutation is reported in approximately 15% of AML cases (DOI: 10.1182/blood-2022-166323). It has been associated with an increased risk of post transplant relapse in patients with intermediae risk genetics (DOI: 10.1182/blood-2022-166323).</t>
   </si>
   <si>
     <t>ABL1 TKD mutations are a known mechanism of  resistance in CML, particularly in patients with suboptimal response or progression to accelerated or blast phase (DOI: 10.1182/blood-2010-12-326405). Please correlate with current clinical guidelines for therapeutic indications.</t>
@@ -1920,6 +1914,48 @@
   </si>
   <si>
     <t xml:space="preserve">CLL reporting caveat (applied to all cases with a CNV) </t>
+  </si>
+  <si>
+    <t>WT1 mutation is reported in approximately 15% of AML cases (DOI: 10.1182/blood-2022-166323). It has been associated with an increased risk of post transplant relapse in patients with intermediate risk genetics (DOI: 10.1182/blood-2022-166323).</t>
+  </si>
+  <si>
+    <t>Insufficient DNA</t>
+  </si>
+  <si>
+    <t>Please note the quantity of DNA obtained from this sample did not meet the quality criteria for NGS testing. Please send a repeat sample, if possible.</t>
+  </si>
+  <si>
+    <t>Copy number analysis has not been performed, as it has only been validated for samples with ≥40% neoplastic content.</t>
+  </si>
+  <si>
+    <t>&lt;40% tumour content CNV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNVs statistically significant and pertinent but below the validation threshold (threshold: segmental mean &gt;=0.2) </t>
+  </si>
+  <si>
+    <t>The copy number variation plot suggests xxxxxxx however this is below the validated threshold for this assay. This could be due to lower tumour content of the sample or the presence of subclones. Validation of this finding using xxxxxx method is recommended before any clinical interpretation.</t>
+  </si>
+  <si>
+    <t>CNVs statistically significant and pertinent but below the validation threshold (threshold: segmental mean &gt;=0.2) - no available validation method (most of the CNVs in solid tumour sample)</t>
+  </si>
+  <si>
+    <t>The copy number variation plot suggests xxxxxxx however this is below the validated threshold for this assay. This could be due to lower tumour content of the sample or the presence of subclones. A sample with a higher tumour content may be more informative about the validity of this finding if applicable.</t>
+  </si>
+  <si>
+    <t>Poor sample quality (sw-nscr score &gt;0.02)</t>
+  </si>
+  <si>
+    <t>CNV analysis by NGS was not performed for this sample due to a high noise score, which prevented reliable assessment of copy number variation.</t>
+  </si>
+  <si>
+    <t>High genomic complexity (gw-dsrptn-scr &gt;0.02)</t>
+  </si>
+  <si>
+    <t>CNV analysis by NGS was not performed for this sample due to high genome wide disruption, which prevented reliable assessment of copy number variation.</t>
+  </si>
+  <si>
+    <t>The neoplastic cell content of this sample is not available. The presence of low-level variants cannot be excluded. This assay has been validated to detect small variants present at ≥1% mutant DNA in a background of wild-type DNA. Copy number analysis has not been performed as it has only been validated for samples with ≥40% neoplastic content.</t>
   </si>
 </sst>
 </file>
@@ -2423,7 +2459,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F2" s="6"/>
     </row>
@@ -2432,7 +2468,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2440,7 +2476,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="150" x14ac:dyDescent="0.2">
@@ -2448,367 +2484,367 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="255" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="167.25" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="333" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="285" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="345" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="195" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>167</v>
+        <v>419</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2818,7 +2854,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71C181D1-9A1A-4B63-974F-1376CEB759F1}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.21875" customWidth="1"/>
@@ -2835,10 +2871,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2846,7 +2882,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -2854,39 +2890,87 @@
         <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>26</v>
+    </row>
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>423</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>424</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>426</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>428</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>430</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -2916,79 +3000,79 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -3007,10 +3091,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3021,10 +3105,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -3032,10 +3116,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3043,10 +3127,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3054,10 +3138,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3065,10 +3149,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3076,10 +3160,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3087,10 +3171,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3098,10 +3182,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3109,10 +3193,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3120,10 +3204,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3131,10 +3215,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3142,10 +3226,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3153,10 +3237,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3164,10 +3248,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3175,10 +3259,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3186,10 +3270,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3197,114 +3281,114 @@
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>371</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>372</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>374</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>377</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>380</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>382</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>383</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>384</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>386</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>387</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" s="18"/>
       <c r="B25" s="17" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="18"/>
       <c r="B26" s="17" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A27" s="18"/>
       <c r="B27" s="17" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>395</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -3339,7 +3423,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D2" s="6"/>
     </row>
@@ -3348,7 +3432,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3356,7 +3440,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3364,380 +3448,380 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="120" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="285" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="369" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -3769,7 +3853,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="285" x14ac:dyDescent="0.25">
@@ -3777,7 +3861,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D3" s="6"/>
     </row>
@@ -3786,7 +3870,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3794,360 +3878,360 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="120" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="135" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="150" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="135" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="270" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B48" s="4"/>
     </row>
     <row r="49" spans="1:2" ht="195" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -4178,56 +4262,56 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -4258,7 +4342,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4266,7 +4350,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4274,7 +4358,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4282,207 +4366,207 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="240" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>
@@ -4505,127 +4589,127 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="180" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -4654,7 +4738,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -4662,7 +4746,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -4671,47 +4755,47 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -4743,85 +4827,85 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="375" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="345" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="180" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="345" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="210" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -4852,75 +4936,75 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBDA185-6F98-4AF3-9123-C5EB55D6ACAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61E6D09-B097-4CC6-B3F5-0DF9E509B4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" activeTab="9" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" activeTab="2" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -782,17 +782,6 @@
   </si>
   <si>
     <t>NPM1 mutation is reported in a rare subset of CMML patients and is associated with an aggressive clinical course with rapid progression to acute leukaemia (ICC 2022). In the context of known CMML, detection of NPM1 is not used as a molecular defining feature of AML.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V617F
-The presence of a pathogenic JAK2 V617F variant is supportive of a myeloproliferative neoplasm in the correct clinical context. JAK2 V617F is reported in over 97% of polycythaemia vera cases and in approximately 50% of primary myelofibrosis and essential thrombocythaemia cases (WHO 5th Edition).
-Exon 12
-The presence of a pathogenic JAK2 exon 12 variant is most commonly associated with a diagnosis of PV (WHO 5th Edition).
-Low level:
-Low-level JAK2 mutations may represent age-related CHIP, though they are associated with an increased risk of thrombotic events and potential progression. A definitive diagnosis of MPN requires correlation with blood counts, bone marrow morphology, and clinical features, as per WHO/ICC criteria.
-CMML
-JAK2 mutations have been reported in MPN and CMML, correlation of clinical features with variant allele frequency and the presence of additional variants may aid in diagnosis (WHO 5th Edition). 
-</t>
   </si>
   <si>
     <t>NRAS is commonly mutated in CMML and is associated with increased risk of transformation (WHO 5th Edition, CPSS-Mol).
@@ -1956,6 +1945,19 @@
   </si>
   <si>
     <t>The neoplastic cell content of this sample is not available. The presence of low-level variants cannot be excluded. This assay has been validated to detect small variants present at ≥1% mutant DNA in a background of wild-type DNA. Copy number analysis has not been performed as it has only been validated for samples with ≥40% neoplastic content.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAK2 V617F chr9:5073770 
+JAK2 Exon 12 chr9:5069925-5070052
+V617F
+The presence of a pathogenic JAK2 V617F variant is supportive of a myeloproliferative neoplasm in the correct clinical context. JAK2 V617F is reported in over 97% of polycythaemia vera cases and in approximately 50% of primary myelofibrosis and essential thrombocythaemia cases (WHO 5th Edition).
+Exon 12
+The presence of a pathogenic JAK2 exon 12 variant is most commonly associated with a diagnosis of PV (WHO 5th Edition).
+Low level:
+Low-level JAK2 mutations may represent age-related CHIP, though they are associated with an increased risk of thrombotic events and potential progression. A definitive diagnosis of MPN requires correlation with blood counts, bone marrow morphology, and clinical features, as per WHO/ICC criteria.
+CMML
+JAK2 mutations have been reported in MPN and CMML, correlation of clinical features with variant allele frequency and the presence of additional variants may aid in diagnosis (WHO 5th Edition). 
+</t>
   </si>
 </sst>
 </file>
@@ -2505,10 +2507,10 @@
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>330</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.2">
@@ -2524,7 +2526,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2548,7 +2550,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2580,7 +2582,7 @@
         <v>75</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -2612,7 +2614,7 @@
         <v>81</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -2825,10 +2827,10 @@
     </row>
     <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>332</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2836,7 +2838,7 @@
         <v>119</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2871,10 +2873,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2898,7 +2900,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2927,50 +2929,50 @@
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>423</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>425</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>426</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>427</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>429</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -3005,74 +3007,74 @@
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>409</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>411</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -3091,10 +3093,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3141,7 +3143,7 @@
         <v>47</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3152,7 +3154,7 @@
         <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3207,7 +3209,7 @@
         <v>60</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3270,10 +3272,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3289,106 +3291,106 @@
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>370</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>373</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>376</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>379</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="B23" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="C23" s="15" t="s">
         <v>382</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="C24" s="15" t="s">
         <v>385</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" s="18"/>
       <c r="B25" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>387</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="18"/>
       <c r="B26" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>389</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A27" s="18"/>
       <c r="B27" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>391</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="B28" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="C28" s="15" t="s">
         <v>394</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -3423,7 +3425,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D2" s="6"/>
     </row>
@@ -3432,7 +3434,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3440,7 +3442,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3448,7 +3450,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -3456,7 +3458,7 @@
         <v>121</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -3464,7 +3466,7 @@
         <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -3472,7 +3474,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -3480,7 +3482,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3488,7 +3490,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3496,7 +3498,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
@@ -3504,7 +3506,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3512,7 +3514,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3520,7 +3522,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="285" x14ac:dyDescent="0.2">
@@ -3528,7 +3530,7 @@
         <v>73</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -3536,7 +3538,7 @@
         <v>74</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3544,7 +3546,7 @@
         <v>75</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -3552,7 +3554,7 @@
         <v>77</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -3568,7 +3570,7 @@
         <v>79</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3576,7 +3578,7 @@
         <v>81</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3584,7 +3586,7 @@
         <v>82</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -3597,7 +3599,7 @@
         <v>86</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -3605,7 +3607,7 @@
         <v>87</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -3613,7 +3615,7 @@
         <v>105</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -3621,7 +3623,7 @@
         <v>88</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -3629,7 +3631,7 @@
         <v>90</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -3637,7 +3639,7 @@
         <v>122</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -3645,7 +3647,7 @@
         <v>92</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -3653,7 +3655,7 @@
         <v>96</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3661,7 +3663,7 @@
         <v>97</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -3669,7 +3671,7 @@
         <v>99</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3677,7 +3679,7 @@
         <v>101</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -3685,7 +3687,7 @@
         <v>102</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="369" customHeight="1" x14ac:dyDescent="0.2">
@@ -3693,7 +3695,7 @@
         <v>103</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -3701,7 +3703,7 @@
         <v>104</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -3709,7 +3711,7 @@
         <v>107</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -3717,7 +3719,7 @@
         <v>108</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -3725,7 +3727,7 @@
         <v>123</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -3733,7 +3735,7 @@
         <v>109</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -3741,7 +3743,7 @@
         <v>124</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -3749,7 +3751,7 @@
         <v>111</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -3757,7 +3759,7 @@
         <v>112</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3765,7 +3767,7 @@
         <v>113</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3773,7 +3775,7 @@
         <v>114</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -3781,7 +3783,7 @@
         <v>115</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="150" x14ac:dyDescent="0.2">
@@ -3789,7 +3791,7 @@
         <v>116</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -3797,15 +3799,15 @@
         <v>118</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>334</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
@@ -3813,7 +3815,7 @@
         <v>119</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -3821,7 +3823,7 @@
         <v>120</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -3942,7 +3944,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -4025,12 +4027,12 @@
         <v>186</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="270" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" ht="315" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>191</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
@@ -4070,7 +4072,7 @@
         <v>97</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -4078,7 +4080,7 @@
         <v>99</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4086,7 +4088,7 @@
         <v>101</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4094,7 +4096,7 @@
         <v>102</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -4102,7 +4104,7 @@
         <v>103</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4110,7 +4112,7 @@
         <v>105</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4118,10 +4120,10 @@
         <v>88</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4129,7 +4131,7 @@
         <v>87</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4137,7 +4139,7 @@
         <v>107</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4145,7 +4147,7 @@
         <v>108</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4153,7 +4155,7 @@
         <v>109</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4161,7 +4163,7 @@
         <v>110</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -4169,7 +4171,7 @@
         <v>111</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4177,7 +4179,7 @@
         <v>112</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4185,7 +4187,7 @@
         <v>113</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4193,7 +4195,7 @@
         <v>125</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4201,7 +4203,7 @@
         <v>115</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4209,7 +4211,7 @@
         <v>116</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4217,7 +4219,7 @@
         <v>118</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -4231,7 +4233,7 @@
         <v>120</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -4262,7 +4264,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4270,15 +4272,15 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4286,7 +4288,7 @@
         <v>84</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F5" s="6"/>
     </row>
@@ -4295,7 +4297,7 @@
         <v>105</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4303,7 +4305,7 @@
         <v>97</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4311,7 +4313,7 @@
         <v>116</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -4342,7 +4344,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4350,7 +4352,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4358,7 +4360,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4366,7 +4368,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4374,7 +4376,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4382,7 +4384,7 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4390,7 +4392,7 @@
         <v>127</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4398,7 +4400,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4406,7 +4408,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4414,7 +4416,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4422,7 +4424,7 @@
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4430,7 +4432,7 @@
         <v>74</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4438,7 +4440,7 @@
         <v>76</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -4446,15 +4448,15 @@
         <v>80</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>336</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4462,7 +4464,7 @@
         <v>85</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -4470,7 +4472,7 @@
         <v>105</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4478,7 +4480,7 @@
         <v>89</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4486,7 +4488,7 @@
         <v>128</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4494,7 +4496,7 @@
         <v>91</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -4502,7 +4504,7 @@
         <v>94</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -4510,7 +4512,7 @@
         <v>95</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -4518,47 +4520,47 @@
         <v>97</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>338</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>340</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>342</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>344</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>346</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="240" x14ac:dyDescent="0.2">
@@ -4566,7 +4568,7 @@
         <v>116</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -4589,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4597,7 +4599,7 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4605,15 +4607,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4621,7 +4623,7 @@
         <v>82</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4629,39 +4631,39 @@
         <v>84</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>354</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>356</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>357</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4669,15 +4671,15 @@
         <v>106</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>359</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="180" x14ac:dyDescent="0.2">
@@ -4685,7 +4687,7 @@
         <v>113</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -4693,7 +4695,7 @@
         <v>125</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4701,15 +4703,15 @@
         <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>360</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -4738,7 +4740,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -4746,7 +4748,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -4755,7 +4757,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
@@ -4763,7 +4765,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -4771,7 +4773,7 @@
         <v>94</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -4779,7 +4781,7 @@
         <v>100</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4787,7 +4789,7 @@
         <v>109</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
@@ -4795,7 +4797,7 @@
         <v>116</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -4827,7 +4829,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4835,7 +4837,7 @@
         <v>73</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="270" x14ac:dyDescent="0.2">
@@ -4843,7 +4845,7 @@
         <v>129</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -4857,7 +4859,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="375" x14ac:dyDescent="0.2">
@@ -4865,7 +4867,7 @@
         <v>94</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="345" x14ac:dyDescent="0.2">
@@ -4873,15 +4875,15 @@
         <v>97</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>276</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="180" x14ac:dyDescent="0.2">
@@ -4889,7 +4891,7 @@
         <v>98</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="345" x14ac:dyDescent="0.2">
@@ -4897,7 +4899,7 @@
         <v>105</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="210" x14ac:dyDescent="0.2">
@@ -4936,15 +4938,15 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4952,7 +4954,7 @@
         <v>89</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4960,7 +4962,7 @@
         <v>97</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4968,7 +4970,7 @@
         <v>105</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4976,35 +4978,35 @@
         <v>80</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61E6D09-B097-4CC6-B3F5-0DF9E509B4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F836837-A3B0-4CA1-B913-4B26A9765DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" activeTab="2" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" activeTab="5" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -1539,11 +1539,6 @@
 RHOA variants are most frequently reported in TFHL, but have also been reported rarely in other T cell lymphomas DOI: 10.1182/blood-2015-06-644948).</t>
   </si>
   <si>
-    <t>STAT5B variants are reported in a number of T lyphoid malignancies (WHO 5th Edition).
-T-large granular lymphocytic leukaemia
-STAT3 and STAT5B mutations are the most commonly recognized gain of function genetic lesions in T LGL (WHO 5th edition).</t>
-  </si>
-  <si>
     <t>TET2 is recurrently mutated in various haematological malignancies, including nodal T-follicular helper cell lymphoma, angioimmunoblastic type (TFH-AITL) (WHO 5th Edition). Some TET2 alterations can however be age related or present in other neoplasms. Please correlate with other clinical and pathological findings for interpretation.</t>
   </si>
   <si>
@@ -1958,6 +1953,11 @@
 CMML
 JAK2 mutations have been reported in MPN and CMML, correlation of clinical features with variant allele frequency and the presence of additional variants may aid in diagnosis (WHO 5th Edition). 
 </t>
+  </si>
+  <si>
+    <t>STAT5B variants are reported in a number of T lymphoid malignancies (WHO 5th Edition).
+T-large granular lymphocytic leukaemia
+STAT3 and STAT5B mutations are the most commonly recognized gain of function genetic lesions in T LGL (WHO 5th edition).</t>
   </si>
 </sst>
 </file>
@@ -2507,10 +2507,10 @@
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>329</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.2">
@@ -2614,7 +2614,7 @@
         <v>81</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -2827,10 +2827,10 @@
     </row>
     <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>331</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2838,7 +2838,7 @@
         <v>119</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2873,10 +2873,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2900,7 +2900,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2929,50 +2929,50 @@
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>418</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>422</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>424</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>426</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>427</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>428</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -3007,74 +3007,74 @@
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>408</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>410</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
   </sheetData>
@@ -3093,10 +3093,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3143,7 +3143,7 @@
         <v>47</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3154,7 +3154,7 @@
         <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3209,7 +3209,7 @@
         <v>60</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3272,10 +3272,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3291,106 +3291,106 @@
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>368</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>369</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>372</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>375</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>378</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="B23" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="C23" s="15" t="s">
         <v>381</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="C24" s="15" t="s">
         <v>384</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" s="18"/>
       <c r="B25" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>386</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="18"/>
       <c r="B26" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>388</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A27" s="18"/>
       <c r="B27" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>390</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="B28" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="C28" s="15" t="s">
         <v>393</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -3783,7 +3783,7 @@
         <v>115</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="150" x14ac:dyDescent="0.2">
@@ -3804,10 +3804,10 @@
     </row>
     <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>333</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
@@ -4032,7 +4032,7 @@
         <v>86</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
@@ -4264,7 +4264,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4277,10 +4277,10 @@
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4297,7 +4297,7 @@
         <v>105</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4305,7 +4305,7 @@
         <v>97</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4313,7 +4313,7 @@
         <v>116</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -4453,10 +4453,10 @@
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>335</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4464,7 +4464,7 @@
         <v>85</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -4496,7 +4496,7 @@
         <v>91</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -4504,7 +4504,7 @@
         <v>94</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -4512,7 +4512,7 @@
         <v>95</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -4525,42 +4525,42 @@
     </row>
     <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>337</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>339</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>341</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>343</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>345</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="240" x14ac:dyDescent="0.2">
@@ -4568,7 +4568,7 @@
         <v>116</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4623,7 +4623,7 @@
         <v>82</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4636,34 +4636,34 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>353</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>355</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4676,10 +4676,10 @@
     </row>
     <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>357</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="180" x14ac:dyDescent="0.2">
@@ -4687,7 +4687,7 @@
         <v>113</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -4695,7 +4695,7 @@
         <v>125</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>313</v>
+        <v>432</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4703,15 +4703,15 @@
         <v>115</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>359</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -4943,10 +4943,10 @@
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F836837-A3B0-4CA1-B913-4B26A9765DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156D8529-8097-454C-9BD4-290DE9135456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" activeTab="5" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" activeTab="9" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="435">
   <si>
     <t>Gene</t>
   </si>
@@ -1958,6 +1958,12 @@
     <t>STAT5B variants are reported in a number of T lymphoid malignancies (WHO 5th Edition).
 T-large granular lymphocytic leukaemia
 STAT3 and STAT5B mutations are the most commonly recognized gain of function genetic lesions in T LGL (WHO 5th edition).</t>
+  </si>
+  <si>
+    <t>NGS negative tumour content unknown</t>
+  </si>
+  <si>
+    <t>Please review the tumour content of the sample for interpretation of this result. Low tumour content reduces the sensitivity of NGS and it may result in false negative findings. This assay has been validated to detect as little as 1% mutant DNA in a background of wild type DNA. Copy number analysis has not been performed as it has only been validated for samples with ≥40% neoplastic content.</t>
   </si>
 </sst>
 </file>
@@ -2856,7 +2862,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71C181D1-9A1A-4B63-974F-1376CEB759F1}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.21875" customWidth="1"/>
@@ -2897,81 +2903,89 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>433</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>418</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>419</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>418</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>421</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>420</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>422</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>422</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>424</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>425</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>426</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>426</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>428</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>429</v>
       </c>
     </row>

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156D8529-8097-454C-9BD4-290DE9135456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE746BF0-AF37-4903-AF8D-8404C444BBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" activeTab="9" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" firstSheet="2" activeTab="11" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
     <author>tc={61FD660D-2DBF-40EC-B926-88247D8CDA05}</author>
   </authors>
   <commentList>
-    <comment ref="C28" authorId="0" shapeId="0" xr:uid="{61FD660D-2DBF-40EC-B926-88247D8CDA05}">
+    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{61FD660D-2DBF-40EC-B926-88247D8CDA05}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="431">
   <si>
     <t>Gene</t>
   </si>
@@ -220,33 +220,13 @@
 Absence of JAK2 V617F and JAK2 exon 12, MPL exon 10 and CALR exon 9 pathogenic variants does not exclude a myeloproliferative neoplasm. JAK2 (V617F/exon12), MPL exon 10 or CALR exon 9 pathogenic variants have been reported to be present in &gt;97% of cases of polycythaemia vera and approximately 90% of cases of primary myelofibrosis and essential thrombocythaemia.</t>
   </si>
   <si>
-    <t>del(17p) (TP53 deletion)
-note: del(17p) is mostly accompanied by TP53 mutations, and sole del(17p) is infrequent, while sole TP53 mutations are more commonly found (ERIC 2024)
-If TP53 mutation is also detected</t>
-  </si>
-  <si>
     <t>Trisomy 12</t>
   </si>
   <si>
-    <t>del(11q) (ATM del)</t>
-  </si>
-  <si>
-    <t>DLEU2/7del (chr13q)</t>
-  </si>
-  <si>
-    <t>RB1 copy number loss (focal)</t>
-  </si>
-  <si>
     <t>Genomic complexity defined as &gt;= 5 CNAs</t>
   </si>
   <si>
     <t>Trisomy 19</t>
-  </si>
-  <si>
-    <t>6q del</t>
-  </si>
-  <si>
-    <t>14 (14q) del</t>
   </si>
   <si>
     <t>Del(17p) occurs in 4 to 8% of early stage CLL, 5 to 8% at the start of first-line therapy, and 40–50% in relapsed/refractory CLL.
@@ -264,12 +244,6 @@
   </si>
   <si>
     <t>Approximately 10% of CLL cases with trisomy 12 also have trisomy 19 and are associated with mutated IGHV genes in CLL  (PMID: 17593029)</t>
-  </si>
-  <si>
-    <t>6q deletions are recurrent aberrations in CLL, detected in 3 to 7% of cases (PMID: 10482982)</t>
-  </si>
-  <si>
-    <t>14q deletions are rare but recurrent aberrations in CLL, detected in &lt;5% cases (PMID: 20649559)</t>
   </si>
   <si>
     <t>No copy number aberrations detected in a sample with &gt;=40% NCC</t>
@@ -1964,6 +1938,20 @@
   </si>
   <si>
     <t>Please review the tumour content of the sample for interpretation of this result. Low tumour content reduces the sensitivity of NGS and it may result in false negative findings. This assay has been validated to detect as little as 1% mutant DNA in a background of wild type DNA. Copy number analysis has not been performed as it has only been validated for samples with ≥40% neoplastic content.</t>
+  </si>
+  <si>
+    <t>Del(13q) DLEU2/miR15</t>
+  </si>
+  <si>
+    <t>Del(17p) (TP53 deletion)
+note: del(17p) is mostly accompanied by TP53 mutations, and sole del(17p) is infrequent, while sole TP53 mutations are more commonly found (ERIC 2024)
+If TP53 mutation is also detected</t>
+  </si>
+  <si>
+    <t>Del(11q) (ATM)</t>
+  </si>
+  <si>
+    <t>RB1 copy number loss (focal, to be used in absence of miR 15 loss)</t>
   </si>
 </sst>
 </file>
@@ -2438,7 +2426,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C28" dT="2025-10-24T14:51:55.67" personId="{E177F675-2BF7-4D34-B125-6F3DDBFD449B}" id="{61FD660D-2DBF-40EC-B926-88247D8CDA05}">
+  <threadedComment ref="C26" dT="2025-10-24T14:51:55.67" personId="{E177F675-2BF7-4D34-B125-6F3DDBFD449B}" id="{61FD660D-2DBF-40EC-B926-88247D8CDA05}">
     <text>Incorrect in WHO - PTEN is on 10q</text>
   </threadedComment>
 </ThreadedComments>
@@ -2467,7 +2455,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F2" s="6"/>
     </row>
@@ -2476,7 +2464,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2484,7 +2472,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="150" x14ac:dyDescent="0.2">
@@ -2492,15 +2480,15 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.2">
@@ -2508,15 +2496,15 @@
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.2">
@@ -2524,7 +2512,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
@@ -2532,7 +2520,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2540,7 +2528,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="255" x14ac:dyDescent="0.2">
@@ -2548,7 +2536,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="167.25" x14ac:dyDescent="0.2">
@@ -2556,7 +2544,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2564,295 +2552,295 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="333" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="285" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="345" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="195" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2867,6 +2855,7 @@
   <cols>
     <col min="1" max="1" width="34.21875" customWidth="1"/>
     <col min="2" max="2" width="84.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="41" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -2879,10 +2868,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2903,10 +2892,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -2914,7 +2903,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2943,50 +2932,50 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -3021,74 +3010,74 @@
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -3098,33 +3087,34 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9F24A3-EA82-4A17-B915-0BA86DD79F59}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
     <col min="2" max="2" width="46" style="1" customWidth="1"/>
     <col min="3" max="3" width="72.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="225" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>429</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -3132,10 +3122,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3143,10 +3133,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>427</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>55</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3154,109 +3144,109 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>430</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="225" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>48</v>
+        <v>428</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3264,152 +3254,130 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>64</v>
+        <v>408</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A17" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A18" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="B19" s="17" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="B20" s="17" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
+      <c r="C20" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="B20" s="17" t="s">
+    </row>
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A21" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="B21" s="17" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="16" t="s">
+      <c r="C21" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="B21" s="17" t="s">
+    </row>
+    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A22" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="B22" s="17" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="16" t="s">
+      <c r="C22" s="15" t="s">
         <v>376</v>
       </c>
-      <c r="B22" s="17" t="s">
+    </row>
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A23" s="18"/>
+      <c r="B23" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C23" s="15" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A23" s="16" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="18"/>
+      <c r="B24" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="C24" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="C23" s="15" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A24" s="18" t="s">
-        <v>382</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>383</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="18"/>
       <c r="B25" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+      <c r="A26" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>385</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="18"/>
-      <c r="B26" s="17" t="s">
-        <v>387</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="17" t="s">
-        <v>389</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="60" x14ac:dyDescent="0.2">
-      <c r="A28" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>392</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>393</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A22:A25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -3439,7 +3407,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D2" s="6"/>
     </row>
@@ -3448,7 +3416,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3456,7 +3424,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3464,15 +3432,15 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -3480,7 +3448,7 @@
         <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -3488,7 +3456,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -3496,7 +3464,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3504,7 +3472,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3512,7 +3480,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
@@ -3520,7 +3488,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3528,7 +3496,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3536,308 +3504,308 @@
         <v>40</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="285" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="369" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3869,7 +3837,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="285" x14ac:dyDescent="0.25">
@@ -3877,7 +3845,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D3" s="6"/>
     </row>
@@ -3886,7 +3854,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3894,15 +3862,15 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3910,15 +3878,15 @@
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="135" x14ac:dyDescent="0.2">
@@ -3926,7 +3894,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -3934,7 +3902,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -3942,7 +3910,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
@@ -3950,7 +3918,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="150" x14ac:dyDescent="0.2">
@@ -3958,7 +3926,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3966,288 +3934,288 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="135" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="315" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B48" s="4"/>
     </row>
     <row r="49" spans="1:2" ht="195" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -4278,7 +4246,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4286,48 +4254,48 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -4358,7 +4326,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4366,7 +4334,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4374,7 +4342,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4382,7 +4350,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4390,7 +4358,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4398,15 +4366,15 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4414,7 +4382,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4422,7 +4390,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4430,7 +4398,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4438,151 +4406,151 @@
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="240" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -4605,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4613,7 +4581,7 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4621,111 +4589,111 @@
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="180" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -4754,7 +4722,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -4762,7 +4730,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -4771,7 +4739,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
@@ -4779,39 +4747,39 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -4843,85 +4811,85 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="375" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="345" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="180" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="345" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="210" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -4952,75 +4920,75 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE746BF0-AF37-4903-AF8D-8404C444BBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07260E46-91CB-42B8-8D37-6F027DAD1A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" firstSheet="2" activeTab="11" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
@@ -3090,7 +3090,7 @@
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="46" style="1" customWidth="1"/>
     <col min="3" max="3" width="72.6640625" style="1" customWidth="1"/>
   </cols>

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07260E46-91CB-42B8-8D37-6F027DAD1A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895EC41D-174A-4D4E-8D31-CE5555610D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" firstSheet="2" activeTab="11" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="431">
   <si>
     <t>Gene</t>
   </si>
@@ -2073,7 +2073,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3338,7 +3338,9 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
+      <c r="A23" s="18" t="s">
+        <v>374</v>
+      </c>
       <c r="B23" s="17" t="s">
         <v>377</v>
       </c>
@@ -3347,7 +3349,9 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
+      <c r="A24" s="18" t="s">
+        <v>374</v>
+      </c>
       <c r="B24" s="17" t="s">
         <v>379</v>
       </c>
@@ -3356,7 +3360,9 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A25" s="18"/>
+      <c r="A25" s="18" t="s">
+        <v>374</v>
+      </c>
       <c r="B25" s="17" t="s">
         <v>381</v>
       </c>
@@ -3376,9 +3382,6 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A22:A25"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895EC41D-174A-4D4E-8D31-CE5555610D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C0DF6F-E316-4DFA-BA20-4022C78205F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" firstSheet="2" activeTab="11" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" firstSheet="1" activeTab="2" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -1916,42 +1916,40 @@
     <t>The neoplastic cell content of this sample is not available. The presence of low-level variants cannot be excluded. This assay has been validated to detect small variants present at ≥1% mutant DNA in a background of wild-type DNA. Copy number analysis has not been performed as it has only been validated for samples with ≥40% neoplastic content.</t>
   </si>
   <si>
+    <t>STAT5B variants are reported in a number of T lymphoid malignancies (WHO 5th Edition).
+T-large granular lymphocytic leukaemia
+STAT3 and STAT5B mutations are the most commonly recognized gain of function genetic lesions in T LGL (WHO 5th edition).</t>
+  </si>
+  <si>
+    <t>NGS negative tumour content unknown</t>
+  </si>
+  <si>
+    <t>Please review the tumour content of the sample for interpretation of this result. Low tumour content reduces the sensitivity of NGS and it may result in false negative findings. This assay has been validated to detect as little as 1% mutant DNA in a background of wild type DNA. Copy number analysis has not been performed as it has only been validated for samples with ≥40% neoplastic content.</t>
+  </si>
+  <si>
+    <t>Del(13q) DLEU2/miR15</t>
+  </si>
+  <si>
+    <t>Del(17p) (TP53 deletion)
+note: del(17p) is mostly accompanied by TP53 mutations, and sole del(17p) is infrequent, while sole TP53 mutations are more commonly found (ERIC 2024)
+If TP53 mutation is also detected</t>
+  </si>
+  <si>
+    <t>Del(11q) (ATM)</t>
+  </si>
+  <si>
+    <t>RB1 copy number loss (focal, to be used in absence of miR 15 loss)</t>
+  </si>
+  <si>
     <t xml:space="preserve">JAK2 V617F chr9:5073770 
 JAK2 Exon 12 chr9:5069925-5070052
 V617F
 The presence of a pathogenic JAK2 V617F variant is supportive of a myeloproliferative neoplasm in the correct clinical context. JAK2 V617F is reported in over 97% of polycythaemia vera cases and in approximately 50% of primary myelofibrosis and essential thrombocythaemia cases (WHO 5th Edition).
 Exon 12
 The presence of a pathogenic JAK2 exon 12 variant is most commonly associated with a diagnosis of PV (WHO 5th Edition).
-Low level:
-Low-level JAK2 mutations may represent age-related CHIP, though they are associated with an increased risk of thrombotic events and potential progression. A definitive diagnosis of MPN requires correlation with blood counts, bone marrow morphology, and clinical features, as per WHO/ICC criteria.
 CMML
 JAK2 mutations have been reported in MPN and CMML, correlation of clinical features with variant allele frequency and the presence of additional variants may aid in diagnosis (WHO 5th Edition). 
 </t>
-  </si>
-  <si>
-    <t>STAT5B variants are reported in a number of T lymphoid malignancies (WHO 5th Edition).
-T-large granular lymphocytic leukaemia
-STAT3 and STAT5B mutations are the most commonly recognized gain of function genetic lesions in T LGL (WHO 5th edition).</t>
-  </si>
-  <si>
-    <t>NGS negative tumour content unknown</t>
-  </si>
-  <si>
-    <t>Please review the tumour content of the sample for interpretation of this result. Low tumour content reduces the sensitivity of NGS and it may result in false negative findings. This assay has been validated to detect as little as 1% mutant DNA in a background of wild type DNA. Copy number analysis has not been performed as it has only been validated for samples with ≥40% neoplastic content.</t>
-  </si>
-  <si>
-    <t>Del(13q) DLEU2/miR15</t>
-  </si>
-  <si>
-    <t>Del(17p) (TP53 deletion)
-note: del(17p) is mostly accompanied by TP53 mutations, and sole del(17p) is infrequent, while sole TP53 mutations are more commonly found (ERIC 2024)
-If TP53 mutation is also detected</t>
-  </si>
-  <si>
-    <t>Del(11q) (ATM)</t>
-  </si>
-  <si>
-    <t>RB1 copy number loss (focal, to be used in absence of miR 15 loss)</t>
   </si>
 </sst>
 </file>
@@ -2892,10 +2890,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>424</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3111,7 +3109,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>49</v>
@@ -3133,7 +3131,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>357</v>
@@ -3144,7 +3142,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>358</v>
@@ -3155,7 +3153,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -4012,12 +4010,12 @@
         <v>178</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="315" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" ht="240" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
@@ -4680,7 +4678,7 @@
         <v>117</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C0DF6F-E316-4DFA-BA20-4022C78205F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226AA1EC-955D-4AC4-94E7-03D94CDAA9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" firstSheet="1" activeTab="2" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" firstSheet="2" activeTab="11" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="431">
   <si>
     <t>Gene</t>
   </si>
@@ -3085,7 +3085,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9F24A3-EA82-4A17-B915-0BA86DD79F59}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -3377,6 +3377,38 @@
       </c>
       <c r="C26" s="15" t="s">
         <v>385</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>414</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>416</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>418</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>420</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226AA1EC-955D-4AC4-94E7-03D94CDAA9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE79162C-379A-4B44-BB2F-AD4B75FD880F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" firstSheet="2" activeTab="11" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="431">
   <si>
     <t>Gene</t>
   </si>
@@ -3085,7 +3085,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9F24A3-EA82-4A17-B915-0BA86DD79F59}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -3377,38 +3377,6 @@
       </c>
       <c r="C26" s="15" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>414</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="60" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>416</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>418</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>420</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE79162C-379A-4B44-BB2F-AD4B75FD880F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92847E1-8598-47AB-A896-8008B98AAA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31200" yWindow="-855" windowWidth="24615" windowHeight="14175" firstSheet="2" activeTab="11" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -1695,9 +1695,6 @@
     <t>VAV1</t>
   </si>
   <si>
-    <t>VAV1 variants have been reported in angioimmunoblastic T-cell lymphoma (AITL) and nodal PTCL with T-follicular helper (Tfh) phenotype (PTCL-Tfh) (DOI: 10.1016/j.celrep.2016.05.008).</t>
-  </si>
-  <si>
     <t>CSF1R</t>
   </si>
   <si>
@@ -1950,6 +1947,9 @@
 CMML
 JAK2 mutations have been reported in MPN and CMML, correlation of clinical features with variant allele frequency and the presence of additional variants may aid in diagnosis (WHO 5th Edition). 
 </t>
+  </si>
+  <si>
+    <t>VAV1 variants have been reported in angioimmunoblastic T-cell lymphoma (AITL) and nodal PTCL with T-follicular helper (Tfh) phenotype (PTCL-Tfh) (DOI: 10.1182/blood.2020006513).</t>
   </si>
 </sst>
 </file>
@@ -2606,7 +2606,7 @@
         <v>73</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -2830,7 +2830,7 @@
         <v>111</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2866,10 +2866,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2890,10 +2890,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>423</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -2901,7 +2901,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2930,50 +2930,50 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>409</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>413</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>415</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>417</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>419</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -3008,74 +3008,74 @@
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>399</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>401</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -3109,7 +3109,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>49</v>
@@ -3131,10 +3131,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3142,10 +3142,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="225" x14ac:dyDescent="0.2">
@@ -3153,7 +3153,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -3189,7 +3189,7 @@
         <v>52</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3252,10 +3252,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3271,112 +3271,112 @@
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="B17" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>360</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>363</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>366</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>368</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>369</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>372</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A22" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>375</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B23" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>377</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B24" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>379</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B25" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>381</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>384</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -3766,7 +3766,7 @@
         <v>107</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="150" x14ac:dyDescent="0.2">
@@ -4015,7 +4015,7 @@
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
@@ -4678,7 +4678,7 @@
         <v>117</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4694,7 +4694,7 @@
         <v>351</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>352</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -4926,10 +4926,10 @@
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92847E1-8598-47AB-A896-8008B98AAA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08D1DE8-D171-4214-91B7-ECA5AD41D525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="29220" yWindow="165" windowWidth="27075" windowHeight="13425" activeTab="10" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -1809,9 +1809,6 @@
     <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ETV6, FBXW7, HRAS, IKZF1, KRAS, NOTCH1, NRAS, NUDT15, PAX5, PTEN, TP53, TPMT  genes.</t>
   </si>
   <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ATM, ARID1A, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, EP300, EZH2, FOXO1, HRAS, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PLCG2, TP53, ID3, PDCD1LG2, STAT6, TCF3, TNFAIP3, TNFRSF14 genes.</t>
-  </si>
-  <si>
     <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ATM, CARD11, DNMT3A, FYN, IDH2, IRF4, JAK1, JAK3, PLCG1, POT1, RHOA, SETD2, STAT3, STAT5B, TET2, TP53, VAV1 genes.</t>
   </si>
   <si>
@@ -1950,6 +1947,9 @@
   </si>
   <si>
     <t>VAV1 variants have been reported in angioimmunoblastic T-cell lymphoma (AITL) and nodal PTCL with T-follicular helper (Tfh) phenotype (PTCL-Tfh) (DOI: 10.1182/blood.2020006513).</t>
+  </si>
+  <si>
+    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ARID1A, ATM, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, EP300, EZH2, FOXO1, HRAS, ID3, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PDCD1LG2, PLCG2, STAT6, TCF3, TNFAIP3, TNFRSF14, TP53 genes.</t>
   </si>
 </sst>
 </file>
@@ -2830,7 +2830,7 @@
         <v>111</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2890,10 +2890,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>423</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -2901,7 +2901,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2930,50 +2930,50 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>408</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>412</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>414</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>416</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>418</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>419</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -3008,55 +3008,55 @@
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>388</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>387</v>
@@ -3064,18 +3064,18 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>400</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -3109,7 +3109,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>49</v>
@@ -3131,7 +3131,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>356</v>
@@ -3142,7 +3142,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>357</v>
@@ -3153,7 +3153,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -3189,7 +3189,7 @@
         <v>52</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3252,10 +3252,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4015,7 +4015,7 @@
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
@@ -4678,7 +4678,7 @@
         <v>117</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4694,7 +4694,7 @@
         <v>351</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08D1DE8-D171-4214-91B7-ECA5AD41D525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4184AA8-2FF1-402B-B149-3297B646768D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29220" yWindow="165" windowWidth="27075" windowHeight="13425" activeTab="10" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="2295" yWindow="750" windowWidth="24645" windowHeight="14010" activeTab="9" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="432">
   <si>
     <t>Gene</t>
   </si>
@@ -785,9 +785,6 @@
 KRAS mutations have been reported in MDS/MPN cases (WHO 5th Edition).
 JMML
 JMML is associated with mutations in RAS genes (KRAS 15 to 20%) or in regulators of the RAS pathway in more than 90% of cases (WHO 5th Edition). Please note that this assay cannot exclude the germline origin for the KRAS c.xxx p.(xxx) variant. Referral to clinical genetics service for family history and further assessment is recommended.</t>
-  </si>
-  <si>
-    <t>Not agreed</t>
   </si>
   <si>
     <t>KIT mutation, particularly KITD816V, is most commonly reported in systemic mastocytosis (WHO 5th Edition).
@@ -1129,34 +1126,11 @@
 Childhood ALL cases with ETV6 germline mutations constitute a rare novel ALL predisposition syndrome (DOI: DOI: 10.1182/blood.2020006164). Please note that this assay cannot exclude the germline origin for the ETV6 c.xxx p.(xxx) variant. Referral to clinical genetics service for family history and further assessment is recommended if clinically indicated.</t>
   </si>
   <si>
-    <t>T-ALL
-Loss of function mutations in FBXW7, a negative regulator of NOTCH1 has been reported in 30% of cases. NOTCH1 and/or FBXW7 mutations have been associated with better clinical outcomes, while loss of heterozygosity at 6q, PTEN mutations, and KMT2D mutations have been associated with worse outcomes (WHO 5th edition) (Blood. 2021 Apr 29,137(17):2347_2359.).
-This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
-adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
-The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009 )
-adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
-The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
-Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
-Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).</t>
-  </si>
-  <si>
     <t xml:space="preserve">IKZF1 is recurrently altered in childhood B-ALL (DOI: 10.1056/NEJMoa0808253).
 IKZF1 is recurrently altered in cases of adult ALL (DOI: 10.1016/j.blre.2020.100677).
 Deletion or splicing abnormalities of IKZF1 are reported in 80% of B-ALL cases with BCR::ABL1 fusion (WHO 5th Edition).
 Please note that this assay cannot exclude the germline origin for the IKZF1 c.xxx p.(xxx) variant. Referral to clinical genetics service for family history and further assessment is recommended if clinically indicated.
 </t>
-  </si>
-  <si>
-    <t>T-lymphoblastic leukaemia / lymphoma, NOS
-Signalling pathway deregulation in T ALL occurs in the NOTCH1. Over 75% of cases show NOTCH1 pathway activation, which can be caused by activating mutations involving the extracellular heterodimerization domain and / or the C terminal PEST domain of NOTCH1 (50% of cases) and/or by loss of function mutations in FBXW7, a negative regulator of NOTCH1 (30% of cases). NOTCH1 and/or FBXW7 mutations have been associated with better clinical outcomes, while loss of heterozygosity at 6q, PTEN mutations, and KMT2D mutations have been associated with worse outcomes (WHO 5th edition).
-NOTCH1 and/or FBXW7 mutations have been associated with better clinical outcomes, while loss of heterozygosity at 6q, PTEN mutations, and KMT2D mutations have been associated with worse outcomes (Blood. 2021 Apr 29,137(17):2347_2359.).
-This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
-adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
-The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009)
-adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
-The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
-Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
-Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).</t>
   </si>
   <si>
     <t xml:space="preserve">NRAS is altered in 14% of acute lymphoblastic leukaemia patients 
@@ -1426,9 +1400,6 @@
 DNMT3A is recurrently mutated in various haematological malignancies, however, some DNMT3A alterations can be age related or present in other neoplasms. Please correlate with other clinical and pathological findings.</t>
   </si>
   <si>
-    <t>KMT2A alterations have been reported rarely in triple negative MPN cases (DOI: 10.1182/blood-2019-128764). As KMT2A fusions are clinically significant we had better not comment on KMT2A SNVs.</t>
-  </si>
-  <si>
     <t>ARID1A variants are especially prevalent in follicular lymphoma but also occur in diffuse large B-cell lymphoma and other B-cell lymphomas (DOI: 10.1016/j.ccell.2024.02.010).
 ARID1A variants are recurrent in follicular lymphoma and are  included in the M7 FLIPI risk score (DOI: 10.1016/S1470-2045(15)00169-2).</t>
   </si>
@@ -1806,9 +1777,6 @@
 </t>
   </si>
   <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ETV6, FBXW7, HRAS, IKZF1, KRAS, NOTCH1, NRAS, NUDT15, PAX5, PTEN, TP53, TPMT  genes.</t>
-  </si>
-  <si>
     <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ATM, CARD11, DNMT3A, FYN, IDH2, IRF4, JAK1, JAK3, PLCG1, POT1, RHOA, SETD2, STAT3, STAT5B, TET2, TP53, VAV1 genes.</t>
   </si>
   <si>
@@ -1951,12 +1919,51 @@
   <si>
     <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ARID1A, ATM, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, EP300, EZH2, FOXO1, HRAS, ID3, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PDCD1LG2, PLCG2, STAT6, TCF3, TNFAIP3, TNFRSF14, TP53 genes.</t>
   </si>
+  <si>
+    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ETV6, FBXW7, HRAS, IKZF1, KRAS, NOTCH1, NRAS, NUDT15, PAX5, PTEN, TP53, TPMT  genes.
+For children:
+Please note that copy number variation (CNV) and structural variation (SV) analyses are not performed in cases of lymphoblastic leukaemia (ALL). Please refer to SNP array, RNA NGS and cytogenetics report for findings where available.
+For adults:
+Please note that copy number variation (CNV) and structural variation (SV) analyses are not performed in cases of lymphoblastic leukaemia (ALL). Please refer to RNA NGS and cytogenetics report for findings where available.</t>
+  </si>
+  <si>
+    <t>KMT2A alterations have been reported rarely in MPN cases (DOI: 10.1182/blood-2019-128764).</t>
+  </si>
+  <si>
+    <t>T-ALL
+Loss of function mutations in FBXW7, a negative regulator of NOTCH1 have been reported in 30% of cases. NOTCH1 and/or FBXW7 mutations have been associated with better clinical outcomes, while loss of heterozygosity at 6q, PTEN mutations, and KMT2D mutations have been associated with worse outcomes (WHO 5th edition) (Blood. 2021 Apr 29,137(17):2347_2359.).
+This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
+adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
+The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009 )
+adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
+The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
+Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
+Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).</t>
+  </si>
+  <si>
+    <t>T-lymphoblastic leukaemia / lymphoma, NOS
+NOTCH1 variants may contribute to signalling pathway dysregulation in T-ALL. Over 75% of cases show NOTCH1 pathway activation, which can be caused by activating mutations involving the extracellular heterodimerization domain and / or the C terminal PEST domain of NOTCH1 (50% of cases) and/or by loss of function mutations in FBXW7, a negative regulator of NOTCH1 (30% of cases). NOTCH1 and/or FBXW7 mutations have been associated with better clinical outcomes, while loss of heterozygosity at 6q, PTEN mutations, and KMT2D mutations have been associated with worse outcomes (WHO 5th edition).
+NOTCH1 and/or FBXW7 mutations have been associated with better clinical outcomes, while loss of heterozygosity at 6q, PTEN mutations, and KMT2D mutations have been associated with worse outcomes (Blood. 2021 Apr 29,137(17):2347_2359.).
+This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
+adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
+The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009)
+adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
+The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
+Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
+Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).</t>
+  </si>
+  <si>
+    <t>Unfortunately the NGS analysis failed. Please send a repeat sample, if possible.</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1999,6 +2006,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2020,7 +2033,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2072,6 +2085,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2499,10 +2515,10 @@
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.2">
@@ -2518,7 +2534,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2542,7 +2558,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2574,7 +2590,7 @@
         <v>67</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -2606,7 +2622,7 @@
         <v>73</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -2819,10 +2835,10 @@
     </row>
     <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2830,7 +2846,7 @@
         <v>111</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2848,7 +2864,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71C181D1-9A1A-4B63-974F-1376CEB759F1}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.21875" customWidth="1"/>
@@ -2866,10 +2882,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2890,10 +2906,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -2901,7 +2917,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2930,50 +2946,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>419</v>
+        <v>414</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>431</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -3008,74 +3032,74 @@
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>387</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -3095,10 +3119,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3109,7 +3133,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>49</v>
@@ -3131,10 +3155,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3142,10 +3166,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="225" x14ac:dyDescent="0.2">
@@ -3153,7 +3177,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -3189,7 +3213,7 @@
         <v>52</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3252,10 +3276,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3271,112 +3295,112 @@
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A22" s="18" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>373</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>376</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -3408,7 +3432,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D2" s="6"/>
     </row>
@@ -3417,7 +3441,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3425,7 +3449,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3433,7 +3457,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -3441,7 +3465,7 @@
         <v>113</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -3449,7 +3473,7 @@
         <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -3457,7 +3481,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -3465,7 +3489,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3473,7 +3497,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3481,7 +3505,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
@@ -3489,7 +3513,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3497,7 +3521,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3505,7 +3529,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="285" x14ac:dyDescent="0.2">
@@ -3513,7 +3537,7 @@
         <v>65</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -3521,7 +3545,7 @@
         <v>66</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3529,7 +3553,7 @@
         <v>67</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -3537,7 +3561,7 @@
         <v>69</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -3553,7 +3577,7 @@
         <v>71</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3561,7 +3585,7 @@
         <v>73</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3569,7 +3593,7 @@
         <v>74</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -3582,7 +3606,7 @@
         <v>78</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -3590,7 +3614,7 @@
         <v>79</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -3598,7 +3622,7 @@
         <v>97</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -3606,7 +3630,7 @@
         <v>80</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -3614,7 +3638,7 @@
         <v>82</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -3622,7 +3646,7 @@
         <v>114</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -3630,7 +3654,7 @@
         <v>84</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -3638,7 +3662,7 @@
         <v>88</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3646,7 +3670,7 @@
         <v>89</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -3654,7 +3678,7 @@
         <v>91</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3662,7 +3686,7 @@
         <v>93</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -3670,7 +3694,7 @@
         <v>94</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="369" customHeight="1" x14ac:dyDescent="0.2">
@@ -3678,7 +3702,7 @@
         <v>95</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -3686,7 +3710,7 @@
         <v>96</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -3694,7 +3718,7 @@
         <v>99</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -3702,7 +3726,7 @@
         <v>100</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -3710,7 +3734,7 @@
         <v>115</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -3718,7 +3742,7 @@
         <v>101</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -3726,7 +3750,7 @@
         <v>116</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -3734,7 +3758,7 @@
         <v>103</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -3742,7 +3766,7 @@
         <v>104</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3750,7 +3774,7 @@
         <v>105</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3758,7 +3782,7 @@
         <v>106</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -3766,7 +3790,7 @@
         <v>107</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="150" x14ac:dyDescent="0.2">
@@ -3774,7 +3798,7 @@
         <v>108</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -3782,15 +3806,15 @@
         <v>110</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
@@ -3798,7 +3822,7 @@
         <v>111</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -3806,7 +3830,7 @@
         <v>112</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3927,7 +3951,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -4015,7 +4039,7 @@
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
@@ -4098,23 +4122,21 @@
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>282</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="C35" s="4"/>
     </row>
     <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4122,7 +4144,7 @@
         <v>99</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4130,7 +4152,7 @@
         <v>100</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4138,7 +4160,7 @@
         <v>101</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4146,7 +4168,7 @@
         <v>102</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -4154,7 +4176,7 @@
         <v>103</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4162,7 +4184,7 @@
         <v>104</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4170,7 +4192,7 @@
         <v>105</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4178,7 +4200,7 @@
         <v>117</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4186,7 +4208,7 @@
         <v>107</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4194,7 +4216,7 @@
         <v>108</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4202,7 +4224,7 @@
         <v>110</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -4216,7 +4238,7 @@
         <v>112</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -4247,7 +4269,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4255,15 +4277,15 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4271,7 +4293,7 @@
         <v>76</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F5" s="6"/>
     </row>
@@ -4280,7 +4302,7 @@
         <v>97</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4288,7 +4310,7 @@
         <v>89</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4296,7 +4318,7 @@
         <v>108</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -4327,7 +4349,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4335,7 +4357,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4343,7 +4365,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4351,7 +4373,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4359,7 +4381,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4367,7 +4389,7 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4375,7 +4397,7 @@
         <v>119</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4383,7 +4405,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4391,7 +4413,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4399,7 +4421,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4407,7 +4429,7 @@
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4415,7 +4437,7 @@
         <v>66</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4423,7 +4445,7 @@
         <v>68</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -4431,15 +4453,15 @@
         <v>72</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4447,7 +4469,7 @@
         <v>77</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -4455,7 +4477,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4463,7 +4485,7 @@
         <v>81</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4471,7 +4493,7 @@
         <v>120</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4479,7 +4501,7 @@
         <v>83</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -4487,7 +4509,7 @@
         <v>86</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -4495,7 +4517,7 @@
         <v>87</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -4503,47 +4525,47 @@
         <v>89</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="240" x14ac:dyDescent="0.2">
@@ -4551,7 +4573,7 @@
         <v>108</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -4574,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4582,7 +4604,7 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4590,15 +4612,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4606,7 +4628,7 @@
         <v>74</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4614,39 +4636,39 @@
         <v>76</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4654,15 +4676,15 @@
         <v>98</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="180" x14ac:dyDescent="0.2">
@@ -4670,7 +4692,7 @@
         <v>105</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -4678,7 +4700,7 @@
         <v>117</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4686,15 +4708,15 @@
         <v>107</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -4723,7 +4745,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -4731,7 +4753,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -4740,7 +4762,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
@@ -4748,7 +4770,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -4756,7 +4778,7 @@
         <v>86</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -4764,7 +4786,7 @@
         <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4772,7 +4794,7 @@
         <v>101</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
@@ -4780,7 +4802,7 @@
         <v>108</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -4812,7 +4834,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4820,7 +4842,7 @@
         <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="270" x14ac:dyDescent="0.2">
@@ -4828,7 +4850,7 @@
         <v>121</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>262</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -4842,7 +4864,7 @@
         <v>75</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="375" x14ac:dyDescent="0.2">
@@ -4850,7 +4872,7 @@
         <v>86</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>264</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="345" x14ac:dyDescent="0.2">
@@ -4858,15 +4880,15 @@
         <v>89</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="180" x14ac:dyDescent="0.2">
@@ -4874,7 +4896,7 @@
         <v>90</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="345" x14ac:dyDescent="0.2">
@@ -4882,7 +4904,7 @@
         <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="210" x14ac:dyDescent="0.2">
@@ -4921,15 +4943,15 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4937,7 +4959,7 @@
         <v>81</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4945,7 +4967,7 @@
         <v>89</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4953,7 +4975,7 @@
         <v>97</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4961,35 +4983,35 @@
         <v>72</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4184AA8-2FF1-402B-B149-3297B646768D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E0D04F-F0C4-40B8-82BA-73888B47B994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="750" windowWidth="24645" windowHeight="14010" activeTab="9" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -685,12 +685,6 @@
 While ASXL1 alterations are common in myeloid malignancies, they are also observed in a subset of healthy, older individuals with clonal haematopoiesis.
 SM                                                                                                                                                                                                                                                            
 Detection of non KIT mutations usually indicate (myeloid) systemic mastocytosis with an associated haematological neoplasm (SM AHN), and some, including ASXL1, are associated with adverse prognostic significance (WHO 5th Edition). </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mutations in ETNK1 and/or SETBP1 are most frequently reported in MDS/MPN N (WHO 5th Edition).
-ETNK1 mutations have been reported in myeloid malignancies, including MDS/MPN N, CMML and SM with eosinophilia (DOI: 10.1038/s41467-020-19721-w).
-ETNK1 mutations have been reported rarely in CNL (WHO 5th Edition).
-</t>
   </si>
   <si>
     <t>ETV6 mutations are rare in myeloid malignancies but have been reported in cases of MPN (DOI: 10.1182/blood-2024-211479).
@@ -1920,13 +1914,6 @@
     <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ARID1A, ATM, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, EP300, EZH2, FOXO1, HRAS, ID3, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PDCD1LG2, PLCG2, STAT6, TCF3, TNFAIP3, TNFRSF14, TP53 genes.</t>
   </si>
   <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ETV6, FBXW7, HRAS, IKZF1, KRAS, NOTCH1, NRAS, NUDT15, PAX5, PTEN, TP53, TPMT  genes.
-For children:
-Please note that copy number variation (CNV) and structural variation (SV) analyses are not performed in cases of lymphoblastic leukaemia (ALL). Please refer to SNP array, RNA NGS and cytogenetics report for findings where available.
-For adults:
-Please note that copy number variation (CNV) and structural variation (SV) analyses are not performed in cases of lymphoblastic leukaemia (ALL). Please refer to RNA NGS and cytogenetics report for findings where available.</t>
-  </si>
-  <si>
     <t>KMT2A alterations have been reported rarely in MPN cases (DOI: 10.1182/blood-2019-128764).</t>
   </si>
   <si>
@@ -1957,6 +1944,22 @@
   </si>
   <si>
     <t>Failed</t>
+  </si>
+  <si>
+    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ETV6, FBXW7, HRAS, IKZF1, KRAS, NOTCH1, NRAS, PAX5, PTEN, TP53  genes.
+For children:
+Please note that copy number variation (CNV) and structural variation (SV) analyses are not performed in cases of lymphoblastic leukaemia (ALL). Please refer to SNP array, RNA NGS and cytogenetics report for findings where available.
+For adults:
+Please note that copy number variation (CNV) and structural variation (SV) analyses are not performed in cases of lymphoblastic leukaemia (ALL). Please refer to RNA NGS and cytogenetics report for findings where available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mutations in ETNK1 and/or SETBP1 are most frequently reported in MDS/MPN N (WHO 5th Edition).
+ETNK1 mutations have been reported in myeloid malignancies, including MDS/MPN N, CMML and SM with eosinophilia (DOI: 10.1038/s41467-020-19721-w).
+ETNK1 mutations have been reported rarely in CNL (WHO 5th Edition).
+For reporting purposes:
+Old - ETNK1 N244S (ENST00000671733.1)
+New - ETNK1 c.724A&gt;G p.Asn155Ser (ENST00000266517.9) (NM_018638.5)
+</t>
   </si>
 </sst>
 </file>
@@ -2515,10 +2518,10 @@
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.2">
@@ -2534,7 +2537,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2558,7 +2561,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2590,7 +2593,7 @@
         <v>67</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -2622,7 +2625,7 @@
         <v>73</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -2835,10 +2838,10 @@
     </row>
     <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>318</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2846,7 +2849,7 @@
         <v>111</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2882,10 +2885,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2906,10 +2909,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>416</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -2917,7 +2920,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2946,58 +2949,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>402</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>406</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>408</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>410</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>412</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -3032,74 +3035,74 @@
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>392</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>394</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -3119,10 +3122,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3133,7 +3136,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>49</v>
@@ -3155,10 +3158,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3166,10 +3169,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="225" x14ac:dyDescent="0.2">
@@ -3177,7 +3180,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -3213,7 +3216,7 @@
         <v>52</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3276,10 +3279,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3295,112 +3298,112 @@
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="B17" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>355</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>358</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>361</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>364</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>367</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A22" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>369</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>370</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B23" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>372</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B24" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>374</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B25" s="17" t="s">
+        <v>375</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>376</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>379</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +3435,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D2" s="6"/>
     </row>
@@ -3441,7 +3444,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3449,7 +3452,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3457,7 +3460,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -3465,7 +3468,7 @@
         <v>113</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -3473,7 +3476,7 @@
         <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -3481,7 +3484,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -3489,7 +3492,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3497,7 +3500,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3505,7 +3508,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
@@ -3513,7 +3516,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3521,7 +3524,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3529,7 +3532,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="285" x14ac:dyDescent="0.2">
@@ -3537,7 +3540,7 @@
         <v>65</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -3545,7 +3548,7 @@
         <v>66</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3553,7 +3556,7 @@
         <v>67</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -3561,7 +3564,7 @@
         <v>69</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -3577,7 +3580,7 @@
         <v>71</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3585,7 +3588,7 @@
         <v>73</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3593,7 +3596,7 @@
         <v>74</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -3606,7 +3609,7 @@
         <v>78</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -3614,7 +3617,7 @@
         <v>79</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -3622,7 +3625,7 @@
         <v>97</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -3630,7 +3633,7 @@
         <v>80</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -3638,7 +3641,7 @@
         <v>82</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -3646,7 +3649,7 @@
         <v>114</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -3654,7 +3657,7 @@
         <v>84</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -3662,7 +3665,7 @@
         <v>88</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3670,7 +3673,7 @@
         <v>89</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -3678,7 +3681,7 @@
         <v>91</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3686,7 +3689,7 @@
         <v>93</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -3694,7 +3697,7 @@
         <v>94</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="369" customHeight="1" x14ac:dyDescent="0.2">
@@ -3702,7 +3705,7 @@
         <v>95</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -3710,7 +3713,7 @@
         <v>96</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -3718,7 +3721,7 @@
         <v>99</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -3726,7 +3729,7 @@
         <v>100</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -3734,7 +3737,7 @@
         <v>115</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -3742,7 +3745,7 @@
         <v>101</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -3750,7 +3753,7 @@
         <v>116</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -3758,7 +3761,7 @@
         <v>103</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -3766,7 +3769,7 @@
         <v>104</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3774,7 +3777,7 @@
         <v>105</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3782,7 +3785,7 @@
         <v>106</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -3790,7 +3793,7 @@
         <v>107</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="150" x14ac:dyDescent="0.2">
@@ -3798,7 +3801,7 @@
         <v>108</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -3806,15 +3809,15 @@
         <v>110</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>320</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
@@ -3822,7 +3825,7 @@
         <v>111</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -3830,7 +3833,7 @@
         <v>112</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3951,15 +3954,15 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="180" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>169</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="135" x14ac:dyDescent="0.2">
@@ -3967,7 +3970,7 @@
         <v>65</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="90" x14ac:dyDescent="0.2">
@@ -3975,7 +3978,7 @@
         <v>66</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3983,7 +3986,7 @@
         <v>67</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -3991,7 +3994,7 @@
         <v>70</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -3999,7 +4002,7 @@
         <v>71</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -4007,7 +4010,7 @@
         <v>72</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -4015,7 +4018,7 @@
         <v>73</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -4023,7 +4026,7 @@
         <v>74</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -4031,7 +4034,7 @@
         <v>75</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="240" x14ac:dyDescent="0.2">
@@ -4039,7 +4042,7 @@
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
@@ -4047,7 +4050,7 @@
         <v>82</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4055,7 +4058,7 @@
         <v>84</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4063,7 +4066,7 @@
         <v>85</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4071,7 +4074,7 @@
         <v>88</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -4079,7 +4082,7 @@
         <v>89</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -4087,7 +4090,7 @@
         <v>91</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4095,7 +4098,7 @@
         <v>93</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4103,7 +4106,7 @@
         <v>94</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -4111,7 +4114,7 @@
         <v>95</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4119,7 +4122,7 @@
         <v>97</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4127,7 +4130,7 @@
         <v>80</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C35" s="4"/>
     </row>
@@ -4136,7 +4139,7 @@
         <v>79</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4144,7 +4147,7 @@
         <v>99</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4152,7 +4155,7 @@
         <v>100</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4160,7 +4163,7 @@
         <v>101</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4168,7 +4171,7 @@
         <v>102</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -4176,7 +4179,7 @@
         <v>103</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4184,7 +4187,7 @@
         <v>104</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4192,7 +4195,7 @@
         <v>105</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4200,7 +4203,7 @@
         <v>117</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4208,7 +4211,7 @@
         <v>107</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4216,7 +4219,7 @@
         <v>108</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4224,7 +4227,7 @@
         <v>110</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -4238,7 +4241,7 @@
         <v>112</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -4269,7 +4272,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4277,15 +4280,15 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4293,7 +4296,7 @@
         <v>76</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F5" s="6"/>
     </row>
@@ -4302,7 +4305,7 @@
         <v>97</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4310,7 +4313,7 @@
         <v>89</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4318,7 +4321,7 @@
         <v>108</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -4349,7 +4352,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4357,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4365,7 +4368,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4373,7 +4376,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4381,7 +4384,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4389,7 +4392,7 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4397,7 +4400,7 @@
         <v>119</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4405,7 +4408,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4413,7 +4416,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4421,7 +4424,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4429,7 +4432,7 @@
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4437,7 +4440,7 @@
         <v>66</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4445,7 +4448,7 @@
         <v>68</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -4453,15 +4456,15 @@
         <v>72</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>322</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4469,7 +4472,7 @@
         <v>77</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -4477,7 +4480,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4485,7 +4488,7 @@
         <v>81</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4493,7 +4496,7 @@
         <v>120</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4501,7 +4504,7 @@
         <v>83</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -4509,7 +4512,7 @@
         <v>86</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -4517,7 +4520,7 @@
         <v>87</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -4525,47 +4528,47 @@
         <v>89</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>324</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>326</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>328</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>330</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="240" x14ac:dyDescent="0.2">
@@ -4573,7 +4576,7 @@
         <v>108</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -4596,7 +4599,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4604,7 +4607,7 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4612,15 +4615,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4628,7 +4631,7 @@
         <v>74</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4636,39 +4639,39 @@
         <v>76</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4676,15 +4679,15 @@
         <v>98</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>344</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="180" x14ac:dyDescent="0.2">
@@ -4692,7 +4695,7 @@
         <v>105</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -4700,7 +4703,7 @@
         <v>117</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4708,15 +4711,15 @@
         <v>107</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -4745,7 +4748,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -4753,7 +4756,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -4762,7 +4765,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
@@ -4770,7 +4773,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -4778,7 +4781,7 @@
         <v>86</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -4786,7 +4789,7 @@
         <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4794,7 +4797,7 @@
         <v>101</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
@@ -4802,7 +4805,7 @@
         <v>108</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -4834,7 +4837,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4842,7 +4845,7 @@
         <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="270" x14ac:dyDescent="0.2">
@@ -4850,7 +4853,7 @@
         <v>121</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -4864,7 +4867,7 @@
         <v>75</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="375" x14ac:dyDescent="0.2">
@@ -4872,7 +4875,7 @@
         <v>86</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="345" x14ac:dyDescent="0.2">
@@ -4880,15 +4883,15 @@
         <v>89</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>264</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="180" x14ac:dyDescent="0.2">
@@ -4896,7 +4899,7 @@
         <v>90</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="345" x14ac:dyDescent="0.2">
@@ -4904,7 +4907,7 @@
         <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="210" x14ac:dyDescent="0.2">
@@ -4943,15 +4946,15 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4959,7 +4962,7 @@
         <v>81</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4967,7 +4970,7 @@
         <v>89</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4975,7 +4978,7 @@
         <v>97</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4983,35 +4986,35 @@
         <v>72</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E0D04F-F0C4-40B8-82BA-73888B47B994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175A03DB-B03F-410C-B952-E82705E32931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="433">
   <si>
     <t>Gene</t>
   </si>
@@ -1124,20 +1124,6 @@
 IKZF1 is recurrently altered in cases of adult ALL (DOI: 10.1016/j.blre.2020.100677).
 Deletion or splicing abnormalities of IKZF1 are reported in 80% of B-ALL cases with BCR::ABL1 fusion (WHO 5th Edition).
 Please note that this assay cannot exclude the germline origin for the IKZF1 c.xxx p.(xxx) variant. Referral to clinical genetics service for family history and further assessment is recommended if clinically indicated.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRAS is altered in 14% of acute lymphoblastic leukaemia patients 
-B-ALL
-KRAS and NRAS mutations have been associated or reported in B ALL and their prognostic significance  is influenced by the subtype; therefore, it should be interpreted in the context of the B ALL subtype. Please correlate with cytogenetics results for interpretation. 
-T-lymphoblastic leukaemia / lymphoma, NOS
-This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
-adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
-The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009 )
-adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
-The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
-Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
-Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).
 </t>
   </si>
   <si>
@@ -1959,6 +1945,44 @@
 For reporting purposes:
 Old - ETNK1 N244S (ENST00000671733.1)
 New - ETNK1 c.724A&gt;G p.Asn155Ser (ENST00000266517.9) (NM_018638.5)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRAS variants are reported in ALL (WHO 5th Edition).
+B-ALL
+KRAS and NRAS mutations have been associated or reported in B ALL and their prognostic significance  is influenced by the subtype; therefore, it should be interpreted in the context of the B ALL subtype. Please correlate with cytogenetics results for interpretation. 
+T-lymphoblastic leukaemia / lymphoma, NOS
+This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
+adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
+The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009 )
+adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
+The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
+Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
+Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KRAS variants are reported in ALL (WHO 5th Edition).
+B-ALL
+KRAS and NRAS mutations have been associated or reported in B ALL and their prognostic significance  is influenced by the subtype; therefore, it should be interpreted in the context of the B ALL subtype. Please correlate with cytogenetics results for interpretation. 
+T-lymphoblastic leukaemia / lymphoma, NOS
+This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
+adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
+The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009 )
+adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
+The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
+Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
+Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).
+B-ALL
+KRAS and NRAS mutations have been associated or reported in B ALL and their prognostic significance  is influenced by the subtype; therefore, it should be interpreted in the context of the B ALL subtype. Please correlate with cytogenetics results for interpretation. 
+T-lymphoblastic leukaemia / lymphoma, NOS
+This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
+adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
+The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009 )
+adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
+The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
+Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
+Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).
 </t>
   </si>
 </sst>
@@ -2518,10 +2542,10 @@
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.2">
@@ -2537,7 +2561,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2561,7 +2585,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2593,7 +2617,7 @@
         <v>67</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -2625,7 +2649,7 @@
         <v>73</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -2838,10 +2862,10 @@
     </row>
     <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>317</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2849,7 +2873,7 @@
         <v>111</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2885,10 +2909,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2909,10 +2933,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -2920,7 +2944,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2949,58 +2973,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>401</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>405</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>407</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>409</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>411</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -3035,74 +3059,74 @@
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>393</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -3122,10 +3146,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3136,7 +3160,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>49</v>
@@ -3158,10 +3182,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3169,10 +3193,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="225" x14ac:dyDescent="0.2">
@@ -3180,7 +3204,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>47</v>
@@ -3216,7 +3240,7 @@
         <v>52</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3279,10 +3303,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3298,112 +3322,112 @@
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="B17" s="17" t="s">
         <v>353</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>354</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>356</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>357</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>360</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>363</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>366</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A22" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>368</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>369</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B23" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>371</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B24" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>373</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B25" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>375</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>378</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -3793,7 +3817,7 @@
         <v>107</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="150" x14ac:dyDescent="0.2">
@@ -3814,10 +3838,10 @@
     </row>
     <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>319</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
@@ -3954,7 +3978,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="180" x14ac:dyDescent="0.2">
@@ -3962,7 +3986,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="135" x14ac:dyDescent="0.2">
@@ -4042,7 +4066,7 @@
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
@@ -4130,7 +4154,7 @@
         <v>80</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C35" s="4"/>
     </row>
@@ -4272,7 +4296,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4285,10 +4309,10 @@
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4305,7 +4329,7 @@
         <v>97</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4313,7 +4337,7 @@
         <v>89</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4321,7 +4345,7 @@
         <v>108</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -4352,7 +4376,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4360,7 +4384,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4368,7 +4392,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4376,7 +4400,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4384,7 +4408,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4392,7 +4416,7 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4400,7 +4424,7 @@
         <v>119</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4408,7 +4432,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4416,7 +4440,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4424,7 +4448,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4432,7 +4456,7 @@
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4440,7 +4464,7 @@
         <v>66</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4448,7 +4472,7 @@
         <v>68</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -4456,15 +4480,15 @@
         <v>72</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>321</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4472,7 +4496,7 @@
         <v>77</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -4480,7 +4504,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4488,7 +4512,7 @@
         <v>81</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4496,7 +4520,7 @@
         <v>120</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4504,7 +4528,7 @@
         <v>83</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -4512,7 +4536,7 @@
         <v>86</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -4520,7 +4544,7 @@
         <v>87</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -4528,47 +4552,47 @@
         <v>89</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>323</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>325</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>327</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>329</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>331</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="240" x14ac:dyDescent="0.2">
@@ -4576,7 +4600,7 @@
         <v>108</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -4607,7 +4631,7 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4615,15 +4639,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4631,7 +4655,7 @@
         <v>74</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4639,39 +4663,39 @@
         <v>76</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>339</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>341</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4679,15 +4703,15 @@
         <v>98</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>343</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="180" x14ac:dyDescent="0.2">
@@ -4695,7 +4719,7 @@
         <v>105</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -4703,7 +4727,7 @@
         <v>117</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4711,15 +4735,15 @@
         <v>107</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -4853,7 +4877,7 @@
         <v>121</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -4875,7 +4899,7 @@
         <v>86</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="345" x14ac:dyDescent="0.2">
@@ -4883,15 +4907,15 @@
         <v>89</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>261</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="180" x14ac:dyDescent="0.2">
@@ -4899,15 +4923,15 @@
         <v>90</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="345" x14ac:dyDescent="0.2">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>261</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="210" x14ac:dyDescent="0.2">
@@ -4946,15 +4970,15 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4962,7 +4986,7 @@
         <v>81</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4970,7 +4994,7 @@
         <v>89</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4978,7 +5002,7 @@
         <v>97</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4986,35 +5010,35 @@
         <v>72</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175A03DB-B03F-410C-B952-E82705E32931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C3200C-476D-4678-AF5D-5C910D26BE26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="7" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="10" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -214,10 +214,6 @@
   </si>
   <si>
     <t>Please note that clonal B cells with a xx phenotype represent only xx% of the total nucleated cells according to flow cytometry.  Therefore, we cannot exclude the presence of low-level variants in this sample.</t>
-  </si>
-  <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the JAK2, CALR, MPL, CSF3R and KIT genes.
-Absence of JAK2 V617F and JAK2 exon 12, MPL exon 10 and CALR exon 9 pathogenic variants does not exclude a myeloproliferative neoplasm. JAK2 (V617F/exon12), MPL exon 10 or CALR exon 9 pathogenic variants have been reported to be present in &gt;97% of cases of polycythaemia vera and approximately 90% of cases of primary myelofibrosis and essential thrombocythaemia.</t>
   </si>
   <si>
     <t>Trisomy 12</t>
@@ -1802,10 +1798,6 @@
     <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NRAS, PHF6, PPM1D, PRPF8, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, UBA1, UBTF, U2AF1, WT1, ZRSR2  genes.</t>
   </si>
   <si>
-    <t>Anaysis on CD138+ cells:
-No pathogenic/likely pathogenic variants were detected in the regions analysed within the BRAF, DIS3, TENT5C, IRF4, KRAS, NRAS, TP53 genes.</t>
-  </si>
-  <si>
     <t>No pertinent (tier 1 or tier 2) copy number aberrations were detected in this sample. 
 This report includes only copy number aberrations pertinent to CLL (tier 1 or tier 2). CNV analysis for chronic lymphocytic leukaemia (CLL) includes chromosome 11, 12, 13, and the short arm of chromosome 17 (17p).</t>
   </si>
@@ -1984,6 +1976,14 @@
 Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
 Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).
 </t>
+  </si>
+  <si>
+    <t>Analysis on CD138+ cells:
+No pathogenic/likely pathogenic variants were detected in the regions analysed within the BRAF, DIS3, TENT5C, IRF4, KRAS, NRAS, TP53 genes.</t>
+  </si>
+  <si>
+    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the JAK2, CALR, MPL, CSF3R and KIT genes.
+Absence of JAK2 V617F and JAK2 exon 12, MPL exon 10 and CALR exon 9 pathogenic variants does not exclude a myeloproliferative neoplasm. JAK2 (V617F/exon 12), MPL exon 10 or CALR exon 9 pathogenic variants have been reported to be present in &gt;97% of cases of polycythaemia vera and approximately 90% of cases of primary myelofibrosis and essential thrombocythaemia.</t>
   </si>
 </sst>
 </file>
@@ -2496,7 +2496,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F2" s="6"/>
     </row>
@@ -2505,7 +2505,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2513,7 +2513,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="150" x14ac:dyDescent="0.2">
@@ -2521,15 +2521,15 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.2">
@@ -2537,15 +2537,15 @@
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>314</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.2">
@@ -2553,7 +2553,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
@@ -2561,7 +2561,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2569,7 +2569,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="255" x14ac:dyDescent="0.2">
@@ -2577,7 +2577,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="167.25" x14ac:dyDescent="0.2">
@@ -2585,7 +2585,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2593,295 +2593,295 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="333" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="285" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="345" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="195" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>316</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2933,10 +2933,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -2944,7 +2944,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2973,58 +2973,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -3054,79 +3054,79 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>396</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>390</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>392</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -3146,10 +3146,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3160,10 +3160,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -3171,10 +3171,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3182,10 +3182,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3193,10 +3193,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="225" x14ac:dyDescent="0.2">
@@ -3204,10 +3204,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3215,10 +3215,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3226,10 +3226,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3237,10 +3237,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3248,10 +3248,10 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3259,10 +3259,10 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3270,10 +3270,10 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3281,10 +3281,10 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3292,10 +3292,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3303,10 +3303,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3314,120 +3314,120 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="B17" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>353</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>356</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>359</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>362</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>364</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>365</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A22" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>368</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B23" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>370</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B24" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>372</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B25" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>374</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>377</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3459,7 +3459,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D2" s="6"/>
     </row>
@@ -3468,7 +3468,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3476,7 +3476,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3484,15 +3484,15 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -3500,7 +3500,7 @@
         <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -3508,7 +3508,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -3516,7 +3516,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3524,7 +3524,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3532,7 +3532,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
@@ -3540,7 +3540,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3548,7 +3548,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3556,308 +3556,308 @@
         <v>40</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="285" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="369" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>318</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3889,7 +3889,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="285" x14ac:dyDescent="0.25">
@@ -3897,7 +3897,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D3" s="6"/>
     </row>
@@ -3906,7 +3906,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3914,15 +3914,15 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3930,15 +3930,15 @@
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="135" x14ac:dyDescent="0.2">
@@ -3946,7 +3946,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -3954,7 +3954,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -3962,7 +3962,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
@@ -3970,7 +3970,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="150" x14ac:dyDescent="0.2">
@@ -3978,7 +3978,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="180" x14ac:dyDescent="0.2">
@@ -3986,286 +3986,286 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="135" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="240" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C35" s="4"/>
     </row>
     <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B48" s="4"/>
     </row>
     <row r="49" spans="1:2" ht="195" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -4296,7 +4296,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4304,48 +4304,48 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -4376,7 +4376,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4384,7 +4384,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4392,7 +4392,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4400,7 +4400,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4408,7 +4408,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4416,15 +4416,15 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4432,7 +4432,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4440,7 +4440,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4448,7 +4448,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4456,151 +4456,151 @@
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>320</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>322</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>324</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>326</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>328</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>330</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="240" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -4623,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4631,7 +4631,7 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4639,111 +4639,111 @@
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>338</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>340</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="180" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -4772,7 +4772,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -4780,7 +4780,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -4789,7 +4789,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
@@ -4797,39 +4797,39 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -4861,85 +4861,85 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5" s="3"/>
     </row>
     <row r="6" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="375" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="345" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="180" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="210" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -4970,75 +4970,75 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C3200C-476D-4678-AF5D-5C910D26BE26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B630E977-7612-41C6-9C2A-B276976FEE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="10" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="1185" yWindow="1800" windowWidth="26010" windowHeight="12720" firstSheet="4" activeTab="4" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -1496,12 +1496,6 @@
     <t>NOTCH1 mutations have been reported in  B-NHL, including MCL, SMZL, DLBCL and FL (DOI: 10.3389/fonc.2018.00550).</t>
   </si>
   <si>
-    <t>To look for low level when strongly suspected: MYD88 chr3:38182641
-This MYD88 variant is characteristic of Waldenstrom macroglobulinemia/ Lymphoplasmacytic Lymphoma, detected in 93 to 97% of cases (WHO 5th Edition). This variant can however also be found in DLBCL, CLL, MZL and IgM MGUS (DOI: 10.1056/NEJMoa1200710; DOI: 10.1038/nature09671). Please correlate with other clinical and pathological findings.
-For non-hotspot variants:
-Please note that this variant is not the classic MYD88 L265P mutation.</t>
-  </si>
-  <si>
     <t>KLF2 variants are most frequently reported in splenic and nodal marginal zone lymphoma, but have also been reported in other B-NHL cases including HCL (DOI: 10.1038/leu.2014.330).</t>
   </si>
   <si>
@@ -1984,6 +1978,13 @@
   <si>
     <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the JAK2, CALR, MPL, CSF3R and KIT genes.
 Absence of JAK2 V617F and JAK2 exon 12, MPL exon 10 and CALR exon 9 pathogenic variants does not exclude a myeloproliferative neoplasm. JAK2 (V617F/exon 12), MPL exon 10 or CALR exon 9 pathogenic variants have been reported to be present in &gt;97% of cases of polycythaemia vera and approximately 90% of cases of primary myelofibrosis and essential thrombocythaemia.</t>
+  </si>
+  <si>
+    <t>To look for low level when strongly suspected: MYD88 chr3:38182641
+MYD88 pathogenic hotspot variant c.818T&gt;C p.(Leu273Pro) also known as p.(L265P) was detected at xx% VAF by NGS.
+This MYD88 variant is characteristic of Waldenstrom macroglobulinemia/ Lymphoplasmacytic Lymphoma, detected in 93 to 97% of cases (WHO 5th Edition). This variant can however also be found in DLBCL, CLL, MZL and IgM MGUS (DOI: 10.1056/NEJMoa1200710; DOI: 10.1038/nature09671). Please correlate with other clinical and pathological findings.
+For non-hotspot variants:
+Please note that this variant is not the classic MYD88 L265P mutation.</t>
   </si>
 </sst>
 </file>
@@ -2542,10 +2543,10 @@
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.2">
@@ -2649,7 +2650,7 @@
         <v>72</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -2862,10 +2863,10 @@
     </row>
     <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>315</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2873,7 +2874,7 @@
         <v>110</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2909,10 +2910,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2933,10 +2934,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>412</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -2944,7 +2945,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2973,58 +2974,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>402</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>404</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>406</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>408</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -3054,79 +3055,79 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>389</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>391</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -3146,10 +3147,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3160,7 +3161,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>48</v>
@@ -3182,10 +3183,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3193,10 +3194,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="225" x14ac:dyDescent="0.2">
@@ -3204,7 +3205,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>46</v>
@@ -3240,7 +3241,7 @@
         <v>51</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3303,10 +3304,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3322,112 +3323,112 @@
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="B17" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>352</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>355</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>358</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>361</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>364</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A22" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>366</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>367</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B23" s="17" t="s">
+        <v>368</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>369</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B24" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>371</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B25" s="17" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>373</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>376</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -3817,7 +3818,7 @@
         <v>106</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="150" x14ac:dyDescent="0.2">
@@ -3838,10 +3839,10 @@
     </row>
     <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>317</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
@@ -3986,7 +3987,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="135" x14ac:dyDescent="0.2">
@@ -4066,7 +4067,7 @@
         <v>77</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
@@ -4154,7 +4155,7 @@
         <v>79</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C35" s="4"/>
     </row>
@@ -4309,10 +4310,10 @@
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4329,7 +4330,7 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4337,7 +4338,7 @@
         <v>88</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4485,10 +4486,10 @@
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>319</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4496,7 +4497,7 @@
         <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -4523,12 +4524,12 @@
         <v>292</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" ht="150" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>303</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -4557,42 +4558,42 @@
     </row>
     <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>321</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>323</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>325</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>327</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>329</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="240" x14ac:dyDescent="0.2">
@@ -4600,7 +4601,7 @@
         <v>107</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -4644,10 +4645,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4655,7 +4656,7 @@
         <v>73</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4668,34 +4669,34 @@
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>337</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>339</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4708,10 +4709,10 @@
     </row>
     <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>341</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="180" x14ac:dyDescent="0.2">
@@ -4719,7 +4720,7 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -4727,7 +4728,7 @@
         <v>116</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4740,10 +4741,10 @@
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -4877,7 +4878,7 @@
         <v>120</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -4899,7 +4900,7 @@
         <v>85</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="345" x14ac:dyDescent="0.2">
@@ -4907,7 +4908,7 @@
         <v>88</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="225" x14ac:dyDescent="0.2">
@@ -4931,7 +4932,7 @@
         <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="210" x14ac:dyDescent="0.2">
@@ -4975,10 +4976,10 @@
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B630E977-7612-41C6-9C2A-B276976FEE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0B97A6-FCD9-44F5-90FB-09E9B28AC2AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="1800" windowWidth="26010" windowHeight="12720" firstSheet="4" activeTab="4" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="29190" yWindow="-1350" windowWidth="26010" windowHeight="12720" firstSheet="4" activeTab="10" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -1747,9 +1747,6 @@
 </t>
   </si>
   <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ATM, CARD11, DNMT3A, FYN, IDH2, IRF4, JAK1, JAK3, PLCG1, POT1, RHOA, SETD2, STAT3, STAT5B, TET2, TP53, VAV1 genes.</t>
-  </si>
-  <si>
     <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ARID1A, ATM, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, DNMT3A, EP300, EZH2, FOXO1, FYN, HRAS, ID3, IDH2, IRF4, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PDCD1LG2, PLCG1, PLCG2, POT1, RHOA, SETD2, STAT3, STAT5B, STAT6, TCF3, TET2, TNFAIP3, TNFRSF14, TP53, VAV1 genes.</t>
   </si>
   <si>
@@ -1881,9 +1878,6 @@
   </si>
   <si>
     <t>VAV1 variants have been reported in angioimmunoblastic T-cell lymphoma (AITL) and nodal PTCL with T-follicular helper (Tfh) phenotype (PTCL-Tfh) (DOI: 10.1182/blood.2020006513).</t>
-  </si>
-  <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ARID1A, ATM, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, EP300, EZH2, FOXO1, HRAS, ID3, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PDCD1LG2, PLCG2, STAT6, TCF3, TNFAIP3, TNFRSF14, TP53 genes.</t>
   </si>
   <si>
     <t>KMT2A alterations have been reported rarely in MPN cases (DOI: 10.1182/blood-2019-128764).</t>
@@ -1985,6 +1979,14 @@
 This MYD88 variant is characteristic of Waldenstrom macroglobulinemia/ Lymphoplasmacytic Lymphoma, detected in 93 to 97% of cases (WHO 5th Edition). This variant can however also be found in DLBCL, CLL, MZL and IgM MGUS (DOI: 10.1056/NEJMoa1200710; DOI: 10.1038/nature09671). Please correlate with other clinical and pathological findings.
 For non-hotspot variants:
 Please note that this variant is not the classic MYD88 L265P mutation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No pathogenic/likely pathogenic variants were detected in the regions analysed within the ARID1A, ATM, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, EP300, EZH2, FOXO1, HRAS, ID3, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PDCD1LG2, PLCG2, STAT6, TCF3, TNFAIP3, TNFRSF14, TP53 genes.
+The analysis did not find copy number alterations supporting copy number loss of 1p, 6q, 7q or copy number gain of 3,12, 18, however, please note this has not been clinically validated so it should be interpreted with caution. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No pathogenic/likely pathogenic variants were detected in the regions analysed within the ATM, CARD11, DNMT3A, FYN, IDH2, IRF4, JAK1, JAK3, PLCG1, POT1, RHOA, SETD2, STAT3, STAT5B, TET2, TP53, VAV1 genes.
+The analysis did not find copy number alterations supporting copy number loss of 9p (containing CDKN2A), 10q (containing PTEN), 11, 17q or copy number gain of 3,12, 18, however, please note this has not been clinically validated so it should be interpreted with caution. </t>
   </si>
 </sst>
 </file>
@@ -2874,7 +2876,7 @@
         <v>110</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2934,10 +2936,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>411</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -2945,7 +2947,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2974,58 +2976,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>397</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>401</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>403</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>405</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>407</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -3055,79 +3057,79 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>385</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>386</v>
-      </c>
       <c r="B5" s="1" t="s">
-        <v>379</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>388</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>390</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -3161,7 +3163,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>48</v>
@@ -3183,7 +3185,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>348</v>
@@ -3194,7 +3196,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>349</v>
@@ -3205,7 +3207,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>46</v>
@@ -3241,7 +3243,7 @@
         <v>51</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3304,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3987,7 +3989,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="135" x14ac:dyDescent="0.2">
@@ -4067,7 +4069,7 @@
         <v>77</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
@@ -4155,7 +4157,7 @@
         <v>79</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C35" s="4"/>
     </row>
@@ -4529,7 +4531,7 @@
         <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -4728,7 +4730,7 @@
         <v>116</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4744,7 +4746,7 @@
         <v>343</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -4809,7 +4811,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>91</v>
       </c>
@@ -4878,7 +4880,7 @@
         <v>120</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -4900,7 +4902,7 @@
         <v>85</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="345" x14ac:dyDescent="0.2">
@@ -4908,7 +4910,7 @@
         <v>88</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="225" x14ac:dyDescent="0.2">
@@ -4932,7 +4934,7 @@
         <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="210" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0B97A6-FCD9-44F5-90FB-09E9B28AC2AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009C3666-D0B9-4B83-AC51-41F5E8848AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29190" yWindow="-1350" windowWidth="26010" windowHeight="12720" firstSheet="4" activeTab="10" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="24735" windowHeight="14550" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -504,11 +504,6 @@
     <t xml:space="preserve">Myeloid neoplasms with germline GATA2 mutation is an ICC disease category and encompassed by the WHO 5th Edition category of myeloid neoplasms associated with germline predisposition. 
 Please note that this assay cannot exclude the germline origin for the GATA2 c.xxx p.(xxx) variant. Identification of a germline predisposition may have implications for patient management including donor selection for allogeneic transplantation. Referral to clinical genetics service for family history and further assessment is recommended.
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somatic IDH2 mutations occur in approximately 12% of AML cases, with increased prevalence in elderly patients (DOI: https://doi.org/10.1038/s41408-021-00497-1). 
-AML with NPM1
-IDH2 mutations frequently cooccur with NPM1 mutated AML (DOI: 10.1182/bloodadvances.2022008282). </t>
   </si>
   <si>
     <t>JAK2 mutations are most commonly associated with myeloproliferative neoplasms and are uncommon in de novo AML  (DOI: 10.1111/bjh.15276). Their presence in AML raises the possibility of secondary AML, particularly arising from an underlying MPN, even in the absence of a documented clinical history.</t>
@@ -1987,6 +1982,11 @@
   <si>
     <t xml:space="preserve">No pathogenic/likely pathogenic variants were detected in the regions analysed within the ATM, CARD11, DNMT3A, FYN, IDH2, IRF4, JAK1, JAK3, PLCG1, POT1, RHOA, SETD2, STAT3, STAT5B, TET2, TP53, VAV1 genes.
 The analysis did not find copy number alterations supporting copy number loss of 9p (containing CDKN2A), 10q (containing PTEN), 11, 17q or copy number gain of 3,12, 18, however, please note this has not been clinically validated so it should be interpreted with caution. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somatic IDH2 mutations occur in approximately 12% of AML cases, with increased prevalence in elderly patients (DOI: 10.1038/s41408-021-00497-1). 
+AML with NPM1
+IDH2 mutations frequently cooccur with NPM1 mutated AML (DOI: 10.1182/bloodadvances.2022008282). </t>
   </si>
 </sst>
 </file>
@@ -2516,7 +2516,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="150" x14ac:dyDescent="0.2">
@@ -2532,7 +2532,7 @@
         <v>112</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.2">
@@ -2545,10 +2545,10 @@
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>312</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.2">
@@ -2564,7 +2564,7 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2588,7 +2588,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2620,7 +2620,7 @@
         <v>66</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -2644,7 +2644,7 @@
         <v>70</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -2652,15 +2652,15 @@
         <v>72</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>131</v>
+        <v>432</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2668,7 +2668,7 @@
         <v>77</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="150" x14ac:dyDescent="0.2">
@@ -2676,7 +2676,7 @@
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -2684,7 +2684,7 @@
         <v>96</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -2692,7 +2692,7 @@
         <v>79</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -2700,7 +2700,7 @@
         <v>81</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -2708,7 +2708,7 @@
         <v>113</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="285" x14ac:dyDescent="0.2">
@@ -2716,7 +2716,7 @@
         <v>87</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -2724,7 +2724,7 @@
         <v>88</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -2732,7 +2732,7 @@
         <v>90</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2740,7 +2740,7 @@
         <v>92</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -2748,7 +2748,7 @@
         <v>93</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -2756,7 +2756,7 @@
         <v>94</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2764,7 +2764,7 @@
         <v>95</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="345" x14ac:dyDescent="0.2">
@@ -2772,7 +2772,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -2780,7 +2780,7 @@
         <v>99</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -2788,7 +2788,7 @@
         <v>114</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2804,7 +2804,7 @@
         <v>115</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="195" x14ac:dyDescent="0.2">
@@ -2812,7 +2812,7 @@
         <v>102</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="150" x14ac:dyDescent="0.2">
@@ -2820,7 +2820,7 @@
         <v>103</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2828,7 +2828,7 @@
         <v>104</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -2836,7 +2836,7 @@
         <v>116</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2844,7 +2844,7 @@
         <v>106</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -2852,7 +2852,7 @@
         <v>107</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2865,10 +2865,10 @@
     </row>
     <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>314</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2876,7 +2876,7 @@
         <v>110</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2936,10 +2936,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -2947,7 +2947,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2976,58 +2976,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>400</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>402</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>404</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>406</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -3057,79 +3057,79 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>387</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>389</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -3149,10 +3149,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3163,7 +3163,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>48</v>
@@ -3185,10 +3185,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3196,10 +3196,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="225" x14ac:dyDescent="0.2">
@@ -3207,7 +3207,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>46</v>
@@ -3243,7 +3243,7 @@
         <v>51</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3306,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3325,112 +3325,112 @@
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="B17" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="C17" s="15" t="s">
         <v>351</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>353</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>354</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>356</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>357</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>359</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>360</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>363</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A22" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>365</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>366</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B23" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>368</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B24" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>370</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B25" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>372</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>375</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3462,7 +3462,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D2" s="6"/>
     </row>
@@ -3471,7 +3471,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -3479,7 +3479,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3487,7 +3487,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -3495,7 +3495,7 @@
         <v>112</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -3503,7 +3503,7 @@
         <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -3511,7 +3511,7 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -3519,7 +3519,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3527,7 +3527,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3535,7 +3535,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
@@ -3543,7 +3543,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3551,7 +3551,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3559,7 +3559,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="285" x14ac:dyDescent="0.2">
@@ -3567,7 +3567,7 @@
         <v>64</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -3575,7 +3575,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3583,7 +3583,7 @@
         <v>66</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -3591,7 +3591,7 @@
         <v>68</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -3607,7 +3607,7 @@
         <v>70</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3615,7 +3615,7 @@
         <v>72</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3623,7 +3623,7 @@
         <v>73</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -3636,7 +3636,7 @@
         <v>77</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -3644,7 +3644,7 @@
         <v>78</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -3652,7 +3652,7 @@
         <v>96</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -3660,7 +3660,7 @@
         <v>79</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -3668,7 +3668,7 @@
         <v>81</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
@@ -3676,7 +3676,7 @@
         <v>113</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -3684,7 +3684,7 @@
         <v>83</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -3692,7 +3692,7 @@
         <v>87</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3700,7 +3700,7 @@
         <v>88</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -3708,7 +3708,7 @@
         <v>90</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3716,7 +3716,7 @@
         <v>92</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -3724,7 +3724,7 @@
         <v>93</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="369" customHeight="1" x14ac:dyDescent="0.2">
@@ -3732,7 +3732,7 @@
         <v>94</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
@@ -3740,7 +3740,7 @@
         <v>95</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
@@ -3748,7 +3748,7 @@
         <v>98</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -3756,7 +3756,7 @@
         <v>99</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
@@ -3764,7 +3764,7 @@
         <v>114</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -3772,7 +3772,7 @@
         <v>100</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
@@ -3780,7 +3780,7 @@
         <v>115</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -3788,7 +3788,7 @@
         <v>102</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -3796,7 +3796,7 @@
         <v>103</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3804,7 +3804,7 @@
         <v>104</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3812,7 +3812,7 @@
         <v>105</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -3820,7 +3820,7 @@
         <v>106</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="150" x14ac:dyDescent="0.2">
@@ -3828,7 +3828,7 @@
         <v>107</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -3836,15 +3836,15 @@
         <v>109</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>316</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
@@ -3852,7 +3852,7 @@
         <v>110</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -3860,7 +3860,7 @@
         <v>111</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3892,7 +3892,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="285" x14ac:dyDescent="0.25">
@@ -3900,7 +3900,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D3" s="6"/>
     </row>
@@ -3909,7 +3909,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3917,7 +3917,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3925,7 +3925,7 @@
         <v>112</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="120" x14ac:dyDescent="0.2">
@@ -3933,7 +3933,7 @@
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -3941,7 +3941,7 @@
         <v>117</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="135" x14ac:dyDescent="0.2">
@@ -3949,7 +3949,7 @@
         <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -3957,7 +3957,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -3965,7 +3965,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
@@ -3973,7 +3973,7 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="150" x14ac:dyDescent="0.2">
@@ -3981,7 +3981,7 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="180" x14ac:dyDescent="0.2">
@@ -3989,7 +3989,7 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="135" x14ac:dyDescent="0.2">
@@ -3997,7 +3997,7 @@
         <v>64</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="90" x14ac:dyDescent="0.2">
@@ -4005,7 +4005,7 @@
         <v>65</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4013,7 +4013,7 @@
         <v>66</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4021,7 +4021,7 @@
         <v>69</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -4029,7 +4029,7 @@
         <v>70</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
@@ -4037,7 +4037,7 @@
         <v>71</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -4045,7 +4045,7 @@
         <v>72</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -4053,7 +4053,7 @@
         <v>73</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -4061,7 +4061,7 @@
         <v>74</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="240" x14ac:dyDescent="0.2">
@@ -4069,7 +4069,7 @@
         <v>77</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
@@ -4077,7 +4077,7 @@
         <v>81</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4085,7 +4085,7 @@
         <v>83</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4093,7 +4093,7 @@
         <v>84</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4101,7 +4101,7 @@
         <v>87</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="165" x14ac:dyDescent="0.2">
@@ -4109,7 +4109,7 @@
         <v>88</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -4117,7 +4117,7 @@
         <v>90</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4125,7 +4125,7 @@
         <v>92</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4133,7 +4133,7 @@
         <v>93</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -4141,7 +4141,7 @@
         <v>94</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4149,7 +4149,7 @@
         <v>96</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4157,7 +4157,7 @@
         <v>79</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C35" s="4"/>
     </row>
@@ -4166,7 +4166,7 @@
         <v>78</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4174,7 +4174,7 @@
         <v>98</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4182,7 +4182,7 @@
         <v>99</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4190,7 +4190,7 @@
         <v>100</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4198,7 +4198,7 @@
         <v>101</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -4206,7 +4206,7 @@
         <v>102</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4214,7 +4214,7 @@
         <v>103</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4222,7 +4222,7 @@
         <v>104</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4230,7 +4230,7 @@
         <v>116</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4238,7 +4238,7 @@
         <v>106</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4246,7 +4246,7 @@
         <v>107</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4254,7 +4254,7 @@
         <v>109</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -4268,7 +4268,7 @@
         <v>111</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -4299,7 +4299,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4307,15 +4307,15 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4323,7 +4323,7 @@
         <v>75</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F5" s="6"/>
     </row>
@@ -4332,7 +4332,7 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4340,7 +4340,7 @@
         <v>88</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4348,7 +4348,7 @@
         <v>107</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -4379,7 +4379,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4387,7 +4387,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4395,7 +4395,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4403,7 +4403,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4411,7 +4411,7 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4419,7 +4419,7 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4427,7 +4427,7 @@
         <v>118</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4435,7 +4435,7 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4443,7 +4443,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4451,7 +4451,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4459,7 +4459,7 @@
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4467,7 +4467,7 @@
         <v>65</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4475,7 +4475,7 @@
         <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
@@ -4483,15 +4483,15 @@
         <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>318</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -4499,7 +4499,7 @@
         <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -4507,7 +4507,7 @@
         <v>96</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4515,7 +4515,7 @@
         <v>80</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4523,7 +4523,7 @@
         <v>119</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="150" x14ac:dyDescent="0.2">
@@ -4531,7 +4531,7 @@
         <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
@@ -4539,7 +4539,7 @@
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -4547,7 +4547,7 @@
         <v>86</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -4555,47 +4555,47 @@
         <v>88</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>320</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>322</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>324</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>326</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>328</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="240" x14ac:dyDescent="0.2">
@@ -4603,7 +4603,7 @@
         <v>107</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4634,7 +4634,7 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4642,15 +4642,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4658,7 +4658,7 @@
         <v>73</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -4666,39 +4666,39 @@
         <v>75</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>332</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>336</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>338</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -4706,15 +4706,15 @@
         <v>97</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="180" x14ac:dyDescent="0.2">
@@ -4722,7 +4722,7 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.2">
@@ -4730,7 +4730,7 @@
         <v>116</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -4738,15 +4738,15 @@
         <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -4775,7 +4775,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.2">
@@ -4783,7 +4783,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -4792,7 +4792,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
@@ -4800,7 +4800,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -4808,7 +4808,7 @@
         <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4816,7 +4816,7 @@
         <v>91</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4824,7 +4824,7 @@
         <v>100</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
@@ -4832,7 +4832,7 @@
         <v>107</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -4864,7 +4864,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4872,7 +4872,7 @@
         <v>64</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="270" x14ac:dyDescent="0.2">
@@ -4880,7 +4880,7 @@
         <v>120</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -4894,7 +4894,7 @@
         <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="375" x14ac:dyDescent="0.2">
@@ -4902,7 +4902,7 @@
         <v>85</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="345" x14ac:dyDescent="0.2">
@@ -4910,15 +4910,15 @@
         <v>88</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="180" x14ac:dyDescent="0.2">
@@ -4926,7 +4926,7 @@
         <v>89</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
@@ -4934,7 +4934,7 @@
         <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="210" x14ac:dyDescent="0.2">
@@ -4973,15 +4973,15 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
@@ -4989,7 +4989,7 @@
         <v>80</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -4997,7 +4997,7 @@
         <v>88</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -5005,7 +5005,7 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
@@ -5013,35 +5013,35 @@
         <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\NGS\Documents\Comments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Documents\Comments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009C3666-D0B9-4B83-AC51-41F5E8848AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F03E5F-3EF9-4944-8FEC-C05A87A22EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="24735" windowHeight="14550" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="29370" yWindow="465" windowWidth="25725" windowHeight="14145" activeTab="4" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -1969,24 +1969,24 @@
 Absence of JAK2 V617F and JAK2 exon 12, MPL exon 10 and CALR exon 9 pathogenic variants does not exclude a myeloproliferative neoplasm. JAK2 (V617F/exon 12), MPL exon 10 or CALR exon 9 pathogenic variants have been reported to be present in &gt;97% of cases of polycythaemia vera and approximately 90% of cases of primary myelofibrosis and essential thrombocythaemia.</t>
   </si>
   <si>
+    <t xml:space="preserve">No pathogenic/likely pathogenic variants were detected in the regions analysed within the ARID1A, ATM, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, EP300, EZH2, FOXO1, HRAS, ID3, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PDCD1LG2, PLCG2, STAT6, TCF3, TNFAIP3, TNFRSF14, TP53 genes.
+The analysis did not find copy number alterations supporting copy number loss of 1p, 6q, 7q or copy number gain of 3,12, 18, however, please note this has not been clinically validated so it should be interpreted with caution. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">No pathogenic/likely pathogenic variants were detected in the regions analysed within the ATM, CARD11, DNMT3A, FYN, IDH2, IRF4, JAK1, JAK3, PLCG1, POT1, RHOA, SETD2, STAT3, STAT5B, TET2, TP53, VAV1 genes.
+The analysis did not find copy number alterations supporting copy number loss of 9p (containing CDKN2A), 10q (containing PTEN), 11, 17q or copy number gain of 3,12, 18, however, please note this has not been clinically validated so it should be interpreted with caution. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Somatic IDH2 mutations occur in approximately 12% of AML cases, with increased prevalence in elderly patients (DOI: 10.1038/s41408-021-00497-1). 
+AML with NPM1
+IDH2 mutations frequently cooccur with NPM1 mutated AML (DOI: 10.1182/bloodadvances.2022008282). </t>
+  </si>
+  <si>
     <t>To look for low level when strongly suspected: MYD88 chr3:38182641
-MYD88 pathogenic hotspot variant c.818T&gt;C p.(Leu273Pro) also known as p.(L265P) was detected at xx% VAF by NGS.
+MYD88 pathogenic hotspot variant c.755T&gt;C p.(Leu252Pro) also known as p.(L265P) was detected at xx% VAF by NGS.
 This MYD88 variant is characteristic of Waldenstrom macroglobulinemia/ Lymphoplasmacytic Lymphoma, detected in 93 to 97% of cases (WHO 5th Edition). This variant can however also be found in DLBCL, CLL, MZL and IgM MGUS (DOI: 10.1056/NEJMoa1200710; DOI: 10.1038/nature09671). Please correlate with other clinical and pathological findings.
 For non-hotspot variants:
 Please note that this variant is not the classic MYD88 L265P mutation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No pathogenic/likely pathogenic variants were detected in the regions analysed within the ARID1A, ATM, BCL2, BRAF, BTK, CARD11, CCND3, CD79B, CREBBP, CXCR4, EP300, EZH2, FOXO1, HRAS, ID3, JAK1, JAK3, KLF2, KRAS, MAP2K1, MEF2B, MYD88, NOTCH1, NOTCH2, NRAS, PDCD1LG2, PLCG2, STAT6, TCF3, TNFAIP3, TNFRSF14, TP53 genes.
-The analysis did not find copy number alterations supporting copy number loss of 1p, 6q, 7q or copy number gain of 3,12, 18, however, please note this has not been clinically validated so it should be interpreted with caution. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">No pathogenic/likely pathogenic variants were detected in the regions analysed within the ATM, CARD11, DNMT3A, FYN, IDH2, IRF4, JAK1, JAK3, PLCG1, POT1, RHOA, SETD2, STAT3, STAT5B, TET2, TP53, VAV1 genes.
-The analysis did not find copy number alterations supporting copy number loss of 9p (containing CDKN2A), 10q (containing PTEN), 11, 17q or copy number gain of 3,12, 18, however, please note this has not been clinically validated so it should be interpreted with caution. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Somatic IDH2 mutations occur in approximately 12% of AML cases, with increased prevalence in elderly patients (DOI: 10.1038/s41408-021-00497-1). 
-AML with NPM1
-IDH2 mutations frequently cooccur with NPM1 mutated AML (DOI: 10.1182/bloodadvances.2022008282). </t>
   </si>
 </sst>
 </file>
@@ -2660,7 +2660,7 @@
         <v>73</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3073,7 +3073,7 @@
         <v>383</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.2">
@@ -3081,7 +3081,7 @@
         <v>384</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
@@ -4531,7 +4531,7 @@
         <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Documents\Comments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54F03E5F-3EF9-4944-8FEC-C05A87A22EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D6C054-EDE9-46D5-BFB4-ADF0401C1D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29370" yWindow="465" windowWidth="25725" windowHeight="14145" activeTab="4" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="28680" yWindow="-1860" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
     <author>tc={61FD660D-2DBF-40EC-B926-88247D8CDA05}</author>
   </authors>
   <commentList>
-    <comment ref="C26" authorId="0" shapeId="0" xr:uid="{61FD660D-2DBF-40EC-B926-88247D8CDA05}">
+    <comment ref="C27" authorId="0" shapeId="0" xr:uid="{61FD660D-2DBF-40EC-B926-88247D8CDA05}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="440">
   <si>
     <t>Gene</t>
   </si>
@@ -1041,12 +1041,6 @@
 SETBP1 mutations have been reported in MDS/MPN with SF3B1 and thrombocytosis.
 Differential diagnosis - information only
 The overall mutation profile of MDS/MPN_N is similar to that of CNL, CMML, and MDS/MPN_NOS. CSF3R mutations are distinctly more common in CNL than in MDS/MPN_N (&gt; 60% vs &lt; 20%), and SETBP1 mutations are most frequently identified in MDS/MPN_N (&gt; 30%). Hence, morphological criteria are important for distinguishing these entities (WHO 5th edition).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-This is consistent with MDS with mutated (biallelic) TP53, as described by the WHO (5th Edition) and ICC (2022), and is associated with adverse prognosis independent of treatment (DOI: 10.1056/EVIDoa2200008).
-Multihit TP53 can be confirmed by the presence of 2 or more distinct TP53 mutations (VAF &gt; 10%) or a single TP53 mutation associated with (1) a cytogenetic deletion involving the TP53 locus at 17p13.1, (2) a VAF of &gt;49%, or (3) copy neutral loss of heterozygosity (LOH) at the 17p TP53 locus.In the absence of LOH information, the presence of a single TP53 mutation in the context of any complex karyotype is considered equivalent to a multihit TP53 (ICC 2022 and WHO 5th Edition). 
-The prognostic impact of monoallelic TP53 in MDS is currently unconfirmed (DOI: 10.1056/EVIDoa2200008).</t>
   </si>
   <si>
     <t>DIS3 mutations have been reported in approximately 10% of multiple myeloma cases (DOI: 10.1158/1078-0432.CCR-19-1507).</t>
@@ -1987,6 +1981,34 @@
 This MYD88 variant is characteristic of Waldenstrom macroglobulinemia/ Lymphoplasmacytic Lymphoma, detected in 93 to 97% of cases (WHO 5th Edition). This variant can however also be found in DLBCL, CLL, MZL and IgM MGUS (DOI: 10.1056/NEJMoa1200710; DOI: 10.1038/nature09671). Please correlate with other clinical and pathological findings.
 For non-hotspot variants:
 Please note that this variant is not the classic MYD88 L265P mutation.</t>
+  </si>
+  <si>
+    <t>Tumour suppressor</t>
+  </si>
+  <si>
+    <t>Oncogene</t>
+  </si>
+  <si>
+    <t>Insufficient evidence to classify</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>Oncogene / tumour suppressor</t>
+  </si>
+  <si>
+    <t>DLEU2/miR15 del focal</t>
+  </si>
+  <si>
+    <t>CNV analysis detected copy number loss of chromosome 13q14 containing the DLEU2¬-miR¬-15¬-16 cluster. This is frequently reported in CLL (WHO 5th Edition).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+This is consistent with MDS with mutated (biallelic) TP53, as described by the WHO (5th Edition) and ICC (2022), and is associated with adverse prognosis independent of treatment (DOI: 10.1056/EVIDoa2200008).
+Multihit TP53 can be confirmed by the presence of 2 or more distinct TP53 mutations (VAF &gt; 10%) or a single TP53 mutation associated with (1) a cytogenetic deletion involving the TP53 locus at 17p13.1, (2) a VAF of &gt;49%, or (3) copy neutral loss of heterozygosity (LOH) at the 17p TP53 locus.In the absence of LOH information, the presence of a single TP53 mutation in the context of any complex karyotype is considered equivalent to a multihit TP53 (ICC 2022 and WHO 5th Edition). 
+The prognostic impact of monoallelic TP53 in MDS is currently unconfirmed (DOI: 10.1056/EVIDoa2200008).
+Please note that interpretation of these findings should be along with bone marrow morphology and other clinical/pathological features to confirm or exclude age related clonal haematopoiesis of indeterminate potential (CHIP) or any other haematological neoplasm. According to the literature, chemotherapy may select for the TP53 mutants and may lead to therapy related MDS (DOI:10.1038/nature13968).</t>
   </si>
 </sst>
 </file>
@@ -2470,7 +2492,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C26" dT="2025-10-24T14:51:55.67" personId="{E177F675-2BF7-4D34-B125-6F3DDBFD449B}" id="{61FD660D-2DBF-40EC-B926-88247D8CDA05}">
+  <threadedComment ref="C27" dT="2025-10-24T14:51:55.67" personId="{E177F675-2BF7-4D34-B125-6F3DDBFD449B}" id="{61FD660D-2DBF-40EC-B926-88247D8CDA05}">
     <text>Incorrect in WHO - PTEN is on 10q</text>
   </threadedComment>
 </ThreadedComments>
@@ -2478,12 +2500,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57B5312-BC96-450F-B6E5-702AE74DB434}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="126.21875" style="5" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="5"/>
+    <col min="3" max="3" width="16.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -2493,38 +2516,53 @@
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="150.75" x14ac:dyDescent="0.25">
+      <c r="C1" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="105.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>121</v>
       </c>
+      <c r="C2" t="s">
+        <v>432</v>
+      </c>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" ht="120" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="C3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="150" x14ac:dyDescent="0.2">
+      <c r="C4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>121</v>
+      </c>
+      <c r="C5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -2534,29 +2572,41 @@
       <c r="B6" s="4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>123</v>
       </c>
+      <c r="C7" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>311</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="45" x14ac:dyDescent="0.2">
+      <c r="C8" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>124</v>
+      </c>
+      <c r="C9" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
@@ -2564,7 +2614,10 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
+      </c>
+      <c r="C10" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2574,6 +2627,9 @@
       <c r="B11" s="4" t="s">
         <v>125</v>
       </c>
+      <c r="C11" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="255" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
@@ -2582,13 +2638,19 @@
       <c r="B12" s="4" t="s">
         <v>126</v>
       </c>
+      <c r="C12" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="167.25" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
+      </c>
+      <c r="C13" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2598,6 +2660,9 @@
       <c r="B14" s="4" t="s">
         <v>127</v>
       </c>
+      <c r="C14" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
@@ -2606,6 +2671,9 @@
       <c r="B15" s="4" t="s">
         <v>128</v>
       </c>
+      <c r="C15" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
@@ -2614,277 +2682,387 @@
       <c r="B16" s="4" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="333" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="333" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+      <c r="C17" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+      <c r="C18" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+      <c r="C21" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+      <c r="C22" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="150" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="165" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="165" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="C27" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>113</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="285" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="285" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="165" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+      <c r="C30" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>90</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C31" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>92</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="90" x14ac:dyDescent="0.2">
+      <c r="C32" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>93</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C33" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C34" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="345" x14ac:dyDescent="0.2">
+      <c r="C35" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="345" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C36" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>99</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C37" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>114</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+      <c r="C38" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C39" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>115</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="195" x14ac:dyDescent="0.2">
+      <c r="C40" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>102</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="150" x14ac:dyDescent="0.2">
+      <c r="C41" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>103</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C42" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>104</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C43" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>116</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+      <c r="C44" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>106</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+      <c r="C45" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>107</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+      <c r="C46" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>109</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C47" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>313</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C48" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>110</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+      <c r="C49" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>111</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>121</v>
+      </c>
+      <c r="C50" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C51" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -2912,10 +3090,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2936,10 +3114,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>409</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -2947,7 +3125,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -2976,58 +3154,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>395</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>399</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>401</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>403</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>405</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -3057,79 +3235,79 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>386</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>388</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -3139,7 +3317,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9F24A3-EA82-4A17-B915-0BA86DD79F59}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -3149,10 +3327,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3163,7 +3341,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>48</v>
@@ -3185,10 +3363,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3196,76 +3374,76 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="225" x14ac:dyDescent="0.2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="225" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>412</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="75" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3273,43 +3451,43 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>394</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>393</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3317,120 +3495,131 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A19" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>353</v>
       </c>
-      <c r="C18" s="15" t="s">
+    </row>
+    <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A20" s="16" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="16" t="s">
+      <c r="B20" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="C19" s="15" t="s">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="16" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
+      <c r="B21" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="C20" s="15" t="s">
+    </row>
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A22" s="16" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A21" s="16" t="s">
+      <c r="B22" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>362</v>
       </c>
-      <c r="C21" s="15" t="s">
+    </row>
+    <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A23" s="18" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
+      <c r="B23" s="17" t="s">
         <v>364</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C23" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="C22" s="15" t="s">
+    </row>
+    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A24" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A23" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="B23" s="17" t="s">
+      <c r="C24" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="C23" s="15" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="B25" s="17" t="s">
         <v>368</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="B24" s="17" t="s">
+      <c r="C25" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="C24" s="15" t="s">
+    </row>
+    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A26" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A25" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="B25" s="17" t="s">
+      <c r="C26" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="C25" s="15" t="s">
+    </row>
+    <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
+      <c r="A27" s="16" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
+      <c r="B27" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="C27" s="15" t="s">
         <v>374</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -3446,7 +3635,8 @@
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="110.44140625" style="8" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="5"/>
+    <col min="3" max="3" width="26" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3456,6 +3646,9 @@
       <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="5" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="2" spans="1:4" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -3464,6 +3657,9 @@
       <c r="B2" s="7" t="s">
         <v>199</v>
       </c>
+      <c r="C2" t="s">
+        <v>432</v>
+      </c>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:4" ht="75" x14ac:dyDescent="0.2">
@@ -3473,6 +3669,9 @@
       <c r="B3" s="4" t="s">
         <v>237</v>
       </c>
+      <c r="C3" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
@@ -3481,6 +3680,9 @@
       <c r="B4" s="8" t="s">
         <v>200</v>
       </c>
+      <c r="C4" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
@@ -3489,6 +3691,9 @@
       <c r="B5" s="8" t="s">
         <v>201</v>
       </c>
+      <c r="C5" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
@@ -3497,6 +3702,9 @@
       <c r="B6" s="4" t="s">
         <v>238</v>
       </c>
+      <c r="C6" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
@@ -3505,6 +3713,9 @@
       <c r="B7" s="8" t="s">
         <v>202</v>
       </c>
+      <c r="C7" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
@@ -3513,6 +3724,9 @@
       <c r="B8" s="8" t="s">
         <v>203</v>
       </c>
+      <c r="C8" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
@@ -3521,6 +3735,9 @@
       <c r="B9" s="8" t="s">
         <v>204</v>
       </c>
+      <c r="C9" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -3529,6 +3746,9 @@
       <c r="B10" s="8" t="s">
         <v>205</v>
       </c>
+      <c r="C10" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
@@ -3537,6 +3757,9 @@
       <c r="B11" s="8" t="s">
         <v>206</v>
       </c>
+      <c r="C11" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
@@ -3545,6 +3768,9 @@
       <c r="B12" s="4" t="s">
         <v>207</v>
       </c>
+      <c r="C12" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="120" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
@@ -3553,6 +3779,9 @@
       <c r="B13" s="8" t="s">
         <v>208</v>
       </c>
+      <c r="C13" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
@@ -3561,6 +3790,9 @@
       <c r="B14" s="8" t="s">
         <v>209</v>
       </c>
+      <c r="C14" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="285" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
@@ -3569,6 +3801,9 @@
       <c r="B15" s="8" t="s">
         <v>210</v>
       </c>
+      <c r="C15" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
@@ -3577,290 +3812,401 @@
       <c r="B16" s="5" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="90" x14ac:dyDescent="0.2">
+      <c r="C17" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+      <c r="C18" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C22" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="90" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+      <c r="C27" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>113</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="90" x14ac:dyDescent="0.2">
+      <c r="C30" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+      <c r="C31" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C32" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>90</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C33" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>92</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C34" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>93</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="369" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C35" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="369" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C36" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C37" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>98</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="165" x14ac:dyDescent="0.2">
+      <c r="C38" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>99</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C39" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>114</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="165" x14ac:dyDescent="0.2">
+      <c r="C40" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C41" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>115</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C42" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>102</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C43" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>103</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+      <c r="C44" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>104</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+      <c r="C45" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>105</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="90" x14ac:dyDescent="0.2">
+      <c r="C46" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>106</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="150" x14ac:dyDescent="0.2">
+        <v>345</v>
+      </c>
+      <c r="C47" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="210" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>107</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+        <v>439</v>
+      </c>
+      <c r="C48" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>109</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C49" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>315</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C50" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>110</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="C51" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>111</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>236</v>
+      </c>
+      <c r="C52" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -3886,6 +4232,9 @@
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="5" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
@@ -3894,6 +4243,9 @@
       <c r="B2" s="4" t="s">
         <v>156</v>
       </c>
+      <c r="C2" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="285" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -3902,6 +4254,9 @@
       <c r="B3" s="3" t="s">
         <v>166</v>
       </c>
+      <c r="C3" t="s">
+        <v>432</v>
+      </c>
       <c r="D3" s="6"/>
     </row>
     <row r="4" spans="1:4" ht="75" x14ac:dyDescent="0.2">
@@ -3911,6 +4266,9 @@
       <c r="B4" s="4" t="s">
         <v>157</v>
       </c>
+      <c r="C4" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
@@ -3919,6 +4277,9 @@
       <c r="B5" s="4" t="s">
         <v>158</v>
       </c>
+      <c r="C5" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
@@ -3927,6 +4288,9 @@
       <c r="B6" s="4" t="s">
         <v>159</v>
       </c>
+      <c r="C6" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="120" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
@@ -3935,6 +4299,9 @@
       <c r="B7" s="4" t="s">
         <v>160</v>
       </c>
+      <c r="C7" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
@@ -3943,6 +4310,9 @@
       <c r="B8" s="4" t="s">
         <v>161</v>
       </c>
+      <c r="C8" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="135" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
@@ -3951,6 +4321,9 @@
       <c r="B9" s="4" t="s">
         <v>162</v>
       </c>
+      <c r="C9" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -3959,6 +4332,9 @@
       <c r="B10" s="10" t="s">
         <v>163</v>
       </c>
+      <c r="C10" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
@@ -3967,6 +4343,9 @@
       <c r="B11" s="3" t="s">
         <v>164</v>
       </c>
+      <c r="C11" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
@@ -3975,13 +4354,19 @@
       <c r="B12" s="4" t="s">
         <v>165</v>
       </c>
+      <c r="C12" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="150" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
+      </c>
+      <c r="C13" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="180" x14ac:dyDescent="0.2">
@@ -3989,7 +4374,10 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
+      </c>
+      <c r="C14" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="135" x14ac:dyDescent="0.2">
@@ -3999,6 +4387,9 @@
       <c r="B15" s="3" t="s">
         <v>167</v>
       </c>
+      <c r="C15" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
@@ -4007,133 +4398,184 @@
       <c r="B16" s="3" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+      <c r="C17" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C18" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="90" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="90" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C22" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="240" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="240" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
+        <v>415</v>
+      </c>
+      <c r="C24" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>84</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+      <c r="C27" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="165" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>90</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C30" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>92</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+      <c r="C31" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>93</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>183</v>
+      </c>
+      <c r="C32" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -4143,6 +4585,9 @@
       <c r="B33" s="3" t="s">
         <v>184</v>
       </c>
+      <c r="C33" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="34" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
@@ -4151,15 +4596,20 @@
       <c r="B34" s="3" t="s">
         <v>185</v>
       </c>
+      <c r="C34" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="C35" s="4"/>
+        <v>417</v>
+      </c>
+      <c r="C35" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
@@ -4168,6 +4618,9 @@
       <c r="B36" s="4" t="s">
         <v>186</v>
       </c>
+      <c r="C36" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
@@ -4176,6 +4629,9 @@
       <c r="B37" s="3" t="s">
         <v>197</v>
       </c>
+      <c r="C37" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
@@ -4184,6 +4640,9 @@
       <c r="B38" s="3" t="s">
         <v>198</v>
       </c>
+      <c r="C38" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
@@ -4192,6 +4651,9 @@
       <c r="B39" s="3" t="s">
         <v>187</v>
       </c>
+      <c r="C39" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
@@ -4200,6 +4662,9 @@
       <c r="B40" s="3" t="s">
         <v>188</v>
       </c>
+      <c r="C40" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
@@ -4208,6 +4673,9 @@
       <c r="B41" s="3" t="s">
         <v>189</v>
       </c>
+      <c r="C41" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
@@ -4216,6 +4684,9 @@
       <c r="B42" s="3" t="s">
         <v>190</v>
       </c>
+      <c r="C42" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
@@ -4224,6 +4695,9 @@
       <c r="B43" s="3" t="s">
         <v>191</v>
       </c>
+      <c r="C43" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
@@ -4232,6 +4706,9 @@
       <c r="B44" s="4" t="s">
         <v>192</v>
       </c>
+      <c r="C44" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
@@ -4240,6 +4717,9 @@
       <c r="B45" s="4" t="s">
         <v>193</v>
       </c>
+      <c r="C45" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
@@ -4248,6 +4728,9 @@
       <c r="B46" s="3" t="s">
         <v>194</v>
       </c>
+      <c r="C46" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
@@ -4256,19 +4739,28 @@
       <c r="B47" s="3" t="s">
         <v>195</v>
       </c>
+      <c r="C47" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>110</v>
       </c>
       <c r="B48" s="4"/>
-    </row>
-    <row r="49" spans="1:2" ht="195" x14ac:dyDescent="0.2">
+      <c r="C48" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>111</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>196</v>
+      </c>
+      <c r="C49" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -4283,7 +4775,8 @@
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="68.88671875" style="4" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="5"/>
+    <col min="3" max="3" width="24.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -4293,13 +4786,19 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="5" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="2" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
+      </c>
+      <c r="C2" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4307,15 +4806,21 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>308</v>
+      <c r="C4" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4323,7 +4828,10 @@
         <v>75</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
+      </c>
+      <c r="C5" t="s">
+        <v>433</v>
       </c>
       <c r="F5" s="6"/>
     </row>
@@ -4332,7 +4840,10 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
+      </c>
+      <c r="C6" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4340,7 +4851,10 @@
         <v>88</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
+      </c>
+      <c r="C7" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4348,7 +4862,10 @@
         <v>107</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
+      </c>
+      <c r="C8" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -4358,252 +4875,343 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD634E30-2FF4-4CAE-85E8-877093FDD5DC}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="99.6640625" style="4" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="5"/>
+    <col min="3" max="3" width="25.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+      <c r="C1" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+      <c r="C2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+      <c r="C3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+      <c r="C4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+      <c r="C5" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+        <v>278</v>
+      </c>
+      <c r="C6" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+        <v>279</v>
+      </c>
+      <c r="C7" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>118</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+      <c r="C8" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+      <c r="C9" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+      <c r="C10" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+        <v>283</v>
+      </c>
+      <c r="C11" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+      <c r="C12" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>65</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+        <v>285</v>
+      </c>
+      <c r="C13" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+      <c r="C14" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+        <v>287</v>
+      </c>
+      <c r="C15" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>317</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+      <c r="C17" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+      <c r="C18" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+        <v>289</v>
+      </c>
+      <c r="C19" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>119</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="150" x14ac:dyDescent="0.2">
+        <v>290</v>
+      </c>
+      <c r="C20" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+      <c r="C21" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="C22" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+        <v>299</v>
+      </c>
+      <c r="C23" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+      <c r="C24" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>319</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="B26" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="C26" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="B27" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="B28" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="B29" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="240" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="240" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>107</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
+      </c>
+      <c r="C30" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -4613,7 +5221,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86327E5-C3AE-4491-932D-1E8E8290018D}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.6640625" style="5" customWidth="1"/>
@@ -4621,132 +5229,180 @@
     <col min="3" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+        <v>246</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="C2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+      <c r="C3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+      <c r="C4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+      <c r="C5" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>75</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+        <v>294</v>
+      </c>
+      <c r="C6" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>331</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>334</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="C8" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>335</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="B9" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="B10" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>97</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+      <c r="C11" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>339</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="180" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="90" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+      <c r="C13" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>116</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="60" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+      <c r="C14" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+      <c r="C15" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
+      </c>
+      <c r="C16" t="s">
+        <v>433</v>
       </c>
     </row>
   </sheetData>
@@ -4760,6 +5416,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="170.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -4769,21 +5426,30 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+        <v>247</v>
+      </c>
+      <c r="C2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
+      </c>
+      <c r="C3" t="s">
+        <v>433</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -4792,7 +5458,10 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
+      </c>
+      <c r="C4" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
@@ -4800,7 +5469,10 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
+      </c>
+      <c r="C5" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -4808,7 +5480,10 @@
         <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
+      </c>
+      <c r="C6" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4816,7 +5491,10 @@
         <v>91</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4824,7 +5502,10 @@
         <v>100</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
+      </c>
+      <c r="C8" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
@@ -4832,7 +5513,10 @@
         <v>107</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="C9" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -4843,106 +5527,143 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD65405E-7754-49F8-8BF9-5636ED341878}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="112.44140625" style="5" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="5"/>
+    <col min="3" max="3" width="25.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+      <c r="C1" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+        <v>255</v>
+      </c>
+      <c r="C2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="270" x14ac:dyDescent="0.2">
+        <v>256</v>
+      </c>
+      <c r="C3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>120</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+      <c r="C4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B5" s="3"/>
-    </row>
-    <row r="6" spans="1:2" ht="150" x14ac:dyDescent="0.2">
+      <c r="C5" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="375" x14ac:dyDescent="0.2">
+        <v>257</v>
+      </c>
+      <c r="C6" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="375" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="345" x14ac:dyDescent="0.2">
+        <v>419</v>
+      </c>
+      <c r="C7" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="345" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="225" x14ac:dyDescent="0.2">
+        <v>424</v>
+      </c>
+      <c r="C8" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="180" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>89</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="409.5" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="210" x14ac:dyDescent="0.2">
+        <v>425</v>
+      </c>
+      <c r="C11" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="210" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>107</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>108</v>
+      </c>
+      <c r="C12" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -4952,7 +5673,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D047D86-2DA7-40D0-AE18-DD845C71F766}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="5" customWidth="1"/>
@@ -4960,91 +5681,127 @@
     <col min="3" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="105" x14ac:dyDescent="0.2">
+      <c r="C1" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+        <v>266</v>
+      </c>
+      <c r="C2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="120" x14ac:dyDescent="0.2">
+      <c r="C3" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+        <v>267</v>
+      </c>
+      <c r="C4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>88</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+      <c r="C6" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C7" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="C9" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="C10" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="C11" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B13" s="4"/>
     </row>
   </sheetData>

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D6C054-EDE9-46D5-BFB4-ADF0401C1D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D370F352-E4E2-4A29-985C-1B2BED133DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1860" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="2805" yWindow="2295" windowWidth="25560" windowHeight="12990" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="440">
   <si>
     <t>Gene</t>
   </si>
@@ -402,9 +402,6 @@
   </si>
   <si>
     <t>STAT3</t>
-  </si>
-  <si>
-    <t>STAT5</t>
   </si>
   <si>
     <t>TET2</t>
@@ -1989,9 +1986,6 @@
     <t>Oncogene</t>
   </si>
   <si>
-    <t>Insufficient evidence to classify</t>
-  </si>
-  <si>
     <t>Mode</t>
   </si>
   <si>
@@ -2009,6 +2003,12 @@
 Multihit TP53 can be confirmed by the presence of 2 or more distinct TP53 mutations (VAF &gt; 10%) or a single TP53 mutation associated with (1) a cytogenetic deletion involving the TP53 locus at 17p13.1, (2) a VAF of &gt;49%, or (3) copy neutral loss of heterozygosity (LOH) at the 17p TP53 locus.In the absence of LOH information, the presence of a single TP53 mutation in the context of any complex karyotype is considered equivalent to a multihit TP53 (ICC 2022 and WHO 5th Edition). 
 The prognostic impact of monoallelic TP53 in MDS is currently unconfirmed (DOI: 10.1056/EVIDoa2200008).
 Please note that interpretation of these findings should be along with bone marrow morphology and other clinical/pathological features to confirm or exclude age related clonal haematopoiesis of indeterminate potential (CHIP) or any other haematological neoplasm. According to the literature, chemotherapy may select for the TP53 mutants and may lead to therapy related MDS (DOI:10.1038/nature13968).</t>
+  </si>
+  <si>
+    <t>Oncogene, tumour suppressor</t>
+  </si>
+  <si>
+    <t>Insufficient evidence</t>
   </si>
 </sst>
 </file>
@@ -2505,7 +2505,7 @@
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="126.21875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.33203125" style="5" customWidth="1"/>
     <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
@@ -2517,7 +2517,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="105.75" x14ac:dyDescent="0.25">
@@ -2525,10 +2525,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F2" s="6"/>
     </row>
@@ -2537,10 +2537,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2548,10 +2548,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2559,21 +2559,21 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2581,21 +2581,21 @@
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2603,10 +2603,10 @@
         <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
@@ -2614,10 +2614,10 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2625,10 +2625,10 @@
         <v>35</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="255" x14ac:dyDescent="0.2">
@@ -2636,10 +2636,10 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="167.25" x14ac:dyDescent="0.2">
@@ -2647,10 +2647,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2658,10 +2658,10 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.2">
@@ -2669,10 +2669,10 @@
         <v>64</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2680,10 +2680,10 @@
         <v>65</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="333" x14ac:dyDescent="0.2">
@@ -2691,10 +2691,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C17" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -2702,10 +2702,10 @@
         <v>68</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C18" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -2713,10 +2713,10 @@
         <v>69</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2724,10 +2724,10 @@
         <v>70</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C20" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -2735,10 +2735,10 @@
         <v>72</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -2746,10 +2746,10 @@
         <v>73</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2757,10 +2757,10 @@
         <v>77</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C23" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -2768,10 +2768,10 @@
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C24" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2779,10 +2779,10 @@
         <v>96</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2790,10 +2790,10 @@
         <v>79</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2801,21 +2801,21 @@
         <v>81</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C27" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C28" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="285" x14ac:dyDescent="0.2">
@@ -2823,10 +2823,10 @@
         <v>87</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C29" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2834,7 +2834,7 @@
         <v>88</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C30" t="s">
         <v>432</v>
@@ -2845,10 +2845,10 @@
         <v>90</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2856,10 +2856,10 @@
         <v>92</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C32" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -2867,10 +2867,10 @@
         <v>93</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2878,10 +2878,10 @@
         <v>94</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C34" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2889,10 +2889,10 @@
         <v>95</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C35" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="345" x14ac:dyDescent="0.2">
@@ -2900,10 +2900,10 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C36" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -2911,7 +2911,7 @@
         <v>99</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C37" t="s">
         <v>432</v>
@@ -2919,13 +2919,13 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C38" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -2933,21 +2933,21 @@
         <v>100</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -2955,10 +2955,10 @@
         <v>102</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -2966,10 +2966,10 @@
         <v>103</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C42" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2977,93 +2977,91 @@
         <v>104</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C43" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C44" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C45" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C46" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>312</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C48" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C49" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C50" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C51" t="s">
-        <v>432</v>
-      </c>
+      <c r="C51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3090,10 +3088,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3114,10 +3112,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>408</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>409</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3125,7 +3123,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3154,58 +3152,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>394</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>398</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>400</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>401</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>402</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>403</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>404</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -3235,79 +3233,79 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>385</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>387</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>388</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -3327,10 +3325,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3341,7 +3339,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>48</v>
@@ -3363,10 +3361,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3374,10 +3372,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3385,10 +3383,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="225" x14ac:dyDescent="0.2">
@@ -3396,7 +3394,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>46</v>
@@ -3432,7 +3430,7 @@
         <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3495,10 +3493,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3514,112 +3512,112 @@
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>349</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>352</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>355</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>358</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>361</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="B23" s="17" t="s">
         <v>363</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="C23" s="15" t="s">
         <v>364</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B24" s="17" t="s">
+        <v>365</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>366</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B25" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>368</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B26" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>370</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="B27" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="C27" s="15" t="s">
         <v>373</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -3630,16 +3628,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F5665B4-55C5-4810-AFEE-9F27B311E8F1}">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="110.44140625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="26" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -3647,173 +3645,172 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C2" t="s">
-        <v>432</v>
-      </c>
-      <c r="D2" s="6"/>
-    </row>
-    <row r="3" spans="1:4" ht="75" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>236</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="C4" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+        <v>199</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="C6" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+        <v>237</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="C7" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>201</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="C8" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+        <v>202</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C9" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="C10" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="C11" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C12" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="120" x14ac:dyDescent="0.2">
+        <v>206</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="C13" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="120" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="C14" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="285" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="285" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="C15" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>65</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C16" t="s">
-        <v>436</v>
+        <v>238</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3821,10 +3818,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="C17" t="s">
-        <v>433</v>
+        <v>210</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -3832,10 +3829,10 @@
         <v>68</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C18" t="s">
-        <v>432</v>
+        <v>211</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3843,10 +3840,10 @@
         <v>69</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" t="s">
-        <v>436</v>
+        <v>129</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3854,10 +3851,10 @@
         <v>70</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C20" t="s">
-        <v>433</v>
+        <v>212</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3865,10 +3862,10 @@
         <v>72</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="C21" t="s">
-        <v>433</v>
+        <v>213</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3876,18 +3873,18 @@
         <v>73</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="C22" t="s">
-        <v>433</v>
+        <v>214</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C23" t="s">
-        <v>432</v>
+      <c r="C23" s="5" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -3895,10 +3892,10 @@
         <v>77</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="C24" t="s">
-        <v>433</v>
+        <v>239</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3906,10 +3903,10 @@
         <v>78</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C25" t="s">
-        <v>433</v>
+        <v>215</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3917,10 +3914,10 @@
         <v>96</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="C26" t="s">
-        <v>433</v>
+        <v>216</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3928,10 +3925,10 @@
         <v>79</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="C27" t="s">
-        <v>433</v>
+        <v>217</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3939,21 +3936,21 @@
         <v>81</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="C28" t="s">
-        <v>433</v>
+        <v>240</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="C29" t="s">
-        <v>433</v>
+        <v>218</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3961,21 +3958,21 @@
         <v>83</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="C30" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="90" x14ac:dyDescent="0.2">
+        <v>219</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="C31" t="s">
-        <v>433</v>
+        <v>220</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3983,10 +3980,10 @@
         <v>88</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="C32" t="s">
-        <v>433</v>
+        <v>221</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3994,10 +3991,10 @@
         <v>90</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="C33" t="s">
-        <v>432</v>
+        <v>222</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4005,10 +4002,10 @@
         <v>92</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="C34" t="s">
-        <v>433</v>
+        <v>223</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4016,10 +4013,10 @@
         <v>93</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="C35" t="s">
-        <v>433</v>
+        <v>224</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="369" customHeight="1" x14ac:dyDescent="0.2">
@@ -4027,10 +4024,10 @@
         <v>94</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="C36" t="s">
-        <v>434</v>
+        <v>225</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -4038,10 +4035,10 @@
         <v>95</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="C37" t="s">
-        <v>432</v>
+        <v>241</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -4049,10 +4046,10 @@
         <v>98</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="C38" t="s">
-        <v>432</v>
+        <v>227</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4060,21 +4057,21 @@
         <v>99</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="C39" t="s">
-        <v>433</v>
+        <v>242</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="C40" t="s">
-        <v>434</v>
+        <v>228</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4082,21 +4079,21 @@
         <v>100</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="C41" t="s">
-        <v>433</v>
+        <v>229</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="C42" t="s">
-        <v>432</v>
+        <v>226</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -4104,10 +4101,10 @@
         <v>102</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="C43" t="s">
-        <v>433</v>
+        <v>230</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -4115,10 +4112,10 @@
         <v>103</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="C44" t="s">
-        <v>432</v>
+        <v>231</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4126,87 +4123,87 @@
         <v>104</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C45" t="s">
-        <v>433</v>
+        <v>232</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="C46" t="s">
-        <v>433</v>
+        <v>232</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="C47" t="s">
-        <v>432</v>
+        <v>344</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="210" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>439</v>
-      </c>
-      <c r="C48" t="s">
-        <v>432</v>
+        <v>437</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="C49" t="s">
-        <v>433</v>
+        <v>233</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>314</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C50" t="s">
-        <v>433</v>
+      <c r="C50" s="5" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="C51" t="s">
-        <v>432</v>
+        <v>234</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="C52" t="s">
-        <v>432</v>
+        <v>235</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -4216,16 +4213,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4272D003-0FFA-4F1D-B7A9-9555EFF0D62B}">
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="96.33203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="50.6640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -4233,173 +4230,172 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C2" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="285" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="285" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" t="s">
-        <v>432</v>
-      </c>
-      <c r="D3" s="6"/>
-    </row>
-    <row r="4" spans="1:4" ht="75" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C4" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="120" x14ac:dyDescent="0.2">
+      <c r="C6" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="120" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C7" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="135" x14ac:dyDescent="0.2">
+      <c r="C8" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="135" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>31</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="C10" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+        <v>162</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="270" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C12" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="150" x14ac:dyDescent="0.2">
+        <v>164</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C13" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="180" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="C14" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="135" x14ac:dyDescent="0.2">
+        <v>422</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="135" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C15" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="90" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>65</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C16" t="s">
-        <v>436</v>
+        <v>167</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4407,10 +4403,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C17" t="s">
-        <v>433</v>
+        <v>168</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4418,10 +4414,10 @@
         <v>69</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C18" t="s">
-        <v>436</v>
+        <v>169</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -4429,10 +4425,10 @@
         <v>70</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="C19" t="s">
-        <v>433</v>
+        <v>170</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -4440,10 +4436,10 @@
         <v>71</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C20" t="s">
-        <v>433</v>
+        <v>171</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4451,10 +4447,10 @@
         <v>72</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" t="s">
-        <v>433</v>
+        <v>172</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4462,10 +4458,10 @@
         <v>73</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C22" t="s">
-        <v>433</v>
+        <v>173</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -4473,10 +4469,10 @@
         <v>74</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="C23" t="s">
-        <v>432</v>
+        <v>174</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="240" x14ac:dyDescent="0.2">
@@ -4484,10 +4480,10 @@
         <v>77</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="C24" t="s">
-        <v>433</v>
+        <v>414</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
@@ -4495,10 +4491,10 @@
         <v>81</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C25" t="s">
-        <v>433</v>
+        <v>175</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4506,10 +4502,10 @@
         <v>83</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C26" t="s">
-        <v>432</v>
+        <v>176</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4517,10 +4513,10 @@
         <v>84</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C27" t="s">
-        <v>433</v>
+        <v>177</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4528,10 +4524,10 @@
         <v>87</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C28" t="s">
-        <v>433</v>
+        <v>178</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4539,10 +4535,10 @@
         <v>88</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C29" t="s">
-        <v>433</v>
+        <v>179</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -4550,10 +4546,10 @@
         <v>90</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C30" t="s">
-        <v>432</v>
+        <v>180</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4561,10 +4557,10 @@
         <v>92</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="C31" t="s">
-        <v>433</v>
+        <v>181</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4572,10 +4568,10 @@
         <v>93</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C32" t="s">
-        <v>433</v>
+        <v>182</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -4583,10 +4579,10 @@
         <v>94</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C33" t="s">
-        <v>434</v>
+        <v>183</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4594,10 +4590,10 @@
         <v>96</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C34" t="s">
-        <v>433</v>
+        <v>184</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4605,10 +4601,10 @@
         <v>79</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="C35" t="s">
-        <v>433</v>
+        <v>416</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4616,10 +4612,10 @@
         <v>78</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C36" t="s">
-        <v>433</v>
+        <v>185</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4627,10 +4623,10 @@
         <v>98</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C37" t="s">
-        <v>432</v>
+        <v>196</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4638,10 +4634,10 @@
         <v>99</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C38" t="s">
-        <v>433</v>
+        <v>197</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4649,10 +4645,10 @@
         <v>100</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C39" t="s">
-        <v>433</v>
+        <v>186</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4660,10 +4656,10 @@
         <v>101</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C40" t="s">
-        <v>432</v>
+        <v>187</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -4671,10 +4667,10 @@
         <v>102</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C41" t="s">
-        <v>433</v>
+        <v>188</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4682,10 +4678,10 @@
         <v>103</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C42" t="s">
-        <v>432</v>
+        <v>189</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4693,74 +4689,74 @@
         <v>104</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C43" t="s">
-        <v>433</v>
+        <v>190</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C44" t="s">
-        <v>433</v>
+        <v>191</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C45" t="s">
-        <v>432</v>
+        <v>192</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C46" t="s">
-        <v>432</v>
+        <v>193</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C47" t="s">
-        <v>433</v>
+        <v>194</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B48" s="4"/>
-      <c r="C48" t="s">
-        <v>432</v>
+      <c r="C48" s="5" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C49" t="s">
-        <v>432</v>
+        <v>195</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -4787,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4795,10 +4791,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4806,21 +4802,21 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C4" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4828,10 +4824,10 @@
         <v>75</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="F5" s="6"/>
     </row>
@@ -4840,10 +4836,10 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4851,21 +4847,21 @@
         <v>88</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -4892,7 +4888,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4900,10 +4896,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4911,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -4922,10 +4918,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4933,10 +4929,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -4944,10 +4940,10 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4955,21 +4951,21 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4977,10 +4973,10 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4988,10 +4984,10 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4999,10 +4995,10 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5010,10 +5006,10 @@
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5021,10 +5017,10 @@
         <v>65</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C13" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5032,10 +5028,10 @@
         <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -5043,21 +5039,21 @@
         <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C15" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>316</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C16" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5065,10 +5061,10 @@
         <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C17" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -5076,10 +5072,10 @@
         <v>96</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C18" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5087,21 +5083,21 @@
         <v>80</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C19" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C20" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -5109,10 +5105,10 @@
         <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C21" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -5120,10 +5116,10 @@
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C22" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -5131,10 +5127,10 @@
         <v>86</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C23" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -5142,76 +5138,76 @@
         <v>88</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C24" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>318</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C25" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>320</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C26" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>322</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="C27" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>324</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="C28" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>326</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C29" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="240" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C30" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -5226,7 +5222,8 @@
   <cols>
     <col min="1" max="1" width="9.6640625" style="5" customWidth="1"/>
     <col min="2" max="2" width="69.77734375" style="5" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="5"/>
+    <col min="3" max="3" width="16.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -5234,10 +5231,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5245,10 +5242,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5256,21 +5253,21 @@
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="C4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5278,10 +5275,10 @@
         <v>73</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -5289,54 +5286,54 @@
         <v>75</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>330</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>334</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>336</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5344,21 +5341,21 @@
         <v>97</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C11" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>338</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -5366,43 +5363,43 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C14" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C16" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -5427,7 +5424,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -5435,10 +5432,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -5446,10 +5443,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -5458,10 +5455,10 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
@@ -5469,10 +5466,10 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -5480,10 +5477,10 @@
         <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -5491,10 +5488,10 @@
         <v>91</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -5502,21 +5499,21 @@
         <v>100</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -5544,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5552,10 +5549,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5563,21 +5560,21 @@
         <v>64</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -5586,7 +5583,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -5594,10 +5591,10 @@
         <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="375" x14ac:dyDescent="0.2">
@@ -5605,10 +5602,10 @@
         <v>85</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="345" x14ac:dyDescent="0.2">
@@ -5616,21 +5613,21 @@
         <v>88</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>260</v>
-      </c>
       <c r="C9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -5638,10 +5635,10 @@
         <v>89</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
@@ -5649,21 +5646,21 @@
         <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C11" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="210" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="C12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -5689,7 +5686,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5697,21 +5694,21 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="C3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -5719,10 +5716,10 @@
         <v>80</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5730,10 +5727,10 @@
         <v>88</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5741,10 +5738,10 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5752,53 +5749,53 @@
         <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D370F352-E4E2-4A29-985C-1B2BED133DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3468D12-F757-47A3-9276-22185D04FCF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2805" yWindow="2295" windowWidth="25560" windowHeight="12990" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="14880" firstSheet="1" activeTab="6" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="440">
   <si>
     <t>Gene</t>
   </si>
@@ -504,12 +504,6 @@
   </si>
   <si>
     <t>JAK2 mutations are most commonly associated with myeloproliferative neoplasms and are uncommon in de novo AML  (DOI: 10.1111/bjh.15276). Their presence in AML raises the possibility of secondary AML, particularly arising from an underlying MPN, even in the absence of a documented clinical history.</t>
-  </si>
-  <si>
-    <t>KIT D816 mutations are characteristic of systemic mastocytosis and are frequently detected in systemic mastocytosis with an associated myeloid neoplasm (SM-AMN), including AML, though they may also occur in other myeloid malignancies (DOI: 10.1038/s41379-019-0447-x). In the appropriate clinical, morphologic, and immunophenotypic context, this finding should prompt consideration of SM-AMN.
-KIT exon 17 mutations have been reported in AML with CBFB::MYH11, however their prognostic significance is currently uncertain (DOI: 10.1182/bloodadvances.2019000709). 
-In AML patients with RUNX1::RUNX1T1, the presence of a KIT D816 mutation correlates with a lower relapse free survival rate (WHO 5th Edition).
-KIT mutations have been reported in AML with MECOM rearrangement and AML with NUP98 rearrangement (WHO 5th Edition).</t>
   </si>
   <si>
     <t>Activating RAS mutations are reported in approximately 10 to 15% of AML cases (DOI: 10.1002/ajh.26731). These mutations are enriched in subsets of AML, including AML with CBFB::MYH11, AML with MECOM rearrangement, AML with KMT2A rearrangement, AML with NUP98 rearrangement and AML with NPM1 (WHO 5th Edition). In patients receiving less-intensive therapy, RAS (NRAS/KRAS) mutations are associated with inferior outcomes and are placed in a less favorable risk category in ELN 2024–informed models, as they may attenuate otherwise favorable genetic features.
@@ -937,9 +931,6 @@
     <t>IDH2 mutations have been reported infrequently in MDS, please refer to the IPSS-M for prognostic indications (DOI: 10.1056/EVIDoa2200008).</t>
   </si>
   <si>
-    <t>KIT D816 mutations are strongly associated with systemic mastocytosis, but have been reported in myeloid malignancies including MDS and MDS/MPN (DOI: 10.1038/s41379-019-0447-x). Please correlate with other clinical and pathological findings for differential diagnosis and interpretation .</t>
-  </si>
-  <si>
     <t>KRAS mutations are reported in MDS, please refer to the IPSS-M for prognostic indications (DOI: 10.1056/EVIDoa2200008).
 RAS pathway mutations have been reported in cases of MDS/MPN with neutrophilia (WHO 5th Edition).</t>
   </si>
@@ -1057,28 +1048,6 @@
   <si>
     <t>BCL2 mutations are aquired in approximately 50% of CLL/SLL cases progressing on treatment with BCL2 inhibitors (including venetoclax) (WHO 5th edition). 
 *refer to BCL2 table for reportable variants*</t>
-  </si>
-  <si>
-    <t>CLL patients progressing under treatment with BTK inhibitors often show mutations of BTK (WHO 5th edition).
-Check the context for the following mutation and the treatment
-BTK G164D has been reported as a resistance mutation (DOI: 10.1002/ijc.32502).
-BTK T316A has been reported as a resistance mutation (DOI: 10.1182/bloodadvances.2016003632).
-BTK V416L is a known resistance mutation (DOI: 10.1038/s41375-024-02317-4).
-BTK A428D is a known resistance mutation that may confer resistance to multiple types of BTK inhibitors, including covalent inhibitors, non-covalent inhibitors, and potentially other BTK degraders such as NX-2127 (DOI: 10.1038/s41375-024-02317-4).
-BTK M437R is a known resistance mutation (DOI: 10.1038/s41375-024-02317-4).
-BTK T474I is a known resistance mutation reported in patients treated with pirtobrutinib (DOI: 10.1038/s41375-024-02317-4).
-BTK T474S is a known resistance mutation, particularly for acalabrutinib (DOI: 10.18632/oncotarget.11932).
-BTK C481F is a known resistance mutation (DOI: 10.1200/JCO.2016.70.2282).
-BTK C481R is a known resistance mutation (DOI: 10.1200/JCO.2016.70.2282).
-BTK C481S is a known resistance mutation, developed in patients treated with ibrutinib/acalabrutinib (DOI: 10.1038/s41375-024-02317-4).
-BTK C481Y is a known resistance mutation (DOI: 10.1182/bloodadvances.2016003632).
-BTK L528W is a known resistance mutation, more frequently associated with zanubrutinib resistance (DOI: 10.1182/blood.2024026672).
-BTK Leu528Trp has been seen in patients progressing on Zanubrutinib and may predict resistance to non-covalent/reversible BTK inhibitors such as Pirtobrutinib (DOI: 10.1182/bloodadvances.2022008325).
-BTK R544S is likely oncogenic (DOI: 10.1002/pro.321).
-The primary missense variants conferring resistance to first-generation covalent BTKis, particularly ibrutinib, are those affecting the C481 residue (C481S, C481R, C481Y, C481F) and, less frequently, L528W (DOI: 10.1182/bloodadvances.2022008325).
-The second generation of BTKis, such as acalabrutinib and zanubrutinib, are also susceptible to the C481S mutation because they, like the first-generation BTKis, bind covalently to the cysteine residue at position 481 (C481) of the BTK protein (Blood (2025) 145 (10): 1005–1009.)
-CLL Richter’s transformation:
-BTK and PLCG2 mutations may occur in Richter’s transformation patients on BTK inhibitor therapy (WHO 5th edition).</t>
   </si>
   <si>
     <t>NOTCH1 is one of the most frequently mutated genes in CLL/SLL at the time of first treatment (WHO 5th edition). NOTCH1 mutations have been associated with poorer prognsis, however their significance in the context of novel therapies remains uncertain (DOI: 10.1182/blood-2017-09-806398).</t>
@@ -1580,9 +1549,6 @@
     <t>TNFRSF14</t>
   </si>
   <si>
-    <t>TNFRSF14 variants are reported in germinal center (GC)-derived B cell lymphomas, particularly FL (DOI: 10.1182/blood-2015-10-679191).</t>
-  </si>
-  <si>
     <t>FYN</t>
   </si>
   <si>
@@ -2009,6 +1975,43 @@
   </si>
   <si>
     <t>Insufficient evidence</t>
+  </si>
+  <si>
+    <t>KIT D816 mutations are strongly associated with systemic mastocytosis, but have been reported in myeloid malignancies including MDS and MDS/MPN (DOI: 10.1038/s41379-019-0447-x). Please correlate with other clinical and pathological findings for differential diagnosis and interpretation.
+The detection of a KIT D816 mutation in combination with variants frequently reported in myeloid neoplasms may, in correlation with other clinical and pathological findings, meet the criteria for systemic mastocytosis with an associated haematological neoplasm (SM-AHN) (WHO 5th Edition).</t>
+  </si>
+  <si>
+    <t>KIT D816 mutations are characteristic of systemic mastocytosis and are frequently detected in systemic mastocytosis with an associated myeloid neoplasm (SM-AMN), including AML, though they may also occur in other myeloid malignancies (DOI: 10.1038/s41379-019-0447-x). In the appropriate clinical, morphologic, and immunophenotypic context, this finding should prompt consideration of SM-AMN.
+The detection of a KIT D816 mutation in combination with variants frequently reported in myeloid neoplasms may, in correlation with other clinical and pathological findings, meet the criteria for systemic mastocytosis with an associated haematological neoplasm (SM-AHN) (WHO 5th Edition).
+KIT exon 17 mutations have been reported in AML with CBFB::MYH11, however their prognostic significance is currently uncertain (DOI: 10.1182/bloodadvances.2019000709). 
+In AML patients with RUNX1::RUNX1T1, the presence of a KIT D816 mutation correlates with a lower relapse free survival rate (WHO 5th Edition).
+KIT mutations have been reported in AML with MECOM rearrangement and AML with NUP98 rearrangement (WHO 5th Edition).</t>
+  </si>
+  <si>
+    <t>TNFRSF14 variants are reported in germinal center (GC)-derived B cell lymphomas, particularly FL (DOI: 10.1182/blood-2015-10-679191).
+TNFRSF14 variants are frequently described in pediatric-type follicular lymphoma (PTFL) (DOI: https://doi.org/10.1182/blood-2015-12-682591).</t>
+  </si>
+  <si>
+    <t>CLL patients progressing under treatment with BTK inhibitors often show mutations of BTK (WHO 5th edition).
+Check the context for the following mutation and the treatment
+BTK G164D has been reported as a resistance mutation (DOI: 10.1002/ijc.32502).
+BTK T316A has been reported as a resistance mutation (DOI: 10.1182/bloodadvances.2016003632).
+BTK V416L is a known resistance mutation (DOI: 10.1038/s41375-024-02317-4).
+BTK A428D is a known resistance mutation that may confer resistance to multiple types of BTK inhibitors, including covalent inhibitors, non-covalent inhibitors, and potentially other BTK degraders such as NX-2127 (DOI: 10.1038/s41375-024-02317-4).
+BTK M437R is a known resistance mutation (DOI: 10.1038/s41375-024-02317-4).
+BTK T474I is a known resistance mutation reported in patients treated with pirtobrutinib (DOI: 10.1038/s41375-024-02317-4).
+BTK T474S is a known resistance mutation, particularly for acalabrutinib (DOI: 10.18632/oncotarget.11932).
+BTK C481F is a known resistance mutation (DOI: 10.1200/JCO.2016.70.2282).
+BTK C481R is a known resistance mutation (DOI: 10.1200/JCO.2016.70.2282).
+BTK C481S is a known resistance mutation, developed in patients treated with ibrutinib/acalabrutinib (DOI: 10.1038/s41375-024-02317-4).
+BTK C481Y is a known resistance mutation (DOI: 10.1182/bloodadvances.2016003632).
+BTK L528W is a known resistance mutation, more frequently associated with zanubrutinib resistance (DOI: 10.1182/blood.2024027009).
+BTK Leu528Trp has been seen in patients progressing on Zanubrutinib and may predict resistance to non-covalent/reversible BTK inhibitors such as Pirtobrutinib (DOI: 10.1182/bloodadvances.2022008325).
+BTK R544S is likely oncogenic (DOI: 10.1002/pro.321).
+The primary missense variants conferring resistance to first-generation covalent BTKis, particularly ibrutinib, are those affecting the C481 residue (C481S, C481R, C481Y, C481F) and, less frequently, L528W (DOI: 10.1182/bloodadvances.2022008325).
+The second generation of BTKis, such as acalabrutinib and zanubrutinib, are also susceptible to the C481S mutation because they, like the first-generation BTKis, bind covalently to the cysteine residue at position 481 (C481) of the BTK protein (Blood (2025) 145 (10): 1005–1009.)
+CLL Richter’s transformation:
+BTK and PLCG2 mutations may occur in Richter’s transformation patients on BTK inhibitor therapy (WHO 5th edition).</t>
   </si>
 </sst>
 </file>
@@ -2501,7 +2504,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57B5312-BC96-450F-B6E5-702AE74DB434}">
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="126.21875" style="5" customWidth="1"/>
@@ -2517,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="105.75" x14ac:dyDescent="0.25">
@@ -2528,7 +2531,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F2" s="6"/>
     </row>
@@ -2540,7 +2543,7 @@
         <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2548,10 +2551,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C4" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2562,7 +2565,7 @@
         <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -2570,10 +2573,10 @@
         <v>111</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2584,18 +2587,18 @@
         <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C8" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2606,7 +2609,7 @@
         <v>123</v>
       </c>
       <c r="C9" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
@@ -2614,10 +2617,10 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C10" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2628,7 +2631,7 @@
         <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="255" x14ac:dyDescent="0.2">
@@ -2639,7 +2642,7 @@
         <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="167.25" x14ac:dyDescent="0.2">
@@ -2647,10 +2650,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C13" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2661,7 +2664,7 @@
         <v>126</v>
       </c>
       <c r="C14" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.2">
@@ -2672,7 +2675,7 @@
         <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2683,7 +2686,7 @@
         <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="333" x14ac:dyDescent="0.2">
@@ -2691,10 +2694,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C17" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -2705,7 +2708,7 @@
         <v>128</v>
       </c>
       <c r="C18" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -2716,7 +2719,7 @@
         <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2724,10 +2727,10 @@
         <v>70</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C20" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -2735,10 +2738,10 @@
         <v>72</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C21" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -2746,10 +2749,10 @@
         <v>73</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C22" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2760,18 +2763,18 @@
         <v>130</v>
       </c>
       <c r="C23" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="150" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>131</v>
+        <v>437</v>
       </c>
       <c r="C24" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2779,10 +2782,10 @@
         <v>96</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C25" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2790,10 +2793,10 @@
         <v>79</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C26" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2801,10 +2804,10 @@
         <v>81</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -2812,10 +2815,10 @@
         <v>112</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C28" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="285" x14ac:dyDescent="0.2">
@@ -2823,10 +2826,10 @@
         <v>87</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2834,10 +2837,10 @@
         <v>88</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C30" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -2845,10 +2848,10 @@
         <v>90</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C31" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2856,10 +2859,10 @@
         <v>92</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C32" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -2867,10 +2870,10 @@
         <v>93</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C33" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2878,10 +2881,10 @@
         <v>94</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2889,10 +2892,10 @@
         <v>95</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C35" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="345" x14ac:dyDescent="0.2">
@@ -2900,10 +2903,10 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C36" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -2911,10 +2914,10 @@
         <v>99</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C37" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -2922,10 +2925,10 @@
         <v>113</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C38" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -2936,7 +2939,7 @@
         <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -2944,10 +2947,10 @@
         <v>114</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C40" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -2955,10 +2958,10 @@
         <v>102</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -2966,10 +2969,10 @@
         <v>103</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2977,10 +2980,10 @@
         <v>104</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -2988,10 +2991,10 @@
         <v>115</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C44" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -2999,10 +3002,10 @@
         <v>105</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C45" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3010,10 +3013,10 @@
         <v>106</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C46" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -3024,18 +3027,18 @@
         <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C48" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3043,10 +3046,10 @@
         <v>109</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C49" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -3057,7 +3060,7 @@
         <v>120</v>
       </c>
       <c r="C50" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -3088,10 +3091,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3112,10 +3115,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3123,7 +3126,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3152,58 +3155,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -3233,79 +3236,79 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -3325,10 +3328,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3339,7 +3342,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>48</v>
@@ -3361,10 +3364,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3372,10 +3375,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3383,10 +3386,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="225" x14ac:dyDescent="0.2">
@@ -3394,7 +3397,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>46</v>
@@ -3430,7 +3433,7 @@
         <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3493,10 +3496,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3512,112 +3515,112 @@
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>362</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>365</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -3629,7 +3632,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F5665B4-55C5-4810-AFEE-9F27B311E8F1}">
   <dimension ref="A1:C52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="110.44140625" style="8" customWidth="1"/>
@@ -3645,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3653,10 +3656,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3664,10 +3667,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3675,10 +3678,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3686,10 +3689,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3697,10 +3700,10 @@
         <v>111</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3708,10 +3711,10 @@
         <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3719,10 +3722,10 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3730,10 +3733,10 @@
         <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3741,10 +3744,10 @@
         <v>31</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3752,10 +3755,10 @@
         <v>35</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -3763,21 +3766,21 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="120" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3785,21 +3788,21 @@
         <v>40</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="285" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3807,10 +3810,10 @@
         <v>65</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3818,10 +3821,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -3829,10 +3832,10 @@
         <v>68</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3843,7 +3846,7 @@
         <v>129</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3851,10 +3854,10 @@
         <v>70</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3862,10 +3865,10 @@
         <v>72</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3873,10 +3876,10 @@
         <v>73</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3884,7 +3887,7 @@
         <v>74</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -3892,21 +3895,21 @@
         <v>77</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>215</v>
+        <v>436</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3914,10 +3917,10 @@
         <v>96</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3925,10 +3928,10 @@
         <v>79</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3936,10 +3939,10 @@
         <v>81</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3947,10 +3950,10 @@
         <v>112</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3958,21 +3961,21 @@
         <v>83</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="105" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3980,10 +3983,10 @@
         <v>88</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3991,10 +3994,10 @@
         <v>90</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4002,10 +4005,10 @@
         <v>92</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4013,10 +4016,10 @@
         <v>93</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="369" customHeight="1" x14ac:dyDescent="0.2">
@@ -4024,10 +4027,10 @@
         <v>94</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -4035,10 +4038,10 @@
         <v>95</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -4046,10 +4049,10 @@
         <v>98</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4057,10 +4060,10 @@
         <v>99</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -4068,10 +4071,10 @@
         <v>113</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4079,10 +4082,10 @@
         <v>100</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -4090,10 +4093,10 @@
         <v>114</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -4101,10 +4104,10 @@
         <v>102</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -4112,10 +4115,10 @@
         <v>103</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4123,10 +4126,10 @@
         <v>104</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4134,10 +4137,10 @@
         <v>115</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4145,10 +4148,10 @@
         <v>105</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="210" x14ac:dyDescent="0.2">
@@ -4156,10 +4159,10 @@
         <v>106</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -4167,21 +4170,21 @@
         <v>108</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -4189,10 +4192,10 @@
         <v>109</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4200,10 +4203,10 @@
         <v>110</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -4213,8 +4216,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4272D003-0FFA-4F1D-B7A9-9555EFF0D62B}">
-  <dimension ref="A1:C49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C50"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="96.33203125" style="5" customWidth="1"/>
@@ -4230,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4238,10 +4241,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="285" x14ac:dyDescent="0.2">
@@ -4249,10 +4252,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4260,10 +4263,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4271,10 +4274,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4282,10 +4285,10 @@
         <v>111</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -4293,10 +4296,10 @@
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4304,10 +4307,10 @@
         <v>116</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4315,10 +4318,10 @@
         <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4326,10 +4329,10 @@
         <v>31</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4337,10 +4340,10 @@
         <v>35</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4348,10 +4351,10 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -4359,10 +4362,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -4370,10 +4373,10 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4381,10 +4384,10 @@
         <v>64</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4392,10 +4395,10 @@
         <v>65</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4403,10 +4406,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4414,10 +4417,10 @@
         <v>69</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -4425,10 +4428,10 @@
         <v>70</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -4436,10 +4439,10 @@
         <v>71</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4447,10 +4450,10 @@
         <v>72</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4458,10 +4461,10 @@
         <v>73</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -4469,294 +4472,305 @@
         <v>74</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="105" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="240" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="240" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="C26" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="3" t="s">
+    <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="165" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" s="3" t="s">
+      <c r="C30" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="3" t="s">
+      <c r="C31" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B31" s="10" t="s">
+      <c r="C32" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="105" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="105" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B32" s="3" t="s">
+      <c r="C33" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="3" t="s">
+      <c r="C34" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="270" x14ac:dyDescent="0.2">
+      <c r="A35" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="270" x14ac:dyDescent="0.2">
-      <c r="A34" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B34" s="3" t="s">
+      <c r="C35" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A37" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
-      <c r="A37" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>196</v>
-      </c>
       <c r="C37" s="5" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="195" x14ac:dyDescent="0.2">
+      <c r="A39" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
-      <c r="A39" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="270" x14ac:dyDescent="0.2">
+      <c r="A40" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="105" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
-      <c r="A40" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B40" s="3" t="s">
+      <c r="C41" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="180" x14ac:dyDescent="0.2">
+      <c r="A42" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B41" s="3" t="s">
+      <c r="C42" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="75" x14ac:dyDescent="0.2">
+      <c r="A43" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
-      <c r="A42" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="C43" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+      <c r="A44" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
-      <c r="A43" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B43" s="3" t="s">
+      <c r="C44" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A45" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A44" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="B44" s="4" t="s">
+      <c r="C45" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B45" s="4" t="s">
+      <c r="C46" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="135" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B46" s="3" t="s">
+      <c r="C47" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" s="3" t="s">
+      <c r="C48" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="195" x14ac:dyDescent="0.2">
+      <c r="A50" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="195" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>439</v>
+      <c r="C50" s="5" t="s">
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -4767,7 +4781,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F97093D-988E-4644-B83D-8D3E695F3E69}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="68.88671875" style="4" customWidth="1"/>
@@ -4783,7 +4797,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4791,10 +4805,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4802,21 +4816,21 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C4" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4824,10 +4838,10 @@
         <v>75</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="F5" s="6"/>
     </row>
@@ -4836,10 +4850,10 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C6" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4847,10 +4861,10 @@
         <v>88</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C7" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4858,10 +4872,10 @@
         <v>106</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C8" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -4872,7 +4886,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD634E30-2FF4-4CAE-85E8-877093FDD5DC}">
   <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="99.6640625" style="4" customWidth="1"/>
@@ -4888,7 +4902,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4896,10 +4910,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4907,10 +4921,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -4918,10 +4932,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4929,10 +4943,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -4940,10 +4954,10 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C6" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4951,10 +4965,10 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C7" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4962,10 +4976,10 @@
         <v>117</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C8" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4973,10 +4987,10 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C9" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4984,10 +4998,10 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C10" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4995,10 +5009,10 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C11" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5006,10 +5020,10 @@
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C12" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5017,10 +5031,10 @@
         <v>65</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C13" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5028,10 +5042,10 @@
         <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C14" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -5039,21 +5053,21 @@
         <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C15" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C16" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5061,10 +5075,10 @@
         <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C17" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -5072,10 +5086,10 @@
         <v>96</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C18" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5083,10 +5097,10 @@
         <v>80</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C19" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5094,10 +5108,10 @@
         <v>118</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C20" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -5105,10 +5119,10 @@
         <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C21" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -5116,10 +5130,10 @@
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C22" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -5127,10 +5141,10 @@
         <v>86</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C23" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -5138,65 +5152,65 @@
         <v>88</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C24" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C25" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C26" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C27" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C28" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>327</v>
+        <v>438</v>
       </c>
       <c r="C29" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="240" x14ac:dyDescent="0.2">
@@ -5204,10 +5218,10 @@
         <v>106</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C30" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -5218,7 +5232,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F86327E5-C3AE-4491-932D-1E8E8290018D}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.6640625" style="5" customWidth="1"/>
     <col min="2" max="2" width="69.77734375" style="5" customWidth="1"/>
@@ -5231,10 +5245,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5242,10 +5256,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5253,21 +5267,21 @@
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C4" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5275,10 +5289,10 @@
         <v>73</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -5286,54 +5300,54 @@
         <v>75</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C6" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C7" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C8" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C9" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C10" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5341,21 +5355,21 @@
         <v>97</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C11" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C12" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -5363,10 +5377,10 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C13" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -5374,10 +5388,10 @@
         <v>115</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C14" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5385,21 +5399,21 @@
         <v>105</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C15" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C16" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -5424,7 +5438,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -5432,10 +5446,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -5443,10 +5457,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -5455,10 +5469,10 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C4" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
@@ -5466,10 +5480,10 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>249</v>
+        <v>439</v>
       </c>
       <c r="C5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -5477,10 +5491,10 @@
         <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C6" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -5488,10 +5502,10 @@
         <v>91</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C7" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -5499,10 +5513,10 @@
         <v>100</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C8" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
@@ -5510,10 +5524,10 @@
         <v>106</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C9" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -5525,7 +5539,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD65405E-7754-49F8-8BF9-5636ED341878}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
     <col min="2" max="2" width="112.44140625" style="5" customWidth="1"/>
@@ -5541,7 +5555,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5549,10 +5563,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5560,10 +5574,10 @@
         <v>64</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C3" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -5571,10 +5585,10 @@
         <v>119</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C4" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -5583,7 +5597,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -5591,10 +5605,10 @@
         <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C6" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="375" x14ac:dyDescent="0.2">
@@ -5602,10 +5616,10 @@
         <v>85</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C7" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="345" x14ac:dyDescent="0.2">
@@ -5613,21 +5627,21 @@
         <v>88</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C8" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C9" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -5635,10 +5649,10 @@
         <v>89</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C10" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
@@ -5646,10 +5660,10 @@
         <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C11" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="210" x14ac:dyDescent="0.2">
@@ -5660,7 +5674,7 @@
         <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -5671,7 +5685,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D047D86-2DA7-40D0-AE18-DD845C71F766}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="5" customWidth="1"/>
     <col min="2" max="2" width="75.6640625" style="5" customWidth="1"/>
@@ -5686,7 +5700,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5694,21 +5708,21 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -5716,10 +5730,10 @@
         <v>80</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C4" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5727,10 +5741,10 @@
         <v>88</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C5" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5738,10 +5752,10 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C6" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5749,53 +5763,53 @@
         <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C7" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C8" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C9" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C11" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C12" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3468D12-F757-47A3-9276-22185D04FCF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC498C4-D8BF-40C9-984D-003AAAE311C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="14880" firstSheet="1" activeTab="6" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="14880" firstSheet="1" activeTab="2" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="439">
   <si>
     <t>Gene</t>
   </si>
@@ -761,10 +761,6 @@
 KRAS mutations have been reported in MDS/MPN cases (WHO 5th Edition).
 JMML
 JMML is associated with mutations in RAS genes (KRAS 15 to 20%) or in regulators of the RAS pathway in more than 90% of cases (WHO 5th Edition). Please note that this assay cannot exclude the germline origin for the KRAS c.xxx p.(xxx) variant. Referral to clinical genetics service for family history and further assessment is recommended.</t>
-  </si>
-  <si>
-    <t>KIT mutation, particularly KITD816V, is most commonly reported in systemic mastocytosis (WHO 5th Edition).
-Detection of KIT p.D816V outside the mast cell lineage has adverse prognostic importance (WHO 5th Edition).</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -2520,7 +2516,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="105.75" x14ac:dyDescent="0.25">
@@ -2531,7 +2527,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F2" s="6"/>
     </row>
@@ -2543,7 +2539,7 @@
         <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2554,7 +2550,7 @@
         <v>143</v>
       </c>
       <c r="C4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2565,7 +2561,7 @@
         <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -2576,7 +2572,7 @@
         <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2587,18 +2583,18 @@
         <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>306</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="C8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2609,7 +2605,7 @@
         <v>123</v>
       </c>
       <c r="C9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
@@ -2617,10 +2613,10 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2631,7 +2627,7 @@
         <v>124</v>
       </c>
       <c r="C11" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="255" x14ac:dyDescent="0.2">
@@ -2642,7 +2638,7 @@
         <v>125</v>
       </c>
       <c r="C12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="167.25" x14ac:dyDescent="0.2">
@@ -2650,10 +2646,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2664,7 +2660,7 @@
         <v>126</v>
       </c>
       <c r="C14" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.2">
@@ -2675,7 +2671,7 @@
         <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2686,7 +2682,7 @@
         <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="333" x14ac:dyDescent="0.2">
@@ -2694,10 +2690,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C17" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -2708,7 +2704,7 @@
         <v>128</v>
       </c>
       <c r="C18" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -2719,7 +2715,7 @@
         <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2730,7 +2726,7 @@
         <v>145</v>
       </c>
       <c r="C20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -2738,10 +2734,10 @@
         <v>72</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C21" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -2749,10 +2745,10 @@
         <v>73</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C22" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2763,7 +2759,7 @@
         <v>130</v>
       </c>
       <c r="C23" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -2771,10 +2767,10 @@
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C24" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2785,7 +2781,7 @@
         <v>131</v>
       </c>
       <c r="C25" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2796,7 +2792,7 @@
         <v>132</v>
       </c>
       <c r="C26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2807,7 +2803,7 @@
         <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -2818,7 +2814,7 @@
         <v>134</v>
       </c>
       <c r="C28" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="285" x14ac:dyDescent="0.2">
@@ -2829,7 +2825,7 @@
         <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2840,7 +2836,7 @@
         <v>131</v>
       </c>
       <c r="C30" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -2851,7 +2847,7 @@
         <v>136</v>
       </c>
       <c r="C31" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2862,7 +2858,7 @@
         <v>146</v>
       </c>
       <c r="C32" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -2873,7 +2869,7 @@
         <v>147</v>
       </c>
       <c r="C33" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2884,7 +2880,7 @@
         <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2895,7 +2891,7 @@
         <v>148</v>
       </c>
       <c r="C35" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="345" x14ac:dyDescent="0.2">
@@ -2906,7 +2902,7 @@
         <v>138</v>
       </c>
       <c r="C36" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -2917,7 +2913,7 @@
         <v>149</v>
       </c>
       <c r="C37" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -2928,7 +2924,7 @@
         <v>150</v>
       </c>
       <c r="C38" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -2939,7 +2935,7 @@
         <v>120</v>
       </c>
       <c r="C39" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -2950,7 +2946,7 @@
         <v>151</v>
       </c>
       <c r="C40" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -2961,7 +2957,7 @@
         <v>139</v>
       </c>
       <c r="C41" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -2972,7 +2968,7 @@
         <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2983,7 +2979,7 @@
         <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -2994,7 +2990,7 @@
         <v>152</v>
       </c>
       <c r="C44" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -3005,7 +3001,7 @@
         <v>153</v>
       </c>
       <c r="C45" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3016,7 +3012,7 @@
         <v>142</v>
       </c>
       <c r="C46" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -3027,18 +3023,18 @@
         <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>308</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="C48" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3046,10 +3042,10 @@
         <v>109</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C49" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -3060,7 +3056,7 @@
         <v>120</v>
       </c>
       <c r="C50" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -3091,10 +3087,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3115,10 +3111,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>404</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3126,7 +3122,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3155,58 +3151,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>389</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>393</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>395</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>397</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>399</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -3236,79 +3232,79 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>380</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>382</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -3328,10 +3324,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3342,7 +3338,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>48</v>
@@ -3364,10 +3360,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3375,10 +3371,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3386,10 +3382,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="225" x14ac:dyDescent="0.2">
@@ -3397,7 +3393,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>46</v>
@@ -3433,7 +3429,7 @@
         <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3496,10 +3492,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3515,112 +3511,112 @@
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>343</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="C18" s="15" t="s">
         <v>344</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="C19" s="15" t="s">
         <v>347</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>350</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="C21" s="15" t="s">
         <v>353</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>355</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="C22" s="15" t="s">
         <v>356</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="B23" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="C23" s="15" t="s">
         <v>359</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B24" s="17" t="s">
+        <v>360</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>361</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B25" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>363</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B26" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>365</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="B27" s="17" t="s">
         <v>367</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="C27" s="15" t="s">
         <v>368</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -3648,7 +3644,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3656,10 +3652,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3667,10 +3663,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3678,10 +3674,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3689,10 +3685,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3700,10 +3696,10 @@
         <v>111</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3711,10 +3707,10 @@
         <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3722,10 +3718,10 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3733,10 +3729,10 @@
         <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3744,10 +3740,10 @@
         <v>31</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3755,10 +3751,10 @@
         <v>35</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -3766,10 +3762,10 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -3777,10 +3773,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3788,10 +3784,10 @@
         <v>40</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -3799,10 +3795,10 @@
         <v>64</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3810,10 +3806,10 @@
         <v>65</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3821,10 +3817,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -3832,10 +3828,10 @@
         <v>68</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3846,7 +3842,7 @@
         <v>129</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3854,10 +3850,10 @@
         <v>70</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3865,10 +3861,10 @@
         <v>72</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3876,10 +3872,10 @@
         <v>73</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3887,7 +3883,7 @@
         <v>74</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -3895,10 +3891,10 @@
         <v>77</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -3906,10 +3902,10 @@
         <v>78</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3917,10 +3913,10 @@
         <v>96</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3928,10 +3924,10 @@
         <v>79</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3939,10 +3935,10 @@
         <v>81</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3950,10 +3946,10 @@
         <v>112</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3961,10 +3957,10 @@
         <v>83</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -3972,10 +3968,10 @@
         <v>87</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3983,10 +3979,10 @@
         <v>88</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3994,10 +3990,10 @@
         <v>90</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4005,10 +4001,10 @@
         <v>92</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4016,10 +4012,10 @@
         <v>93</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="369" customHeight="1" x14ac:dyDescent="0.2">
@@ -4027,10 +4023,10 @@
         <v>94</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -4038,10 +4034,10 @@
         <v>95</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -4049,10 +4045,10 @@
         <v>98</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4060,10 +4056,10 @@
         <v>99</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -4071,10 +4067,10 @@
         <v>113</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4082,10 +4078,10 @@
         <v>100</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -4093,10 +4089,10 @@
         <v>114</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -4104,10 +4100,10 @@
         <v>102</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -4115,10 +4111,10 @@
         <v>103</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4126,10 +4122,10 @@
         <v>104</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4137,10 +4133,10 @@
         <v>115</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4148,10 +4144,10 @@
         <v>105</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="210" x14ac:dyDescent="0.2">
@@ -4159,10 +4155,10 @@
         <v>106</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -4170,21 +4166,21 @@
         <v>108</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>310</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C50" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -4192,10 +4188,10 @@
         <v>109</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4203,10 +4199,10 @@
         <v>110</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
@@ -4216,7 +4212,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4272D003-0FFA-4F1D-B7A9-9555EFF0D62B}">
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
@@ -4233,7 +4229,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4244,7 +4240,7 @@
         <v>154</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="285" x14ac:dyDescent="0.2">
@@ -4255,7 +4251,7 @@
         <v>164</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4266,7 +4262,7 @@
         <v>155</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4277,7 +4273,7 @@
         <v>156</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4288,7 +4284,7 @@
         <v>157</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -4299,7 +4295,7 @@
         <v>158</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4310,7 +4306,7 @@
         <v>159</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4321,7 +4317,7 @@
         <v>160</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4332,7 +4328,7 @@
         <v>161</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4343,7 +4339,7 @@
         <v>162</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4354,7 +4350,7 @@
         <v>163</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -4362,10 +4358,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -4373,10 +4369,10 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4387,7 +4383,7 @@
         <v>165</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4398,7 +4394,7 @@
         <v>166</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4409,7 +4405,7 @@
         <v>167</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4420,7 +4416,7 @@
         <v>168</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -4431,7 +4427,7 @@
         <v>169</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -4442,7 +4438,7 @@
         <v>170</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4453,7 +4449,7 @@
         <v>171</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4464,7 +4460,7 @@
         <v>172</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -4475,29 +4471,29 @@
         <v>173</v>
       </c>
       <c r="C23" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="240" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="105" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="240" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>410</v>
-      </c>
       <c r="C25" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
@@ -4508,7 +4504,7 @@
         <v>174</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4519,7 +4515,7 @@
         <v>175</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4530,7 +4526,7 @@
         <v>176</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4541,7 +4537,7 @@
         <v>177</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4552,7 +4548,7 @@
         <v>178</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -4563,7 +4559,7 @@
         <v>179</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4574,7 +4570,7 @@
         <v>180</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4585,7 +4581,7 @@
         <v>181</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -4596,7 +4592,7 @@
         <v>182</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4607,7 +4603,7 @@
         <v>183</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -4615,26 +4611,26 @@
         <v>79</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>184</v>
+        <v>98</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>195</v>
@@ -4643,53 +4639,53 @@
         <v>427</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="195" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="270" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>185</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="105" x14ac:dyDescent="0.2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>186</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="180" x14ac:dyDescent="0.2">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>187</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="75" x14ac:dyDescent="0.2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>188</v>
@@ -4698,42 +4694,42 @@
         <v>427</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B44" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>189</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B46" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>191</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="135" x14ac:dyDescent="0.2">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>192</v>
@@ -4742,35 +4738,24 @@
         <v>427</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="45" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B48" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="5" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="195" x14ac:dyDescent="0.2">
+      <c r="A49" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B49" s="4"/>
       <c r="C49" s="5" t="s">
         <v>434</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="195" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -4797,7 +4782,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4805,10 +4790,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4816,21 +4801,21 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="C4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4838,10 +4823,10 @@
         <v>75</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F5" s="6"/>
     </row>
@@ -4850,10 +4835,10 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4861,10 +4846,10 @@
         <v>88</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4872,10 +4857,10 @@
         <v>106</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -4902,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4910,10 +4895,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4921,10 +4906,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -4932,10 +4917,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4943,10 +4928,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -4954,10 +4939,10 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4965,10 +4950,10 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4976,10 +4961,10 @@
         <v>117</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4987,10 +4972,10 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4998,10 +4983,10 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5009,10 +4994,10 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C11" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5020,10 +5005,10 @@
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5031,10 +5016,10 @@
         <v>65</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5042,10 +5027,10 @@
         <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C14" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -5053,21 +5038,21 @@
         <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>312</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="C16" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5075,10 +5060,10 @@
         <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C17" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -5086,10 +5071,10 @@
         <v>96</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5097,10 +5082,10 @@
         <v>80</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C19" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5108,10 +5093,10 @@
         <v>118</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -5119,10 +5104,10 @@
         <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C21" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -5130,10 +5115,10 @@
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C22" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -5141,10 +5126,10 @@
         <v>86</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C23" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -5152,65 +5137,65 @@
         <v>88</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C24" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>314</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C25" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>316</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>318</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="C27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>320</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C28" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C29" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="240" x14ac:dyDescent="0.2">
@@ -5218,10 +5203,10 @@
         <v>106</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C30" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -5245,10 +5230,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5256,10 +5241,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5267,21 +5252,21 @@
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5289,10 +5274,10 @@
         <v>73</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -5300,54 +5285,54 @@
         <v>75</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>329</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="C10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5355,21 +5340,21 @@
         <v>97</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C11" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -5377,10 +5362,10 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C13" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -5388,10 +5373,10 @@
         <v>115</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C14" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5399,21 +5384,21 @@
         <v>105</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C15" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C16" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -5438,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -5446,10 +5431,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -5457,10 +5442,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -5469,10 +5454,10 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
@@ -5480,10 +5465,10 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -5491,10 +5476,10 @@
         <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -5502,10 +5487,10 @@
         <v>91</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -5513,10 +5498,10 @@
         <v>100</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
@@ -5524,10 +5509,10 @@
         <v>106</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -5555,7 +5540,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5563,10 +5548,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5574,10 +5559,10 @@
         <v>64</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -5585,10 +5570,10 @@
         <v>119</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -5597,7 +5582,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -5605,10 +5590,10 @@
         <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="375" x14ac:dyDescent="0.2">
@@ -5616,10 +5601,10 @@
         <v>85</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="345" x14ac:dyDescent="0.2">
@@ -5627,21 +5612,21 @@
         <v>88</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="225" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>256</v>
-      </c>
       <c r="C9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -5649,10 +5634,10 @@
         <v>89</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
@@ -5660,10 +5645,10 @@
         <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C11" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="210" x14ac:dyDescent="0.2">
@@ -5674,7 +5659,7 @@
         <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -5700,7 +5685,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5708,21 +5693,21 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -5730,10 +5715,10 @@
         <v>80</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5741,10 +5726,10 @@
         <v>88</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5752,10 +5737,10 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5763,53 +5748,53 @@
         <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC498C4-D8BF-40C9-984D-003AAAE311C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCFA806-2CE0-4AC8-99B0-4DFCF2620C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="14880" firstSheet="1" activeTab="2" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="29070" yWindow="1410" windowWidth="26115" windowHeight="12570" firstSheet="1" activeTab="7" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -410,12 +410,6 @@
     <t>TP53</t>
   </si>
   <si>
-    <t>Paediatric ALL
-TP53 mutations are infrequent (2% to 3%) at initial diagnosis and have not been found to be an important marker for prognosis or in the prediction of treatment response in most childhood ALL clinical trials. (Blood. 2011; 118:30807, Blood. 1993; 82:3163). However, TP53 alterations are frequently found in low hypodiploidy ALL, with a somatic mutation rate of up to 90%. The incidence of TP53 alterations is higher in relapsed childhood ALL samples than in diagnostic samples. At relapse, alterations of TP53 have been observed in 12.4% of patients with B cell precursor ALL and 6.4% of patients with T-cell ALL (J Clin Oncol. 2011 Aug 10;29(23):3185-93)
-Adolescent ALL
-Overall TP53 mutation incidence in ALL is 15.7%. TP53 mutations were observed to be most frequent in ALL with low hypodiploidy or MYC rearrangements. For a large number of ALL patients with TP53 mutation, both TP53 alleles were altered, either by two mutations or by one TP53 mutation and a TP53 deletion in the second allele. A high TP53 mutation load has been shown to be correlated to low hypodiploidy, high hyperdiploidy, and a complex karyotype. The median overall survival has been shown to be significantly shorter in patients with TP53 mutation compared with patients with wildtype TP53 and this is especially pronounced when both TP53 alleles are affected (Blood. 2014,124(2):251_258).</t>
-  </si>
-  <si>
     <t>U2AF1</t>
   </si>
   <si>
@@ -1074,22 +1068,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">B ALL with PAX5 p.P80R is a defined B lymphoblastic leukaemia/lymphoma class according to 2022 WHO classification. 
-The PAX5 P80R subtype presents in 3 to 4% of paediatric and 4% of adults B ALL and is associated with intermediate prognosis. Structural rearrangements of chromosomal arms 9p and/or 7p (please correlate with cytogenetics results) as well as secondary mutations in signalling pathway genes are often observed. Signalling pathway mutations (Ras and JAK/STAT pathways, FLT3, BRAF and PIK3CA) are present in almost all PAX5 P80R cases. PAX5 p.P80R mutations appear mutually exclusive and are not reported in other B ALL subtypes (WHO 5th edition). Please notice the risk classification of the PAX5 P80R patients should be in correlation with cytogenetics and PanCancer fusion result as it might change in the presence of other markers with higher risk.                                                                                                                          Other PAX5 alterations, including gene rearrangements, non-p.P80R sequence mutations, or focal intragenic amplifications, should be classified as B-ALL/LBL with PAX5alt, with the exception of PAX5::JAK2 (Philadelphia [Ph] chromosome–like B-ALL) and PAX5::ZCCHC7, which occurs in cases with other class-defining alterations (WHO 5th Edition).
-</t>
-  </si>
-  <si>
     <t>PTEN</t>
-  </si>
-  <si>
-    <t>T-lymphoblastic leukaemia / lymphoma, NOS
-NOTCH1 and/or FBXW7 mutations have been associated with better clinical outcomes, while loss of heterozygosity at 6q, PTEN mutations, and KMT2D mutations have been associated with worse outcomes (Blood. 2021 Apr 29,137(17):2347_2359.).
-adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
-The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009 )
-adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
-The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
-Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
-Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).</t>
   </si>
   <si>
     <t>ERBB3</t>
@@ -1831,29 +1810,6 @@
     <t>KMT2A alterations have been reported rarely in MPN cases (DOI: 10.1182/blood-2019-128764).</t>
   </si>
   <si>
-    <t>T-ALL
-Loss of function mutations in FBXW7, a negative regulator of NOTCH1 have been reported in 30% of cases. NOTCH1 and/or FBXW7 mutations have been associated with better clinical outcomes, while loss of heterozygosity at 6q, PTEN mutations, and KMT2D mutations have been associated with worse outcomes (WHO 5th edition) (Blood. 2021 Apr 29,137(17):2347_2359.).
-This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
-adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
-The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009 )
-adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
-The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
-Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
-Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).</t>
-  </si>
-  <si>
-    <t>T-lymphoblastic leukaemia / lymphoma, NOS
-NOTCH1 variants may contribute to signalling pathway dysregulation in T-ALL. Over 75% of cases show NOTCH1 pathway activation, which can be caused by activating mutations involving the extracellular heterodimerization domain and / or the C terminal PEST domain of NOTCH1 (50% of cases) and/or by loss of function mutations in FBXW7, a negative regulator of NOTCH1 (30% of cases). NOTCH1 and/or FBXW7 mutations have been associated with better clinical outcomes, while loss of heterozygosity at 6q, PTEN mutations, and KMT2D mutations have been associated with worse outcomes (WHO 5th edition).
-NOTCH1 and/or FBXW7 mutations have been associated with better clinical outcomes, while loss of heterozygosity at 6q, PTEN mutations, and KMT2D mutations have been associated with worse outcomes (Blood. 2021 Apr 29,137(17):2347_2359.).
-This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
-adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
-The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009)
-adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
-The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
-Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
-Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).</t>
-  </si>
-  <si>
     <t>Unfortunately the NGS analysis failed. Please send a repeat sample, if possible.</t>
   </si>
   <si>
@@ -1873,44 +1829,6 @@
 For reporting purposes:
 Old - ETNK1 N244S (ENST00000671733.1)
 New - ETNK1 c.724A&gt;G p.Asn155Ser (ENST00000266517.9) (NM_018638.5)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRAS variants are reported in ALL (WHO 5th Edition).
-B-ALL
-KRAS and NRAS mutations have been associated or reported in B ALL and their prognostic significance  is influenced by the subtype; therefore, it should be interpreted in the context of the B ALL subtype. Please correlate with cytogenetics results for interpretation. 
-T-lymphoblastic leukaemia / lymphoma, NOS
-This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
-adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
-The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009 )
-adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
-The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
-Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
-Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRAS variants are reported in ALL (WHO 5th Edition).
-B-ALL
-KRAS and NRAS mutations have been associated or reported in B ALL and their prognostic significance  is influenced by the subtype; therefore, it should be interpreted in the context of the B ALL subtype. Please correlate with cytogenetics results for interpretation. 
-T-lymphoblastic leukaemia / lymphoma, NOS
-This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
-adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
-The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009 )
-adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
-The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
-Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
-Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).
-B-ALL
-KRAS and NRAS mutations have been associated or reported in B ALL and their prognostic significance  is influenced by the subtype; therefore, it should be interpreted in the context of the B ALL subtype. Please correlate with cytogenetics results for interpretation. 
-T-lymphoblastic leukaemia / lymphoma, NOS
-This analysis of the paediatric and adult T-ALL from the GRAALL-2003/2005 trials and FRALLE2000T trial proposes categorizing patients with NOTCH1 and/or FBXW7, PHF6, or EP300 mutations, excluding N-K-RAS, PI3K pathway, TP53, DNMT3A, IDH1/2, and IKZF1 alterations as low risk (Blood. 2024 Jun 7: blood.2023023754.) 
-adult T-ALL; NOTCH1 ± FBXW7 but no RAS/PTEN mutations:
-The presence of NOTCH1 heterodimerisation domain ± FBXW7 in the absence of RAS/PTEN abnormalities predicts good outcome in adult T ALL (Trinquand A et al GRAALL Study JCO 2013, Mansour M  et al UKALLXII/ECOG Study JCO 2009 )
-adult T-ALL; RAS/PTEN mutations but no NOTCH1±FBXW7 mutations:
-The presence of RAS/PTEN alterations and absence of NOTCH1 ± FBXW7 in adult T ALL patients has been associated with poor prognosis (Trinquand A et al GRAALL Study JCO 2013)
-Paediatric T-ALL; NOTCH1/FBXW7 double mutation:
-Double NOTCH1 mutated+FBXW7 wildtype or NOTCH1 mutated+FBXW7 mutated, irrespective of RAS/PTEN mutation status in paediatric T ALL, is associated with good prognosis (Jenkinson S et al MRC UK2003 Study Leukemia 2016).
 </t>
   </si>
   <si>
@@ -2008,6 +1926,32 @@
 The second generation of BTKis, such as acalabrutinib and zanubrutinib, are also susceptible to the C481S mutation because they, like the first-generation BTKis, bind covalently to the cysteine residue at position 481 (C481) of the BTK protein (Blood (2025) 145 (10): 1005–1009.)
 CLL Richter’s transformation:
 BTK and PLCG2 mutations may occur in Richter’s transformation patients on BTK inhibitor therapy (WHO 5th edition).</t>
+  </si>
+  <si>
+    <t>Loss of function FBXW7 variants are frequently reported in T-ALL with prognostic associations reported in some literature. Please correlate with other clinical and pathological findings and interpret in accordance with the current clinical guidelines.</t>
+  </si>
+  <si>
+    <t>NOTCH1 abberations are frequently reported in T-ALL, their prognostic significance must be interpreted in the context of other clinical and pathological findings and the current clinical guidelines.</t>
+  </si>
+  <si>
+    <t>NRAS mutations have been reported in B-ALL; their prognostic significance  is influenced by the subtype and therefore must be interpreted in the context of other clinical and pathological data.</t>
+  </si>
+  <si>
+    <t>PTEN variants are frequently reported in T-ALL with prognostic associations reported in some literature. Please correlate with other clinical and pathological findings and interpret in accordance with the current clinical guidelines.</t>
+  </si>
+  <si>
+    <t>***Check for fusions, these override classifcation***
+B-ALL with PAX5 p.P80R is a defined B lymphoblastic leukaemia/lymphoma class according to the WHO 5th Edition.  Signalling pathway mutations (Ras and JAK/STAT pathways, FLT3, BRAF and PIK3CA) are present in almost all PAX5 P80R cases. Mutations of the second PAX5 allele, via loss of heterozygosity or an additional PAX5 mutation, are present in nearly all cases. The prognostic significance must be interpreted in the context of other clinical and pathological findings.
+B-ALL with PAX5alt is a defined B lymphoblastic leukaemia/lymphoma class according to the WHO 5th Edition. This category includes intragenic amplifications, rearrangements and mutations other than p.P80R. The prognostic significance must be interpreted in the context of other clinical and pathological findings.</t>
+  </si>
+  <si>
+    <t>KRAS mutations have been reported in B-ALL; their prognostic significance  is influenced by the B-ALL subtype and therefore should be interpreted in the context of other clinical and pathological data.</t>
+  </si>
+  <si>
+    <t>Paediatric ALL
+TP53 mutations are infrequent (2% to 3%) at initial diagnosis (Blood. 2011; 118:30807, Blood. 1993; 82:3163). However, TP53 alterations are frequently found in low hypodiploidy ALL, with a somatic mutation rate of up to 90%. The incidence of TP53 alterations is higher in relapsed childhood ALL samples than in diagnostic samples. At relapse, alterations of TP53 have been observed in 12.4% of patients with B cell precursor ALL and 6.4% of patients with T-cell ALL (J Clin Oncol. 2011 Aug 10;29(23):3185-93)
+Adolescent ALL
+Overall TP53 mutation incidence in adolescent ALL is 15.7%. TP53 mutations were observed to be most frequent in ALL with low hypodiploidy or MYC rearrangements. For a large number of ALL patients with TP53 mutation, both TP53 alleles were altered, either by two mutations or by one TP53 mutation and a TP53 deletion in the second allele. A high TP53 mutation load has been shown to be correlated to low hypodiploidy, high hyperdiploidy, and a complex karyotype (Blood. 2014,124(2):251_258).</t>
   </si>
 </sst>
 </file>
@@ -2516,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="105.75" x14ac:dyDescent="0.25">
@@ -2524,10 +2468,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="F2" s="6"/>
     </row>
@@ -2536,10 +2480,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2547,10 +2491,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2558,21 +2502,21 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2580,21 +2524,21 @@
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C8" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2602,10 +2546,10 @@
         <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
@@ -2613,10 +2557,10 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C10" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2624,10 +2568,10 @@
         <v>35</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="255" x14ac:dyDescent="0.2">
@@ -2635,10 +2579,10 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="167.25" x14ac:dyDescent="0.2">
@@ -2646,10 +2590,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C13" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2657,10 +2601,10 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.2">
@@ -2668,10 +2612,10 @@
         <v>64</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C15" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2679,10 +2623,10 @@
         <v>65</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="333" x14ac:dyDescent="0.2">
@@ -2690,10 +2634,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C17" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -2701,10 +2645,10 @@
         <v>68</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -2712,10 +2656,10 @@
         <v>69</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2723,10 +2667,10 @@
         <v>70</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C20" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -2734,10 +2678,10 @@
         <v>72</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C21" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -2745,10 +2689,10 @@
         <v>73</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="C22" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2756,10 +2700,10 @@
         <v>77</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C23" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -2767,10 +2711,10 @@
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C24" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2778,10 +2722,10 @@
         <v>96</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C25" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2789,10 +2733,10 @@
         <v>79</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C26" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2800,21 +2744,21 @@
         <v>81</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C27" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="285" x14ac:dyDescent="0.2">
@@ -2822,10 +2766,10 @@
         <v>87</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C29" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2833,10 +2777,10 @@
         <v>88</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -2844,10 +2788,10 @@
         <v>90</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C31" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2855,10 +2799,10 @@
         <v>92</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -2866,10 +2810,10 @@
         <v>93</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2877,10 +2821,10 @@
         <v>94</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C34" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2888,10 +2832,10 @@
         <v>95</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C35" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="345" x14ac:dyDescent="0.2">
@@ -2899,10 +2843,10 @@
         <v>98</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C36" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -2910,21 +2854,21 @@
         <v>99</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C37" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C38" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -2932,21 +2876,21 @@
         <v>100</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C40" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -2954,10 +2898,10 @@
         <v>102</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -2965,10 +2909,10 @@
         <v>103</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2976,21 +2920,21 @@
         <v>104</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C43" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C44" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -2998,10 +2942,10 @@
         <v>105</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C45" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3009,54 +2953,54 @@
         <v>106</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C47" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C48" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C49" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C50" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -3087,10 +3031,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3111,10 +3055,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3122,7 +3066,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3151,58 +3095,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -3232,79 +3176,79 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -3324,10 +3268,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3338,7 +3282,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>48</v>
@@ -3360,10 +3304,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3371,10 +3315,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3382,10 +3326,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="225" x14ac:dyDescent="0.2">
@@ -3393,7 +3337,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>46</v>
@@ -3429,7 +3373,7 @@
         <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3492,10 +3436,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3511,112 +3455,112 @@
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
+        <v>354</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>357</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>360</v>
-      </c>
       <c r="C24" s="15" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -3644,7 +3588,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3652,10 +3596,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3663,10 +3607,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3674,10 +3618,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3685,21 +3629,21 @@
         <v>7</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3707,10 +3651,10 @@
         <v>27</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3718,10 +3662,10 @@
         <v>28</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3729,10 +3673,10 @@
         <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3740,10 +3684,10 @@
         <v>31</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3751,10 +3695,10 @@
         <v>35</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -3762,10 +3706,10 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -3773,10 +3717,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3784,10 +3728,10 @@
         <v>40</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -3795,10 +3739,10 @@
         <v>64</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3806,10 +3750,10 @@
         <v>65</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3817,10 +3761,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -3828,10 +3772,10 @@
         <v>68</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3839,10 +3783,10 @@
         <v>69</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3850,10 +3794,10 @@
         <v>70</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3861,10 +3805,10 @@
         <v>72</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3872,10 +3816,10 @@
         <v>73</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3883,7 +3827,7 @@
         <v>74</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -3891,10 +3835,10 @@
         <v>77</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -3902,10 +3846,10 @@
         <v>78</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3913,10 +3857,10 @@
         <v>96</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3924,10 +3868,10 @@
         <v>79</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3935,21 +3879,21 @@
         <v>81</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3957,10 +3901,10 @@
         <v>83</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -3968,10 +3912,10 @@
         <v>87</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3979,10 +3923,10 @@
         <v>88</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3990,10 +3934,10 @@
         <v>90</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4001,10 +3945,10 @@
         <v>92</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -4012,10 +3956,10 @@
         <v>93</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="369" customHeight="1" x14ac:dyDescent="0.2">
@@ -4023,10 +3967,10 @@
         <v>94</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -4034,10 +3978,10 @@
         <v>95</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -4045,10 +3989,10 @@
         <v>98</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4056,21 +4000,21 @@
         <v>99</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4078,21 +4022,21 @@
         <v>100</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -4100,10 +4044,10 @@
         <v>102</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -4111,10 +4055,10 @@
         <v>103</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4122,21 +4066,21 @@
         <v>104</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4144,10 +4088,10 @@
         <v>105</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="210" x14ac:dyDescent="0.2">
@@ -4155,54 +4099,54 @@
         <v>106</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -4229,7 +4173,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4237,10 +4181,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="285" x14ac:dyDescent="0.2">
@@ -4248,10 +4192,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4259,10 +4203,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4270,21 +4214,21 @@
         <v>7</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -4292,21 +4236,21 @@
         <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4314,10 +4258,10 @@
         <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4325,10 +4269,10 @@
         <v>31</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4336,10 +4280,10 @@
         <v>35</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4347,10 +4291,10 @@
         <v>36</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -4358,10 +4302,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -4369,10 +4313,10 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4380,10 +4324,10 @@
         <v>64</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4391,10 +4335,10 @@
         <v>65</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4402,10 +4346,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4413,10 +4357,10 @@
         <v>69</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -4424,10 +4368,10 @@
         <v>70</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -4435,10 +4379,10 @@
         <v>71</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4446,10 +4390,10 @@
         <v>72</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4457,10 +4401,10 @@
         <v>73</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -4468,10 +4412,10 @@
         <v>74</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="240" x14ac:dyDescent="0.2">
@@ -4479,10 +4423,10 @@
         <v>77</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4490,10 +4434,10 @@
         <v>78</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
@@ -4501,10 +4445,10 @@
         <v>81</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4512,10 +4456,10 @@
         <v>83</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4523,10 +4467,10 @@
         <v>84</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4534,10 +4478,10 @@
         <v>87</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4545,10 +4489,10 @@
         <v>88</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -4556,10 +4500,10 @@
         <v>90</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4567,10 +4511,10 @@
         <v>92</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4578,10 +4522,10 @@
         <v>93</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -4589,10 +4533,10 @@
         <v>94</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4600,10 +4544,10 @@
         <v>96</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -4611,10 +4555,10 @@
         <v>79</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4622,10 +4566,10 @@
         <v>98</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4633,10 +4577,10 @@
         <v>99</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4644,10 +4588,10 @@
         <v>100</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4655,10 +4599,10 @@
         <v>101</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -4666,10 +4610,10 @@
         <v>102</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4677,10 +4621,10 @@
         <v>103</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4688,21 +4632,21 @@
         <v>104</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4710,10 +4654,10 @@
         <v>105</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4721,41 +4665,41 @@
         <v>106</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="195" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -4782,7 +4726,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4790,10 +4734,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4801,21 +4745,21 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C3" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C4" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4823,10 +4767,10 @@
         <v>75</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="F5" s="6"/>
     </row>
@@ -4835,10 +4779,10 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C6" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4846,10 +4790,10 @@
         <v>88</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C7" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4857,10 +4801,10 @@
         <v>106</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C8" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -4887,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4895,10 +4839,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4906,10 +4850,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C3" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -4917,10 +4861,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C4" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4928,10 +4872,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -4939,10 +4883,10 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C6" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4950,21 +4894,21 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C7" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C8" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4972,10 +4916,10 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C9" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4983,10 +4927,10 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C10" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4994,10 +4938,10 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C11" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5005,10 +4949,10 @@
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C12" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5016,10 +4960,10 @@
         <v>65</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C13" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5027,10 +4971,10 @@
         <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C14" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -5038,21 +4982,21 @@
         <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C15" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C16" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5060,10 +5004,10 @@
         <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C17" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -5071,10 +5015,10 @@
         <v>96</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C18" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5082,21 +5026,21 @@
         <v>80</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C19" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C20" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -5104,10 +5048,10 @@
         <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="C21" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -5115,10 +5059,10 @@
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C22" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -5126,10 +5070,10 @@
         <v>86</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C23" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -5137,65 +5081,65 @@
         <v>88</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C24" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C25" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C26" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C27" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C28" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="C29" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="240" x14ac:dyDescent="0.2">
@@ -5203,10 +5147,10 @@
         <v>106</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C30" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -5230,10 +5174,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5241,10 +5185,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5252,21 +5196,21 @@
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C3" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C4" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5274,10 +5218,10 @@
         <v>73</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -5285,54 +5229,54 @@
         <v>75</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C6" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C7" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C8" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C9" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C10" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5340,21 +5284,21 @@
         <v>97</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C11" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C12" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -5362,21 +5306,21 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C13" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C14" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5384,21 +5328,21 @@
         <v>105</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C15" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C16" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -5423,7 +5367,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -5431,10 +5375,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C2" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -5442,10 +5386,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -5454,10 +5398,10 @@
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C4" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
@@ -5465,10 +5409,10 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="C5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -5476,10 +5420,10 @@
         <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C6" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -5487,10 +5431,10 @@
         <v>91</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C7" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -5498,10 +5442,10 @@
         <v>100</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C8" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
@@ -5509,10 +5453,10 @@
         <v>106</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C9" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -5540,7 +5484,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5548,10 +5492,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5559,21 +5503,21 @@
         <v>64</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C3" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="270" x14ac:dyDescent="0.2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>412</v>
+        <v>118</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>432</v>
       </c>
       <c r="C4" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -5582,7 +5526,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -5590,76 +5534,76 @@
         <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C6" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="375" x14ac:dyDescent="0.2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>413</v>
+      <c r="B7" s="4" t="s">
+        <v>433</v>
       </c>
       <c r="C7" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="345" x14ac:dyDescent="0.2">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>418</v>
+      <c r="B8" s="4" t="s">
+        <v>434</v>
       </c>
       <c r="C8" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="225" x14ac:dyDescent="0.2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>435</v>
       </c>
       <c r="C9" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="180" x14ac:dyDescent="0.2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="150" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>89</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>253</v>
+        <v>436</v>
       </c>
       <c r="C10" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>419</v>
+      <c r="B11" s="4" t="s">
+        <v>437</v>
       </c>
       <c r="C11" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="210" x14ac:dyDescent="0.2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="165" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>106</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="C12" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -5685,7 +5629,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5693,21 +5637,21 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -5715,10 +5659,10 @@
         <v>80</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5726,10 +5670,10 @@
         <v>88</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5737,10 +5681,10 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C6" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5748,53 +5692,53 @@
         <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C7" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C8" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C9" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C10" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C11" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C12" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBCFA806-2CE0-4AC8-99B0-4DFCF2620C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63351A8E-BECB-4690-B03C-ABABE7797E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29070" yWindow="1410" windowWidth="26115" windowHeight="12570" firstSheet="1" activeTab="7" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="960" yWindow="1365" windowWidth="25170" windowHeight="13965" firstSheet="1" activeTab="7" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -1945,13 +1945,14 @@
 B-ALL with PAX5alt is a defined B lymphoblastic leukaemia/lymphoma class according to the WHO 5th Edition. This category includes intragenic amplifications, rearrangements and mutations other than p.P80R. The prognostic significance must be interpreted in the context of other clinical and pathological findings.</t>
   </si>
   <si>
-    <t>KRAS mutations have been reported in B-ALL; their prognostic significance  is influenced by the B-ALL subtype and therefore should be interpreted in the context of other clinical and pathological data.</t>
-  </si>
-  <si>
     <t>Paediatric ALL
 TP53 mutations are infrequent (2% to 3%) at initial diagnosis (Blood. 2011; 118:30807, Blood. 1993; 82:3163). However, TP53 alterations are frequently found in low hypodiploidy ALL, with a somatic mutation rate of up to 90%. The incidence of TP53 alterations is higher in relapsed childhood ALL samples than in diagnostic samples. At relapse, alterations of TP53 have been observed in 12.4% of patients with B cell precursor ALL and 6.4% of patients with T-cell ALL (J Clin Oncol. 2011 Aug 10;29(23):3185-93)
 Adolescent ALL
 Overall TP53 mutation incidence in adolescent ALL is 15.7%. TP53 mutations were observed to be most frequent in ALL with low hypodiploidy or MYC rearrangements. For a large number of ALL patients with TP53 mutation, both TP53 alleles were altered, either by two mutations or by one TP53 mutation and a TP53 deletion in the second allele. A high TP53 mutation load has been shown to be correlated to low hypodiploidy, high hyperdiploidy, and a complex karyotype (Blood. 2014,124(2):251_258).</t>
+  </si>
+  <si>
+    <t>KRAS mutations have been reported in B-ALL; their prognostic significance  is influenced by the B-ALL subtype and therefore should be interpreted in the context of other clinical and pathological data.
+KRAS mutations have been reported in T-ALL (WHO 5th Edition)</t>
   </si>
 </sst>
 </file>
@@ -5584,12 +5585,12 @@
         <v>419</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C11" t="s">
         <v>420</v>
@@ -5600,7 +5601,7 @@
         <v>106</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C12" t="s">
         <v>419</v>

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63351A8E-BECB-4690-B03C-ABABE7797E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD33606-211A-4B34-B961-8B35199BDD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="1365" windowWidth="25170" windowHeight="13965" firstSheet="1" activeTab="7" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="29790" yWindow="-585" windowWidth="24390" windowHeight="14730" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -1038,9 +1038,6 @@
   <si>
     <t>BCL2 mutations are aquired in approximately 50% of CLL/SLL cases progressing on treatment with BCL2 inhibitors (including venetoclax) (WHO 5th edition). 
 *refer to BCL2 table for reportable variants*</t>
-  </si>
-  <si>
-    <t>NOTCH1 is one of the most frequently mutated genes in CLL/SLL at the time of first treatment (WHO 5th edition). NOTCH1 mutations have been associated with poorer prognsis, however their significance in the context of novel therapies remains uncertain (DOI: 10.1182/blood-2017-09-806398).</t>
   </si>
   <si>
     <t>PLCG2 mutations have been reported in CLL patients progressing under treatment with BTK mutations (DOI: 10.1182/blood-2024-200896).</t>
@@ -1482,9 +1479,6 @@
     <t>UBTF</t>
   </si>
   <si>
-    <t>Recurrent exon 13 tandem duplications (TD) in UBTF have emerged as a major subtype-defining genomic alteration in paediatric AML that is associated with poor prognosis and has also recently been reported in 1.2% of all individuals over 18 years of age (DOI: 10.1182/blood.2023021359).</t>
-  </si>
-  <si>
     <t>UBA1</t>
   </si>
   <si>
@@ -1711,9 +1705,6 @@
   </si>
   <si>
     <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FBXW7, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NOTCH1, NRAS, NUDT15, PAX5, PHF6, PPM1D, PRPF8, PTEN, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, TPMT, U2AF1, UBA1, WT1, ZRSR2 genes.</t>
-  </si>
-  <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NRAS, PHF6, PPM1D, PRPF8, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, UBA1, UBTF, U2AF1, WT1, ZRSR2  genes.</t>
   </si>
   <si>
     <t>No pertinent (tier 1 or tier 2) copy number aberrations were detected in this sample. 
@@ -1953,6 +1944,16 @@
   <si>
     <t>KRAS mutations have been reported in B-ALL; their prognostic significance  is influenced by the B-ALL subtype and therefore should be interpreted in the context of other clinical and pathological data.
 KRAS mutations have been reported in T-ALL (WHO 5th Edition)</t>
+  </si>
+  <si>
+    <t>NOTCH1 is one of the most frequently mutated genes in CLL/SLL at the time of first treatment (WHO 5th edition). NOTCH1 mutations have been associated with poorer prognosis, however their significance in the context of novel therapies remains uncertain (DOI: 10.1182/blood-2017-09-806398).</t>
+  </si>
+  <si>
+    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NRAS, PHF6, PPM1D, PRPF8, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, UBA1, U2AF1, WT1, ZRSR2  genes.</t>
+  </si>
+  <si>
+    <t>Coordinates (GRCh38): chr17:44,210,790-44,210,949
+Recurrent exon 13 tandem duplications (TD) in UBTF have emerged as a major subtype-defining genomic alteration in paediatric AML that is associated with poor prognosis and has also recently been reported in 1.2% of all individuals over 18 years of age (DOI: 10.1182/blood.2023021359).</t>
   </si>
 </sst>
 </file>
@@ -2461,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="105.75" x14ac:dyDescent="0.25">
@@ -2472,7 +2473,7 @@
         <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="F2" s="6"/>
     </row>
@@ -2484,7 +2485,7 @@
         <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2495,7 +2496,7 @@
         <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2506,7 +2507,7 @@
         <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -2517,7 +2518,7 @@
         <v>143</v>
       </c>
       <c r="C6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2528,18 +2529,18 @@
         <v>121</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="C8" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2550,7 +2551,7 @@
         <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.2">
@@ -2558,10 +2559,10 @@
         <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
@@ -2572,7 +2573,7 @@
         <v>123</v>
       </c>
       <c r="C11" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="255" x14ac:dyDescent="0.2">
@@ -2583,7 +2584,7 @@
         <v>124</v>
       </c>
       <c r="C12" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="167.25" x14ac:dyDescent="0.2">
@@ -2591,10 +2592,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C13" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.2">
@@ -2605,7 +2606,7 @@
         <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="180" x14ac:dyDescent="0.2">
@@ -2616,7 +2617,7 @@
         <v>126</v>
       </c>
       <c r="C15" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="105" x14ac:dyDescent="0.2">
@@ -2627,7 +2628,7 @@
         <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="333" x14ac:dyDescent="0.2">
@@ -2635,10 +2636,10 @@
         <v>66</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C17" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -2649,7 +2650,7 @@
         <v>127</v>
       </c>
       <c r="C18" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -2660,7 +2661,7 @@
         <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -2671,7 +2672,7 @@
         <v>144</v>
       </c>
       <c r="C20" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -2679,10 +2680,10 @@
         <v>72</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C21" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -2690,10 +2691,10 @@
         <v>73</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C22" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2704,7 +2705,7 @@
         <v>129</v>
       </c>
       <c r="C23" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -2712,10 +2713,10 @@
         <v>78</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C24" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2726,7 +2727,7 @@
         <v>130</v>
       </c>
       <c r="C25" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2737,7 +2738,7 @@
         <v>131</v>
       </c>
       <c r="C26" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -2748,7 +2749,7 @@
         <v>132</v>
       </c>
       <c r="C27" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -2759,7 +2760,7 @@
         <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="285" x14ac:dyDescent="0.2">
@@ -2770,7 +2771,7 @@
         <v>134</v>
       </c>
       <c r="C29" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -2781,7 +2782,7 @@
         <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -2792,7 +2793,7 @@
         <v>135</v>
       </c>
       <c r="C31" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2803,7 +2804,7 @@
         <v>145</v>
       </c>
       <c r="C32" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -2814,7 +2815,7 @@
         <v>146</v>
       </c>
       <c r="C33" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -2825,7 +2826,7 @@
         <v>136</v>
       </c>
       <c r="C34" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2836,7 +2837,7 @@
         <v>147</v>
       </c>
       <c r="C35" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="345" x14ac:dyDescent="0.2">
@@ -2847,7 +2848,7 @@
         <v>137</v>
       </c>
       <c r="C36" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -2858,7 +2859,7 @@
         <v>148</v>
       </c>
       <c r="C37" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -2869,7 +2870,7 @@
         <v>149</v>
       </c>
       <c r="C38" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -2880,7 +2881,7 @@
         <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -2891,7 +2892,7 @@
         <v>150</v>
       </c>
       <c r="C40" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -2902,7 +2903,7 @@
         <v>138</v>
       </c>
       <c r="C41" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -2913,7 +2914,7 @@
         <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2924,7 +2925,7 @@
         <v>140</v>
       </c>
       <c r="C43" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -2935,7 +2936,7 @@
         <v>151</v>
       </c>
       <c r="C44" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -2946,7 +2947,7 @@
         <v>152</v>
       </c>
       <c r="C45" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -2957,7 +2958,7 @@
         <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -2968,18 +2969,18 @@
         <v>119</v>
       </c>
       <c r="C47" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>306</v>
+        <v>438</v>
       </c>
       <c r="C48" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -2987,10 +2988,10 @@
         <v>108</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C49" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -3001,7 +3002,7 @@
         <v>119</v>
       </c>
       <c r="C50" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -3032,10 +3033,10 @@
     </row>
     <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3056,10 +3057,10 @@
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.2">
@@ -3067,7 +3068,7 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
@@ -3096,58 +3097,58 @@
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -3177,79 +3178,79 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>381</v>
+        <v>437</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="105" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3269,10 +3270,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>16</v>
@@ -3283,7 +3284,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>48</v>
@@ -3305,10 +3306,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3316,10 +3317,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3327,10 +3328,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="225" x14ac:dyDescent="0.2">
@@ -3338,7 +3339,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>46</v>
@@ -3374,7 +3375,7 @@
         <v>51</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3437,10 +3438,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3456,112 +3457,112 @@
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>339</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>342</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>343</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>346</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>348</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>351</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>352</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
+        <v>352</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>354</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>355</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="60" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>362</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>363</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -3589,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3600,7 +3601,7 @@
         <v>195</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3611,7 +3612,7 @@
         <v>232</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -3622,7 +3623,7 @@
         <v>196</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3633,7 +3634,7 @@
         <v>197</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3644,7 +3645,7 @@
         <v>233</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3655,7 +3656,7 @@
         <v>198</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3666,7 +3667,7 @@
         <v>199</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3677,7 +3678,7 @@
         <v>200</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3688,7 +3689,7 @@
         <v>201</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3699,7 +3700,7 @@
         <v>202</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -3710,7 +3711,7 @@
         <v>203</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -3721,7 +3722,7 @@
         <v>204</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3732,7 +3733,7 @@
         <v>205</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -3743,7 +3744,7 @@
         <v>206</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3754,7 +3755,7 @@
         <v>234</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3765,7 +3766,7 @@
         <v>207</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -3776,7 +3777,7 @@
         <v>208</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -3787,7 +3788,7 @@
         <v>128</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3798,7 +3799,7 @@
         <v>209</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3809,7 +3810,7 @@
         <v>210</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3820,7 +3821,7 @@
         <v>211</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3828,7 +3829,7 @@
         <v>74</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -3839,7 +3840,7 @@
         <v>235</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -3847,10 +3848,10 @@
         <v>78</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -3861,7 +3862,7 @@
         <v>212</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3872,7 +3873,7 @@
         <v>213</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -3883,7 +3884,7 @@
         <v>236</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3894,7 +3895,7 @@
         <v>214</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3905,10 +3906,10 @@
         <v>215</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="90" x14ac:dyDescent="0.2">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="105" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>87</v>
       </c>
@@ -3916,7 +3917,7 @@
         <v>216</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -3927,7 +3928,7 @@
         <v>217</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3938,7 +3939,7 @@
         <v>218</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -3949,7 +3950,7 @@
         <v>219</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3960,7 +3961,7 @@
         <v>220</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="369" customHeight="1" x14ac:dyDescent="0.2">
@@ -3971,7 +3972,7 @@
         <v>221</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -3982,7 +3983,7 @@
         <v>237</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -3993,7 +3994,7 @@
         <v>223</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4004,7 +4005,7 @@
         <v>238</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -4015,7 +4016,7 @@
         <v>224</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4026,7 +4027,7 @@
         <v>225</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -4037,7 +4038,7 @@
         <v>222</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -4048,7 +4049,7 @@
         <v>226</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -4059,7 +4060,7 @@
         <v>227</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4070,7 +4071,7 @@
         <v>228</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4081,7 +4082,7 @@
         <v>228</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4089,10 +4090,10 @@
         <v>105</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="210" x14ac:dyDescent="0.2">
@@ -4100,10 +4101,10 @@
         <v>106</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -4114,18 +4115,18 @@
         <v>229</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -4136,7 +4137,7 @@
         <v>230</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4147,7 +4148,7 @@
         <v>231</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -4174,7 +4175,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4185,7 +4186,7 @@
         <v>153</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="285" x14ac:dyDescent="0.2">
@@ -4196,7 +4197,7 @@
         <v>163</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4207,7 +4208,7 @@
         <v>154</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4218,7 +4219,7 @@
         <v>155</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4229,7 +4230,7 @@
         <v>156</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -4240,7 +4241,7 @@
         <v>157</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4251,7 +4252,7 @@
         <v>158</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4262,7 +4263,7 @@
         <v>159</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4273,7 +4274,7 @@
         <v>160</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4284,7 +4285,7 @@
         <v>161</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4295,7 +4296,7 @@
         <v>162</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -4303,10 +4304,10 @@
         <v>37</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -4314,10 +4315,10 @@
         <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4328,7 +4329,7 @@
         <v>164</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4339,7 +4340,7 @@
         <v>165</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4350,7 +4351,7 @@
         <v>166</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4361,7 +4362,7 @@
         <v>167</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -4372,7 +4373,7 @@
         <v>168</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -4383,7 +4384,7 @@
         <v>169</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4394,7 +4395,7 @@
         <v>170</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -4405,7 +4406,7 @@
         <v>171</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -4416,7 +4417,7 @@
         <v>172</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="240" x14ac:dyDescent="0.2">
@@ -4424,10 +4425,10 @@
         <v>77</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4435,10 +4436,10 @@
         <v>78</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="409.5" x14ac:dyDescent="0.2">
@@ -4449,7 +4450,7 @@
         <v>173</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4460,7 +4461,7 @@
         <v>174</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4471,7 +4472,7 @@
         <v>175</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4482,7 +4483,7 @@
         <v>176</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -4493,7 +4494,7 @@
         <v>177</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -4504,7 +4505,7 @@
         <v>178</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4515,7 +4516,7 @@
         <v>179</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4526,7 +4527,7 @@
         <v>180</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -4537,7 +4538,7 @@
         <v>181</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4548,7 +4549,7 @@
         <v>182</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -4556,10 +4557,10 @@
         <v>79</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4570,7 +4571,7 @@
         <v>193</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4581,7 +4582,7 @@
         <v>194</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="270" x14ac:dyDescent="0.2">
@@ -4592,7 +4593,7 @@
         <v>183</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4603,7 +4604,7 @@
         <v>184</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -4614,7 +4615,7 @@
         <v>185</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4625,7 +4626,7 @@
         <v>186</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4636,7 +4637,7 @@
         <v>187</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4647,7 +4648,7 @@
         <v>188</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="170.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4658,7 +4659,7 @@
         <v>189</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="135" x14ac:dyDescent="0.2">
@@ -4669,7 +4670,7 @@
         <v>190</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4680,7 +4681,7 @@
         <v>191</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -4689,7 +4690,7 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="195" x14ac:dyDescent="0.2">
@@ -4700,7 +4701,7 @@
         <v>192</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -4727,7 +4728,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4735,10 +4736,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -4749,18 +4750,18 @@
         <v>239</v>
       </c>
       <c r="C3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="C4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -4771,7 +4772,7 @@
         <v>240</v>
       </c>
       <c r="C5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F5" s="6"/>
     </row>
@@ -4780,10 +4781,10 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4791,10 +4792,10 @@
         <v>88</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4802,10 +4803,10 @@
         <v>106</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C8" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -4832,7 +4833,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4840,10 +4841,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4851,10 +4852,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -4862,10 +4863,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4873,10 +4874,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -4884,10 +4885,10 @@
         <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -4895,10 +4896,10 @@
         <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4906,10 +4907,10 @@
         <v>116</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C8" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -4917,10 +4918,10 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4928,10 +4929,10 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C10" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -4939,10 +4940,10 @@
         <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C11" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4950,10 +4951,10 @@
         <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C12" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -4961,10 +4962,10 @@
         <v>65</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C13" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -4972,10 +4973,10 @@
         <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C14" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -4983,21 +4984,21 @@
         <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C15" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C16" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5005,10 +5006,10 @@
         <v>76</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C17" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -5016,10 +5017,10 @@
         <v>96</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C18" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5027,10 +5028,10 @@
         <v>80</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C19" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5038,10 +5039,10 @@
         <v>117</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C20" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -5049,10 +5050,10 @@
         <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C21" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -5060,10 +5061,10 @@
         <v>85</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C22" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -5071,10 +5072,10 @@
         <v>86</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C23" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -5082,65 +5083,65 @@
         <v>88</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C24" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C25" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C26" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C27" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C28" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="75" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C29" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="240" x14ac:dyDescent="0.2">
@@ -5148,10 +5149,10 @@
         <v>106</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C30" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -5178,7 +5179,7 @@
         <v>241</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5186,10 +5187,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5197,21 +5198,21 @@
         <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5219,10 +5220,10 @@
         <v>73</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -5230,54 +5231,54 @@
         <v>75</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C8" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5285,21 +5286,21 @@
         <v>97</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C12" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="180" x14ac:dyDescent="0.2">
@@ -5307,10 +5308,10 @@
         <v>104</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C13" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="90" x14ac:dyDescent="0.2">
@@ -5318,10 +5319,10 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C14" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5329,21 +5330,21 @@
         <v>105</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C15" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C16" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -5368,7 +5369,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -5379,7 +5380,7 @@
         <v>242</v>
       </c>
       <c r="C2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.2">
@@ -5390,7 +5391,7 @@
         <v>244</v>
       </c>
       <c r="C3" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D3" s="11"/>
     </row>
@@ -5402,7 +5403,7 @@
         <v>243</v>
       </c>
       <c r="C4" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="405" x14ac:dyDescent="0.2">
@@ -5410,10 +5411,10 @@
         <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.2">
@@ -5421,10 +5422,10 @@
         <v>85</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>245</v>
+        <v>436</v>
       </c>
       <c r="C6" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -5432,10 +5433,10 @@
         <v>91</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -5443,10 +5444,10 @@
         <v>100</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C8" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.2">
@@ -5454,10 +5455,10 @@
         <v>106</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -5485,7 +5486,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5493,10 +5494,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="75" x14ac:dyDescent="0.2">
@@ -5504,10 +5505,10 @@
         <v>64</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C3" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5515,10 +5516,10 @@
         <v>118</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -5527,7 +5528,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -5535,10 +5536,10 @@
         <v>74</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5546,10 +5547,10 @@
         <v>85</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C7" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.2">
@@ -5557,21 +5558,21 @@
         <v>88</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C8" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="150" x14ac:dyDescent="0.2">
@@ -5579,10 +5580,10 @@
         <v>89</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="60" x14ac:dyDescent="0.2">
@@ -5590,10 +5591,10 @@
         <v>96</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="165" x14ac:dyDescent="0.2">
@@ -5601,10 +5602,10 @@
         <v>106</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C12" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -5618,7 +5619,7 @@
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="75.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="74.5546875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
@@ -5630,7 +5631,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="105" x14ac:dyDescent="0.2">
@@ -5638,21 +5639,21 @@
         <v>10</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C3" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="120" x14ac:dyDescent="0.2">
@@ -5660,10 +5661,10 @@
         <v>80</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5671,10 +5672,10 @@
         <v>88</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5682,10 +5683,10 @@
         <v>96</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.2">
@@ -5693,53 +5694,53 @@
         <v>71</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C8" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C12" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD33606-211A-4B34-B961-8B35199BDD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A350DDE9-0389-4D2E-9438-9AF81A7D6E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29790" yWindow="-585" windowWidth="24390" windowHeight="14730" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="32130" yWindow="1125" windowWidth="27450" windowHeight="12630" activeTab="11" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -1949,11 +1949,12 @@
     <t>NOTCH1 is one of the most frequently mutated genes in CLL/SLL at the time of first treatment (WHO 5th edition). NOTCH1 mutations have been associated with poorer prognosis, however their significance in the context of novel therapies remains uncertain (DOI: 10.1182/blood-2017-09-806398).</t>
   </si>
   <si>
-    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NRAS, PHF6, PPM1D, PRPF8, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, UBA1, U2AF1, WT1, ZRSR2  genes.</t>
-  </si>
-  <si>
     <t>Coordinates (GRCh38): chr17:44,210,790-44,210,949
 Recurrent exon 13 tandem duplications (TD) in UBTF have emerged as a major subtype-defining genomic alteration in paediatric AML that is associated with poor prognosis and has also recently been reported in 1.2% of all individuals over 18 years of age (DOI: 10.1182/blood.2023021359).</t>
+  </si>
+  <si>
+    <t>AML samples: remeber to manually check UBTF for partial tandem duplication. Instructions on iPassport - GEN-SOP 850: NGS analysis and Webserver Instructions (Version 2.0). Coordinates (GRCh38): chr17:44,210,790-44,210,949
+No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NRAS, PHF6, PPM1D, PRPF8, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, UBA1, U2AF1, WT1, ZRSR2  genes.</t>
   </si>
 </sst>
 </file>
@@ -2977,7 +2978,7 @@
         <v>304</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C48" t="s">
         <v>417</v>
@@ -3181,12 +3182,12 @@
         <v>411</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="135" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>374</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="105" x14ac:dyDescent="0.2">

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A350DDE9-0389-4D2E-9438-9AF81A7D6E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FD1FBF-264F-4824-9537-5F695F37D3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32130" yWindow="1125" windowWidth="27450" windowHeight="12630" activeTab="11" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="32130" yWindow="1125" windowWidth="27450" windowHeight="12630" activeTab="10" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -1953,7 +1953,7 @@
 Recurrent exon 13 tandem duplications (TD) in UBTF have emerged as a major subtype-defining genomic alteration in paediatric AML that is associated with poor prognosis and has also recently been reported in 1.2% of all individuals over 18 years of age (DOI: 10.1182/blood.2023021359).</t>
   </si>
   <si>
-    <t>AML samples: remeber to manually check UBTF for partial tandem duplication. Instructions on iPassport - GEN-SOP 850: NGS analysis and Webserver Instructions (Version 2.0). Coordinates (GRCh38): chr17:44,210,790-44,210,949
+    <t>****AML samples: remeber to manually check UBTF for partial tandem duplication. Instructions on iPassport - GEN-SOP 850: NGS analysis and Webserver Instructions (Version 2.0). Coordinates (GRCh38): chr17:44,210,790-44,210,949****
 No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NRAS, PHF6, PPM1D, PRPF8, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, UBA1, U2AF1, WT1, ZRSR2  genes.</t>
   </si>
 </sst>

--- a/NGS_comments_automation.xlsx
+++ b/NGS_comments_automation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\MOLECULAR DIAGNOSTICS\Clinical Scientists\Training Records\Brittany\Haemonc NGS\Comments streamlit version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FD1FBF-264F-4824-9537-5F695F37D3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498CB4EB-B985-43D2-A12B-9DD51CB25125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32130" yWindow="1125" windowWidth="27450" windowHeight="12630" activeTab="10" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="23355" windowHeight="14475" firstSheet="2" activeTab="2" xr2:uid="{E8EAE7A0-7C8C-4249-A16E-D20591EF97F9}"/>
   </bookViews>
   <sheets>
     <sheet name="AML" sheetId="1" r:id="rId1"/>
@@ -1953,8 +1953,7 @@
 Recurrent exon 13 tandem duplications (TD) in UBTF have emerged as a major subtype-defining genomic alteration in paediatric AML that is associated with poor prognosis and has also recently been reported in 1.2% of all individuals over 18 years of age (DOI: 10.1182/blood.2023021359).</t>
   </si>
   <si>
-    <t>****AML samples: remeber to manually check UBTF for partial tandem duplication. Instructions on iPassport - GEN-SOP 850: NGS analysis and Webserver Instructions (Version 2.0). Coordinates (GRCh38): chr17:44,210,790-44,210,949****
-No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NRAS, PHF6, PPM1D, PRPF8, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, UBA1, U2AF1, WT1, ZRSR2  genes.</t>
+    <t>No pathogenic/likely pathogenic variants were detected in the regions analysed within the ABL1, ANKRD26, ASXL1, BCL2, BCOR, BCORL1, CALR, CBFB, CBL, CEBPA, CSF3R, CUX1, DDX41, DNMT3A, ETNK1, ETV6, EZH2, FLT3, GATA1, GATA2, GNB1, HRAS, IDH1, IDH2, IKZF1, JAK2, KIT, KMT2A, KRAS, MPL, MYC, NF1, NFE2, NPM1, NRAS, PHF6, PPM1D, PRPF8, PTPN11, RAD21, RHOA, RUNX1, SETBP1, SF1, SF3B1, SH2B3, SMC3, SRSF2, STAG2, STAT3, STAT5B, TET2, TP53, UBA1, U2AF1, WT1, ZRSR2  genes.</t>
   </si>
 </sst>
 </file>
@@ -3182,7 +3181,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="135" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>374</v>
       </c>
@@ -3910,7 +3909,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="105" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="90" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>87</v>
       </c>
